--- a/data/review/audit_T6.xlsx
+++ b/data/review/audit_T6.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F3F00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,8 +429,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="24" max="24"/>
+    <col width="80" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -532,6 +552,16 @@
           <t>audit_note</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trich_van_ban_goc</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>trich_van_ban_tac_dong</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -584,9 +614,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32593</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -602,17 +629,28 @@
           <t>question_leaks</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Câu hỏi đã nêu khung phạt và diễn đạt lại hành vi (kết quả không đúng với thực tế), đáp án chỉ nhắc lại</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>163/2013/NĐ-CP · hiệu lực 2013-12-31 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 24. Hành vi vi phạm quy định về lấy mẫu và phân tích phân bón
+2. Phạt tiền từ 5.000.000 đồng đến 10.000.000 đồng đối với một trong các hành vi sau đây:
+a) Làm sai lệch kết quả hoặc công bố sai kết quả phân tích kiểm nghiệm chất lượng phân bón;
+b) Không bảo mật các thông tin, số liệu, kết quả lấy mẫu, kiểm định, kiểm nghiệm, chứng nhận chất lượng.</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 55/2018/NĐ-CP · hiệu lực 2018-04-16
+2. Nghị định này bãi bỏ Điều 19, 20, 21, 23, 24, 25 Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013 quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất, phân bón và vật liệu nổ công nghiệp; khoản 18, 19, 20, 21, 22, 23 Điều 1 Nghị định số 115/2016/NĐ-CP ngày 08 tháng 7 năm 2016 sửa đổi, bổ sung một số điều của Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013 của Chính phủ quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất, phân bón và vật liệu nổ công nghiệp.
+CHUYỂN TIẾP: Điều 22. Điều khoản chuyển tiếp
+Các hành vi vi phạm hành chính trong lĩnh phân bón được thực hiện hoặc phát hiện trước ngày Nghị định này có hiệu lực thi hành mà đang xem xét, giải quyết thì xử phạt theo Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013 của Chính phủ quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất, phân bón và vật liệu nổ công nghiệp và Nghị định số 115/2016/NĐ-CP ngày 08 tháng 7 năm 2016 sửa đổi, bổ sung một số điều của Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013, trừ trường hợp hành vi vi phạm hành chính của Nghị định này có quy định trách nhiệm pháp lý nhẹ hơn thì xử phạt theo Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -640,7 +678,6 @@
           <t>2023-03-24 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -661,9 +698,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32593</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -679,17 +713,28 @@
           <t>question_leaks</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Như dòng trước. 55/2018/NĐ-CP Điều 9 không có hành vi làm sai lệch, công bố sai kết quả phân tích, không chuyển chỗ</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>163/2013/NĐ-CP · hiệu lực 2013-12-31 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 24. Hành vi vi phạm quy định về lấy mẫu và phân tích phân bón
+2. Phạt tiền từ 5.000.000 đồng đến 10.000.000 đồng đối với một trong các hành vi sau đây:
+a) Làm sai lệch kết quả hoặc công bố sai kết quả phân tích kiểm nghiệm chất lượng phân bón;
+b) Không bảo mật các thông tin, số liệu, kết quả lấy mẫu, kiểm định, kiểm nghiệm, chứng nhận chất lượng.</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 55/2018/NĐ-CP · hiệu lực 2018-04-16
+2. Nghị định này bãi bỏ Điều 19, 20, 21, 23, 24, 25 Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013 quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất, phân bón và vật liệu nổ công nghiệp; khoản 18, 19, 20, 21, 22, 23 Điều 1 Nghị định số 115/2016/NĐ-CP ngày 08 tháng 7 năm 2016 sửa đổi, bổ sung một số điều của Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013 của Chính phủ quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất, phân bón và vật liệu nổ công nghiệp.
+CHUYỂN TIẾP: Điều 22. Điều khoản chuyển tiếp
+Các hành vi vi phạm hành chính trong lĩnh phân bón được thực hiện hoặc phát hiện trước ngày Nghị định này có hiệu lực thi hành mà đang xem xét, giải quyết thì xử phạt theo Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013 của Chính phủ quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất, phân bón và vật liệu nổ công nghiệp và Nghị định số 115/2016/NĐ-CP ngày 08 tháng 7 năm 2016 sửa đổi, bổ sung một số điều của Nghị định số 163/2013/NĐ-CP ngày 12 tháng 11 năm 2013, trừ trường hợp hành vi vi phạm hành chính của Nghị định này có quy định trách nhiệm pháp lý nhẹ hơn thì xử phạt theo Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -742,9 +787,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118309</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -760,17 +802,32 @@
           <t>question_leaks</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Câu hỏi đã nêu hành vi (công bố công khai Điều lệ đua) và khung phạt; đáp án chỉ thêm chữ "không"</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>06/2017/NĐ-CP · hiệu lực 2017-03-31 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 56. Hành vi vi phạm quy định về xây dựng, ban hành và công bố Điều lệ đua và Thể lệ đặt cược
+2. Phạt tiền từ 90.000.000 đồng đến 100.000.000 đồng đối với một trong các hành vi vi phạm sau:
+a) Không công bố công khai Thể lệ đặt cược theo quy định tại Điều 9 của Nghị định này;
+b) Không công bố công khai Điều lệ đua theo quy định tại Điều 25 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 137/2021/NĐ-CP · hiệu lực 2022-01-01
+a) Chương VII Nghị định số 06/2017/NĐ-CP ngày 24 tháng 01 năm 2017 của Chính phủ về kinh doanh đặt cược đua ngựa, đua chó và bóng đá quốc tế;
+b) Chương VII Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino;
+c) Chương VII Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài;
+d) Khoản 13, khoản 14 và khoản 15 Điều 1 Nghị định số 175/2016/NĐ-CP ngày 30 tháng 12 năm 2016 của Chính phủ sửa đổi, bổ sung một số điều quy định tại Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài.
+CHUYỂN TIẾP: Điều 63. Điều khoản chuyển tiếp
+1. Đối với hành vi vi phạm xảy ra trước thời điểm Nghị định này có hiệu lực mà bị phát hiện hoặc xem xét ra quyết định xử phạt khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn.
+2. Đối với các quyết định xử phạt vi phạm hành chính trong lĩnh vực đặt cược và trò chơi có thưởng đã được ban hành hoặc được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 06/2017/NĐ-CP ngày 24 tháng 01 năm 2017 của Chính phủ về kinh doanh đặt cược đua ngựa, đua chó và bóng đá quốc tế, Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino và Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài để giải quyết.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -798,7 +855,6 @@
           <t>2023-12-26 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -819,9 +875,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118309</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -837,17 +890,32 @@
           <t>question_leaks,gold_wrong</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Như dòng trước. Chuyển chỗ: 137/2021/NĐ-CP điểm b khoản 2 Điều 14 "Không công bố công khai Điều lệ đua theo quy định của pháp luật", cùng khung 90.000.000–100.000.000 đồng; cùng Chính phủ, cùng nghị định bãi bỏ Chương VII NĐ 06/2017</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>06/2017/NĐ-CP · hiệu lực 2017-03-31 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 56. Hành vi vi phạm quy định về xây dựng, ban hành và công bố Điều lệ đua và Thể lệ đặt cược
+2. Phạt tiền từ 90.000.000 đồng đến 100.000.000 đồng đối với một trong các hành vi vi phạm sau:
+a) Không công bố công khai Thể lệ đặt cược theo quy định tại Điều 9 của Nghị định này;
+b) Không công bố công khai Điều lệ đua theo quy định tại Điều 25 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 137/2021/NĐ-CP · hiệu lực 2022-01-01
+a) Chương VII Nghị định số 06/2017/NĐ-CP ngày 24 tháng 01 năm 2017 của Chính phủ về kinh doanh đặt cược đua ngựa, đua chó và bóng đá quốc tế;
+b) Chương VII Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino;
+c) Chương VII Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài;
+d) Khoản 13, khoản 14 và khoản 15 Điều 1 Nghị định số 175/2016/NĐ-CP ngày 30 tháng 12 năm 2016 của Chính phủ sửa đổi, bổ sung một số điều quy định tại Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài.
+CHUYỂN TIẾP: Điều 63. Điều khoản chuyển tiếp
+1. Đối với hành vi vi phạm xảy ra trước thời điểm Nghị định này có hiệu lực mà bị phát hiện hoặc xem xét ra quyết định xử phạt khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn.
+2. Đối với các quyết định xử phạt vi phạm hành chính trong lĩnh vực đặt cược và trò chơi có thưởng đã được ban hành hoặc được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 06/2017/NĐ-CP ngày 24 tháng 01 năm 2017 của Chính phủ về kinh doanh đặt cược đua ngựa, đua chó và bóng đá quốc tế, Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino và Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài để giải quyết.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -875,7 +943,6 @@
           <t>2026-03-01 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -896,9 +963,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178290</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -914,17 +978,34 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 332/2025/NĐ-CP điểm a khoản 1 Điều 49 "Ủy ban nhân dân cấp tỉnh cấp Giấy phép tiến hành công việc bức xạ … sử dụng thiết bị X-quang chẩn đoán y tế, PET/CT, SPECT/CT, thiết bị phát tia X (trừ … chụp ảnh phóng xạ công nghiệp)"; cùng Chính phủ, cùng nghị định chấm dứt Điều 45–47 NĐ 133/2025</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>133/2025/NĐ-CP · hiệu lực 2025-07-01 → 2027-03-01 · lúc thu thập: Còn hiệu lực
+Điều 45. Cấp giấy phép sử dụng thiết bị bức xạ chụp cắt lớp vi tính tích hợp với PET (PET/CT), tích hợp với SPECT (SPECT/CT); thiết bị bức xạ phát tia X trong phân tích huỳnh quang tia X, phân tích nhiễu xạ tia X, soi bo mạch, soi hiển vi điện tử, soi kiểm tra an ninh
+1. Việc cấp giấy phép sử dụng thiết bị bức xạ chụp cắt lớp vi tính tích hợp với PET (PET/CT), tích hợp với SPECT (SPECT/CT); thiết bị bức xạ phát tia X trong phân tích huỳnh quang tia X, phân tích nhiễu xạ tia X, soi bò mạch, soi hiển vi điện tử, soi kiểm tra an ninh quy định tại điểm d khoản 2 Điều 1, khoản 1 Điều 28 Nghị định số 142/2020/NĐ-CP ngày 09 tháng 12 năm 2020 của Chính phủ quy định về việc tiến hành công việc bức xạ và hoạt động dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử (sau đây gọi là Nghị định số 142/2020/NĐ-CP) do Ủy ban nhân dân cấp tỉnh thực hiện.</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 332/2025/NĐ-CP · hiệu lực 2026-01-01
+5. Các Điều 45, Điều 46, Điều 47 Nghị định số 133/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ ban hành quy định về phân quyền, phân cấp trong lĩnh vực quản lý nhà nước của Bộ Khoa học và Công nghệ hết hiệu lực kể từ ngày Nghị định này có hiệu lực thi hành.
+6. Điều kiện nhân lực có bằng tốt nghiệp từ đại học trở lên về vật lý y khoa hoặc được công nhận, xác nhận trình độ tương đương quy định tại điểm c, điểm d khoản 1 Điều 23, điểm d khoản 1 Điều 25 Nghị định này được áp dụng kể từ ngày 01 tháng 01 năm 2031.
+7. Điều kiện về có chương trình bảo đảm chất lượng thực hiện dịch vụ, được quản lý phù hợp theo tiêu chuẩn quốc tế ISO 21000 quy định tại khoản 4 Điều 63 Nghị định này:
+a) Tổ chức được cấp giấy đăng ký hoạt động đào tạo an toàn bức xạ; đào tạo, bồi dưỡng chuyên môn, nghiệp vụ trước thời điểm Nghị định này có hiệu lực phải xây dựng và quản lý chất lượng theo tiêu chuẩn quốc tế ISO 21000 kể từ ngày 01 tháng 01 năm 2029;
+b) Tổ chức được cấp giấy đăng ký hoạt động đào tạo an toàn bức xạ; đào tạo, bồi dưỡng chuyên môn, nghiệp vụ sau thời điểm Nghị định này có hiệu lực phải xây dựng và quản lý chất lượng theo tiêu chuẩn quốc tế ISO 21000 trong thời hạn 03 năm kể từ thời điểm được cấp giấy đăng ký.
+CHUYỂN TIẾP: Điều 106. Điều khoản chuyển tiếp
+Quy định về một số trường hợp chuyển tiếp:
+1. Giấy phép tiến hành công việc bức xạ, Giấy đăng ký hoạt động dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử, Chứng chỉ nhân viên bức xạ, Chứng chỉ hành nghề dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử đã được cơ quan có thẩm quyền cấp trước ngày Nghị định này có hiệu lực thi hành được tiếp tục sử dụng đến hết thời hạn ghi trong giấy phép, giấy đăng ký, chứng chỉ, chứng chỉ hành nghề. Chứng chỉ nhân viên bức xạ hoặc chứng chỉ hành nghề dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử có hiệu lực đã được cơ quan có thẩm quyền cấp không quy định thời hạn trước ngày Nghị định này có hiệu lực thi hành thì có hiệu lực 05 năm kể từ ngày Nghị định này có hiệu lực.
+2. Trường hợp tổ chức, cá nhân đã nộp hồ sơ đề nghị cấp, sửa đổi, bổ sung, gia hạn Giấy phép tiến hành công việc bức xạ, Giấy đăng ký hoạt động dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử, Chứng chỉ hành nghề dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử, Chứng chỉ nhân viên bức xạ mà đến ngày Nghị định này có hiệu lực thi hành chưa được cấp Giấy phép, Giấy đăng ký, Chứng chỉ thì hồ sơ tiếp tục được xử lý theo quy định của pháp luật về năng lượng nguyên tử trước ngày Nghị định này có hiệu lực thi hành.
+3. Các quy chuẩn kỹ thuật quốc gia về an toàn bức xạ, phân nhóm nguồn phóng xạ, miễn trừ khai báo, cấp giấy phép, quy chuẩn kỹ thuật quốc gia đối với máy gia tốc trong xạ trị và thiết bị X-quang trong y tế tiếp tục được áp dụng cho đến khi có văn bản thay thế.
+4. Trường hợp văn bản quy phạm pháp luật được dẫn chiếu tại Nghị định này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo văn bản mới.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -952,7 +1033,6 @@
           <t>2026-06-26 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -973,9 +1053,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178290</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -991,17 +1068,34 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 332/2025/NĐ-CP Điều 36 (khoản 2 điểm a: hồ sơ cấp chứng chỉ nhân viên bức xạ cho người phụ trách an toàn khi dùng PET/CT, SPECT/CT, thiết bị phát tia X nộp tại Trung tâm Phục vụ hành chính công cấp tỉnh); cùng Chính phủ, cùng nghị định chấm dứt Điều 45–47 NĐ 133/2025. Đáp án cũ chỉ dẫn Phụ lục IV nên người audit xem lại yếu tố 4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>133/2025/NĐ-CP · hiệu lực 2025-07-01 → 2027-03-01 · lúc thu thập: Còn hiệu lực
+Điều 46. Cấp chứng chỉ nhân viên bức xạ cho người phụ trách an toàn trong sử dụng thiết bị chụp cắt lớp vi tính tích hợp với PET (PET/CT), tích hợp với SPECT (SPECT/CT), thiết bị phát tia X trong phân tích nhiễu xạ tia X, soi hiển vi điện tử, soi kiểm tra an ninh
+2. Trình tự, thủ tục cấp chứng chỉ nhân viên bức xạ cho người phụ trách an toàn tại cơ sở sử dụng thiết bị bức xạ chụp cắt lớp vi tính tích hợp với PET (PET/CT), tích hợp với SPECT (SPECT/CT), thiết bị phát tia X trong phân tích nhiễu xạ tia X, soi hiển vi điện tử, soi kiểm tra an ninh được quy định tại Mục II Phụ lục IV ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 332/2025/NĐ-CP · hiệu lực 2026-01-01
+5. Các Điều 45, Điều 46, Điều 47 Nghị định số 133/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ ban hành quy định về phân quyền, phân cấp trong lĩnh vực quản lý nhà nước của Bộ Khoa học và Công nghệ hết hiệu lực kể từ ngày Nghị định này có hiệu lực thi hành.
+6. Điều kiện nhân lực có bằng tốt nghiệp từ đại học trở lên về vật lý y khoa hoặc được công nhận, xác nhận trình độ tương đương quy định tại điểm c, điểm d khoản 1 Điều 23, điểm d khoản 1 Điều 25 Nghị định này được áp dụng kể từ ngày 01 tháng 01 năm 2031.
+7. Điều kiện về có chương trình bảo đảm chất lượng thực hiện dịch vụ, được quản lý phù hợp theo tiêu chuẩn quốc tế ISO 21000 quy định tại khoản 4 Điều 63 Nghị định này:
+a) Tổ chức được cấp giấy đăng ký hoạt động đào tạo an toàn bức xạ; đào tạo, bồi dưỡng chuyên môn, nghiệp vụ trước thời điểm Nghị định này có hiệu lực phải xây dựng và quản lý chất lượng theo tiêu chuẩn quốc tế ISO 21000 kể từ ngày 01 tháng 01 năm 2029;
+b) Tổ chức được cấp giấy đăng ký hoạt động đào tạo an toàn bức xạ; đào tạo, bồi dưỡng chuyên môn, nghiệp vụ sau thời điểm Nghị định này có hiệu lực phải xây dựng và quản lý chất lượng theo tiêu chuẩn quốc tế ISO 21000 trong thời hạn 03 năm kể từ thời điểm được cấp giấy đăng ký.
+CHUYỂN TIẾP: Điều 106. Điều khoản chuyển tiếp
+Quy định về một số trường hợp chuyển tiếp:
+1. Giấy phép tiến hành công việc bức xạ, Giấy đăng ký hoạt động dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử, Chứng chỉ nhân viên bức xạ, Chứng chỉ hành nghề dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử đã được cơ quan có thẩm quyền cấp trước ngày Nghị định này có hiệu lực thi hành được tiếp tục sử dụng đến hết thời hạn ghi trong giấy phép, giấy đăng ký, chứng chỉ, chứng chỉ hành nghề. Chứng chỉ nhân viên bức xạ hoặc chứng chỉ hành nghề dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử có hiệu lực đã được cơ quan có thẩm quyền cấp không quy định thời hạn trước ngày Nghị định này có hiệu lực thi hành thì có hiệu lực 05 năm kể từ ngày Nghị định này có hiệu lực.
+2. Trường hợp tổ chức, cá nhân đã nộp hồ sơ đề nghị cấp, sửa đổi, bổ sung, gia hạn Giấy phép tiến hành công việc bức xạ, Giấy đăng ký hoạt động dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử, Chứng chỉ hành nghề dịch vụ hỗ trợ ứng dụng năng lượng nguyên tử, Chứng chỉ nhân viên bức xạ mà đến ngày Nghị định này có hiệu lực thi hành chưa được cấp Giấy phép, Giấy đăng ký, Chứng chỉ thì hồ sơ tiếp tục được xử lý theo quy định của pháp luật về năng lượng nguyên tử trước ngày Nghị định này có hiệu lực thi hành.
+3. Các quy chuẩn kỹ thuật quốc gia về an toàn bức xạ, phân nhóm nguồn phóng xạ, miễn trừ khai báo, cấp giấy phép, quy chuẩn kỹ thuật quốc gia đối với máy gia tốc trong xạ trị và thiết bị X-quang trong y tế tiếp tục được áp dụng cho đến khi có văn bản thay thế.
+4. Trường hợp văn bản quy phạm pháp luật được dẫn chiếu tại Nghị định này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo văn bản mới.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1029,7 +1123,6 @@
           <t>2025-02-21 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -1050,9 +1143,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=60881</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1068,17 +1158,31 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 27/2018/TT-BTNMT Điều 17 (ranh giới khoanh đất "không được tổng hợp, không khái quát hóa", nhãn khoanh đất dạng cell hoặc text, đánh số zích zắc theo Phụ lục số 04); cùng Bộ TNMT, cùng thông tư bãi bỏ Điều 21 TT 02/2015. Bản đồ đổi tên thành "bản đồ kiểm kê đất đai": người audit xem lại yếu tố 4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>02/2015/TT-BTNMT · hiệu lực 2015-03-13 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 21. Sửa đổi, bổ sung quy định của Thông tư số 28/2014/TT-BTNMT
+1. Sửa đổi, bổ sung Điểm c Khoản 2 Điều 19 như sau:
+"c) Ranh giới các khoanh đất thể hiện trên bản đồ kết quả điều tra kiểm kê được phản ánh đúng theo trạng thái đã được xác định trong quá trình khoanh vẽ, không tổng hợp, không khái quát hóa, đảm bảo thể hiện vị trí, diện tích các khoanh đất với độ chính xác cao nhất theo kết quả điều tra thực địa.
+Khoanh đất trên bản đồ kết quả điều tra kiểm kê phải thể hiện nhãn khoanh đất gồm số thứ tự khoanh đất; diện tích khoanh đất; mã loại đất; mã loại đối tượng sử dụng đất hoặc đối tượng quản lý đất theo hình thức như sau:
+* Trường hợp khoanh đất có mục đích chính và mục đích phụ thì thể hiện mục đích chính trước và thể hiện mục đích phụ sau trong ngoặc đơn:
+* Trường hợp khoanh đất có nhiều mục đích sử dụng mà xác định được diện tích sử dụng riêng vào từng mục đích thì thể hiện:
+Nhãn khoanh đất được tạo dưới dạng cell. Mã ký hiệu loại đất, loại đối tượng sử dụng, đối tượng quản lý đất theo quy định tại Phụ lục số 04 ban hành kèm theo Thông tư này.
+Số thứ tự khoanh đất được thể hiện bằng số Ả Rập, từ 01 đến hết trong phạm vi toàn xã, thứ tự đánh số từ trên xuống dưới, từ trái sang phải, theo đường zích zắc (ziczac). Đối với các yếu tố chiếm đất không tạo thành thửa đất được khép vùng theo đường địa giới hành chính và được đánh số thứ tự như thửa đất;"</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 27/2018/TT-BTNMT · hiệu lực 2019-03-01
+3. Bãi bỏ Điều 21 của Thông tư số 02/2015/TT-BTNMT ngày 27 tháng 01 năm 2015 của Bộ Tài nguyên và Môi trường quy định chi tiết một số điều của Nghị định số 43/2014/NĐ-CP và Nghị định số 44/2014/NĐ-CP ngày 15 tháng 5 năm 2014 của Chính phủ.
+4. Trường hợp các văn bản quy phạm pháp luật được dẫn chiếu tại Thông tư này được sửa đổi, bổ sung thì thực hiện theo quy định tại văn bản sửa đổi, bổ sung.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1131,9 +1235,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13675</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1144,14 +1245,32 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>27/2007/QĐ-BYT · hiệu lực 2007-05-31 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Ban hành kèm theo Quyết định này lộ trình triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” và nguyên tắc “Thực hành tốt bảo quản thuốc”, như sau:
+1. Kế hoạch triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” (GMP).
+a) Khuyến khích các cơ sở triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” theo khuyến cáo của Tổ chức Y tế Thế giới (GMP-WHO).
+b) Các cơ sở sản xuất thuốc tân dược xây dựng mới phải đạt nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” của Hiệp hội các nước Đông Nam Á (GMP-ASEAN) hoặc “Thực hành tốt sản xuất thuốc” theo khuyến cáo của Tổ chức Y tế Thế giới (GMP-WHO).
+c) Các cơ sở sản xuất thuốc tiêm, thuốc tiêm truyền, thuốc có chứa kháng sinh nhóm beta-lactam phải đạt nguyên tắc, tiêu chuẩn GMP-ASEAN hoặc GMP-WHO mới được phép sản xuất.
+d) Các cơ sở sản xuất thuốc tân dược đã được phép sản xuất chưa đạt nguyên tắc, tiêu chuẩn GMP-ASEAN hoặc GMP-WHO nhưng đáp ứng qui định tại phụ lục 1 kèm theo Quyết định này được xem xét cho phép sản xuất đến hết ngày 30/6/2008.
+đ) Từ ngày 01/07/2008, các cơ sở sản xuất thuốc tân dược đã được phép sản xuất phải đạt nguyên tắc, tiêu chuẩn GMP-WHO.
+e) Các cơ sở đang triển khai áp dụng nguyên tắc, tiêu chuẩn GMP-ASEAN chỉ được cấp giấy chứng nhận có giá trị đến hết ngày 30/06/2008.
+g) Các cơ sở sản xuất thuốc dùng ngoài da quy định tại danh mục thuộc Phụ lục 1 của Quy chế đăng ký thuốc ban hành kèm theo Quyết định số 3121/2001/QĐ-BYT ngày 18/7/2001 của Bộ trưởng Bộ Y tế được sản xuất đến hết năm 2010. Từ ngày 01/01/2011, các cơ sở sản xuất những thuốc này phải đạt nguyên tắc, tiêu chuẩn GMP-WHO.
+h) Từ ngày 01/01/2011, tất cả các cơ sở sản xuất thuốc từ dược liệu phải đạt nguyên tắc, tiêu chuẩn GMP-WHO.</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 16/2011/TT-BYT · hiệu lực 2011-06-08
+1. Thông tư này có hiệu lực thi hành kể từ ngày 08 tháng 6 năm 2011. Bãi bỏ quy định tại điểm h khoản 1 Điều 1 Quyết định số 27/2007/QĐ-BYT ngày 19/4/2007 của Bộ trưởng Bộ Y tế ban hành lộ trình triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” và nguyên tắc “Thực hành tốt bảo quản thuốc”.
+2. Trong quá trình thực hiện, nếu có khó khăn, vướng mắc đề nghị các đơn vị báo cáo về Bộ Y tế (Cục Quản lý dược) để xem xét, hướng dẫn./.
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Các cơ sở sản xuất thuốc từ dược liệu đã được thẩm định điều kiện sản xuất thuốc theo Quyết định số 15/2008/QĐ-BYT ngày 21/4/2008 của Bộ Y tế và được cấp Giấy chứng nhận đủ điều kiện kinh doanh thuốc có hiệu lực sau ngày 31/12/2010 được phép tiếp tục kinh doanh thuốc đến hết hiệu lực của giấy chứng nhận đủ điều kiện kinh doanh thuốc nhưng không quá ngày 31/12/2013.
+2. Trước ngày 01/01/2014, các giấy chứng nhận đủ điều kiện kinh doanh thuốc cấp mới, bổ sung hoặc gia hạn cho các cơ sở sản xuất thuốc từ dược liệu chưa đáp ứng nguyên tắc, tiêu chuẩn Thực hành tốt sản xuất thuốc (GMP-WHO) chỉ có hiệu lực đến ngày 31/12/2013.
+3. Trong thời hạn kể từ ngày 01/01/2011 đến ngày Thông tư này có hiệu lực, các cơ sở sản xuất thuốc từ dược liệu được cấp Giấy chứng nhận đủ điều kiện kinh doanh thuốc có hiệu lực đến ngày 31/12/2010 được tiếp tục duy trì các hoạt động kinh doanh thuốc theo đúng điều kiện và phạm vi kinh doanh thuốc đã được cấp tại Giấy chứng nhận đủ điều kiện kinh doanh thuốc.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1204,9 +1323,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=13675</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1222,17 +1338,37 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 16/2011/TT-BYT khoản 4 Điều 15 "Kể từ ngày 01/01/2014, các cơ sở sản xuất thuốc từ dược liệu phải đáp ứng … GMP-WHO mới đủ điều kiện kinh doanh thuốc"; cùng Bộ Y tế, cùng thông tư bãi bỏ điểm h khoản 1 Điều 1 QĐ 27/2007; chỉ lùi thời hạn (yếu tố 4 cho phép đổi thời hạn)</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>27/2007/QĐ-BYT · hiệu lực 2007-05-31 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Ban hành kèm theo Quyết định này lộ trình triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” và nguyên tắc “Thực hành tốt bảo quản thuốc”, như sau:
+1. Kế hoạch triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” (GMP).
+a) Khuyến khích các cơ sở triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” theo khuyến cáo của Tổ chức Y tế Thế giới (GMP-WHO).
+b) Các cơ sở sản xuất thuốc tân dược xây dựng mới phải đạt nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” của Hiệp hội các nước Đông Nam Á (GMP-ASEAN) hoặc “Thực hành tốt sản xuất thuốc” theo khuyến cáo của Tổ chức Y tế Thế giới (GMP-WHO).
+c) Các cơ sở sản xuất thuốc tiêm, thuốc tiêm truyền, thuốc có chứa kháng sinh nhóm beta-lactam phải đạt nguyên tắc, tiêu chuẩn GMP-ASEAN hoặc GMP-WHO mới được phép sản xuất.
+d) Các cơ sở sản xuất thuốc tân dược đã được phép sản xuất chưa đạt nguyên tắc, tiêu chuẩn GMP-ASEAN hoặc GMP-WHO nhưng đáp ứng qui định tại phụ lục 1 kèm theo Quyết định này được xem xét cho phép sản xuất đến hết ngày 30/6/2008.
+đ) Từ ngày 01/07/2008, các cơ sở sản xuất thuốc tân dược đã được phép sản xuất phải đạt nguyên tắc, tiêu chuẩn GMP-WHO.
+e) Các cơ sở đang triển khai áp dụng nguyên tắc, tiêu chuẩn GMP-ASEAN chỉ được cấp giấy chứng nhận có giá trị đến hết ngày 30/06/2008.
+g) Các cơ sở sản xuất thuốc dùng ngoài da quy định tại danh mục thuộc Phụ lục 1 của Quy chế đăng ký thuốc ban hành kèm theo Quyết định số 3121/2001/QĐ-BYT ngày 18/7/2001 của Bộ trưởng Bộ Y tế được sản xuất đến hết năm 2010. Từ ngày 01/01/2011, các cơ sở sản xuất những thuốc này phải đạt nguyên tắc, tiêu chuẩn GMP-WHO.
+h) Từ ngày 01/01/2011, tất cả các cơ sở sản xuất thuốc từ dược liệu phải đạt nguyên tắc, tiêu chuẩn GMP-WHO.</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 16/2011/TT-BYT · hiệu lực 2011-06-08
+1. Thông tư này có hiệu lực thi hành kể từ ngày 08 tháng 6 năm 2011. Bãi bỏ quy định tại điểm h khoản 1 Điều 1 Quyết định số 27/2007/QĐ-BYT ngày 19/4/2007 của Bộ trưởng Bộ Y tế ban hành lộ trình triển khai áp dụng nguyên tắc, tiêu chuẩn “Thực hành tốt sản xuất thuốc” và nguyên tắc “Thực hành tốt bảo quản thuốc”.
+2. Trong quá trình thực hiện, nếu có khó khăn, vướng mắc đề nghị các đơn vị báo cáo về Bộ Y tế (Cục Quản lý dược) để xem xét, hướng dẫn./.
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Các cơ sở sản xuất thuốc từ dược liệu đã được thẩm định điều kiện sản xuất thuốc theo Quyết định số 15/2008/QĐ-BYT ngày 21/4/2008 của Bộ Y tế và được cấp Giấy chứng nhận đủ điều kiện kinh doanh thuốc có hiệu lực sau ngày 31/12/2010 được phép tiếp tục kinh doanh thuốc đến hết hiệu lực của giấy chứng nhận đủ điều kiện kinh doanh thuốc nhưng không quá ngày 31/12/2013.
+2. Trước ngày 01/01/2014, các giấy chứng nhận đủ điều kiện kinh doanh thuốc cấp mới, bổ sung hoặc gia hạn cho các cơ sở sản xuất thuốc từ dược liệu chưa đáp ứng nguyên tắc, tiêu chuẩn Thực hành tốt sản xuất thuốc (GMP-WHO) chỉ có hiệu lực đến ngày 31/12/2013.
+3. Trong thời hạn kể từ ngày 01/01/2011 đến ngày Thông tư này có hiệu lực, các cơ sở sản xuất thuốc từ dược liệu được cấp Giấy chứng nhận đủ điều kiện kinh doanh thuốc có hiệu lực đến ngày 31/12/2010 được tiếp tục duy trì các hoạt động kinh doanh thuốc theo đúng điều kiện và phạm vi kinh doanh thuốc đã được cấp tại Giấy chứng nhận đủ điều kiện kinh doanh thuốc.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1285,9 +1421,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=15528</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1303,17 +1436,28 @@
           <t>question_ambiguous</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Khoản 3 Điều 20 NĐ 84/2006 có ba mức (a khiển trách, b cảnh cáo, c hạ bậc lương) theo hình thức kỷ luật của cá nhân (khoản 3, 4, 5 Điều 19); câu hỏi không nêu hình thức nên khớp cả ba điểm</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>84/2006/NĐ-CP · hiệu lực 2006-09-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 20. Xử lý kỷ luật đối với người đứng đầu đơn vị trực thuộc cơ quan, tổ chức được giao quản lý vốn, tài sản
+3. Áp dụng hình thức kỷ luật:
+a) Áp dụng hình thức khiển trách đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 3 Điều 19 Nghị định này;
+b) Áp dụng hình thức cảnh cáo đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 4 Điều 19 Nghị định này;
+c) Áp dụng hình thức hạ bậc lương đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 5 Điều 19 Nghị định này;
+d) Áp dụng hình thức cách chức đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 6 Điều 19 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 103/2007/NĐ-CP · hiệu lực 2007-07-23
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1341,7 +1485,6 @@
           <t>2009-06-09 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -1362,9 +1505,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=15528</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1380,17 +1520,28 @@
           <t>question_ambiguous</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Như dòng trước. unclear: 103/2007/NĐ-CP Điều 22 khoản 1 (khiển trách người đứng đầu khi có người bị kỷ luật theo khoản 2, 3, 4 Điều 21) có thể là quy định kế thừa; cùng nghị định bãi bỏ Mục 2 Chương II NĐ 84/2006, chưa đối chiếu bảy yếu tố</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>84/2006/NĐ-CP · hiệu lực 2006-09-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 20. Xử lý kỷ luật đối với người đứng đầu đơn vị trực thuộc cơ quan, tổ chức được giao quản lý vốn, tài sản
+3. Áp dụng hình thức kỷ luật:
+a) Áp dụng hình thức khiển trách đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 3 Điều 19 Nghị định này;
+b) Áp dụng hình thức cảnh cáo đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 4 Điều 19 Nghị định này;
+c) Áp dụng hình thức hạ bậc lương đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 5 Điều 19 Nghị định này;
+d) Áp dụng hình thức cách chức đối với người đứng đầu nếu trong đơn vị có cá nhân vi phạm quy định về thực hành tiết kiệm, chống lãng phí bị áp dụng hình thức kỷ luật quy định tại khoản 6 Điều 19 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 103/2007/NĐ-CP · hiệu lực 2007-07-23
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1443,9 +1594,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=129423</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1456,14 +1604,42 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>12/2018/TT-BCT · hiệu lực 2018-06-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 9. Giấy phép sản xuất, gia công xuất khẩu quân phục và Giấy phép nhập khẩu mẫu quân phục
+3. Cơ quan cấp giấy phép: Bộ Công Thương, địa chỉ: 54 Hai Bà Trưng, quận Hoàn Kiếm, thành phố Hà Nội.</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 26/2026/TT-BCT · hiệu lực 2026-05-29
+1. Bãi bỏ khoản 3 Điều 9.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1491,7 +1667,6 @@
           <t>2026-01-26 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -1512,9 +1687,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127134</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1530,17 +1702,29 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 02/2025/TT-BCT điểm c khoản 2 Điều 15 "Trường hợp thiết bị, dụng cụ điện ở vị trí không thể thực hiện việc dán tem … thì khi kết thúc kiểm định được cấp Giấy chứng nhận kiểm định"; cùng Bộ Công Thương, cùng thông tư bãi bỏ Điều 3 TT 28/2017</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>28/2017/TT-BCT · hiệu lực 2018-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Sửa đổi, bổ sung, bãi bỏ một số điều của Thông tư số 33/2015/TT-BCT ngày 27 tháng 10 năm 2015 của Bộ trưởng Bộ Công Thương quy định về kiểm định an toàn kỹ thuật các thiết bị, dụng cụ điện
+2. Sửa đổi Điều 7 như sau:
+"1. Việc kiểm định các thiết bị, dụng cụ điện được thực hiện bởi tổ chức kiểm định đáp ứng yêu cầu tại Điều 9 Nghị định số 107/2016/NĐ-CP ngày 01 tháng 7 năm 2016 của Chính phủ quy định về điều kiện kinh doanh dịch vụ đánh giá sự phù hợp và được Bộ Công Thương cấp Giấy chứng nhận đăng ký hoạt động kiểm định theo quy định.
+Hồ sơ, trình tự, thủ tục cấp Giấy chứng nhận đăng ký hoạt động kiểm định thực hiện theo quy định tại Điều 10, Điều 11 và Điều 12 Nghị định số 107/2016/NĐ-CP .</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 02/2025/TT-BCT · hiệu lực 2025-02-01
+3. Bãi bỏ Điều 3 Thông tư số 28/2017/TT-BCT ngày 08 tháng 12 năm 2017 của Bộ Công Thương sửa đổi, bổ sung, bãi bỏ một số Thông tư trong lĩnh vực kinh doanh xăng dầu, kinh doanh dịch vụ đánh giá sự phù hợp và xuất nhập khẩu thuộc phạm vi quản lý nhà nước của Bộ Công Thương, kể từ ngày Thông tư này có hiệu lực thi hành.
+CHUYỂN TIẾP: Điều 21. Quy định chuyển tiếp
+1. Giấy chứng nhận đăng ký hoạt động kiểm định được Bộ Công Thương cấp trước ngày Thông tư này có hiệu lực thi hành thì tiếp tục được thực hiện cho đến khi cấp mới, cấp bổ sung, sửa đổi, cấp lại.
+2. Tổ chức nộp hồ sơ đăng ký hoạt động kiểm định an toàn kỹ thuật thiết bị, dụng cụ điện và đang được Bộ Công Thương (thông qua Cục Kỹ thuật an toàn và Môi trường công nghiệp) tiếp nhận, thẩm định trước ngày Thông tư này có hiệu lực thì được tiếp tục thực hiện theo quy định của pháp luật tại thời điểm nộp hồ sơ đăng ký. Trường hợp cơ quan nhà nước có thẩm quyền yêu cầu chỉnh sửa hoàn thiện, bổ sung hồ sơ đăng ký sau ngày hiệu lực của Thông tư này thì thực hiện theo quy định tại Thông tư này.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1593,9 +1777,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117757</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1606,14 +1787,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>33/2016/TT-BCT · hiệu lực 2017-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Sửa đổi, bổ sung một số Điều của Thông tư số 36/2015/TT-BCT ngày 28 tháng 10 năm 2015 ban hành Quy chuẩn kỹ thuật quốc gia đối với sản phẩm khăn giấy và giấy vệ sinh
+6. Sửa đổi, bổ sung mục 4.4 của QCVN 09:2015/BCT như sau:
+“4.4. Các tổ chức đánh giá sự phù hợp cho sản phẩm khăn giấy, giấy vệ sinh và giấy tissue sau khi được Bộ Công Thương chỉ định chịu trách nhiệm:
+- Lập danh sách các lô hàng đã tiến hành đánh giá và báo cáo Bộ Công Thương vào tuần cuối cùng của hàng quý;
+- Thực hiện đánh giá sự phù hợp theo quy định của Quy chuẩn kỹ thuật này.”</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 42/2019/TT-BCT · hiệu lực 2020-02-05
+a) Khoản 6 Điều 1 Thông tư số 33/2016/TT-BCT ngày 23 tháng 12 năm 2016 của Bộ trưởng Bộ Công Thương sửa đổi, bổ sung một số điều của Thông tư số 36/2015/TT-BCT ngày 28 tháng 10 năm 2015 ban hành Quy chuẩn kỹ thuật quốc gia đối với sản phẩm khăn giấy và giấy vệ sinh.
+b) Điều 4 Thông tư số 51/2018/TT-BCT ngày 19 tháng 12 năm 2018 của Bộ trưởng Bộ Công Thương sửa đổi, bổ sung một số điều của Thông tư liên tịch số 47/2011/TTLT-BCT-BTNMT ngày 30 tháng 12 năm 2011 của Bộ trưởng Bộ Công Thương và Bộ trưởng Bộ Tài nguyên và Môi trường quy định việc quản lý nhập khẩu, xuất khẩu và tạm nhập - tái xuất các chất làm suy giảm tầng ô-dôn theo quy định của Nghị định thư Montreal về các chất làm suy giảm tầng ô-dôn.
+c) Khoản 20 Điều 1 Thông tư số 31/2018/TT-BCT ngày 05 tháng 10 năm 2018 của Bộ trưởng Công Thương sửa đổi, bổ sung một số điều của Thông tư số 27/2013/TT-BCT ngày 31 tháng 10 năm 2013 quy định về kiểm tra hoạt động điện lực và sử dụng điện, giải quyết tranh chấp hợp đồng mua bán điện.
+d) Điều 29 Thông tư số 43/2013/TT-BCT ngày 31 tháng 12 năm 2013 của Bộ trưởng Bộ Công Thương quy định nội dung, trình tự, thủ tục lập, thẩm định, phê duyệt và điều chỉnh Quy hoạch phát triển điện lực
+3. Các chế độ báo cáo định kỳ trong lĩnh vực Công Thương hiện hành phải đảm bảo thời gian chốt số liệu báo cáo theo quy định tại Điều 12 của Nghị định số 09/2019/NĐ-CP .
+4. Trong quá trình thực hiện nếu có vướng mắc, các tổ chức, cá nhân phản ánh về Bộ Công Thương để được hướng dẫn, giải quyết./.
+BỘ TRƯỞNG
+(Đã ký)
+Trần Tuấn Anh</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1666,9 +1863,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117757</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1684,17 +1878,35 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 42/2019/TT-BCT khoản 1 Điều 10 sửa lại mục 4.4 QCVN 09:2015/BCT, giữ hai trách nhiệm (lập danh sách lô hàng, báo cáo Bộ Công Thương vào tuần cuối của tháng cuối mỗi quý; đánh giá sự phù hợp theo Quy chuẩn), thêm phương thức gửi và mẫu Phụ lục B; cùng Bộ, cùng thông tư bãi bỏ khoản 6 Điều 1 TT 33/2016</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>33/2016/TT-BCT · hiệu lực 2017-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Sửa đổi, bổ sung một số Điều của Thông tư số 36/2015/TT-BCT ngày 28 tháng 10 năm 2015 ban hành Quy chuẩn kỹ thuật quốc gia đối với sản phẩm khăn giấy và giấy vệ sinh
+6. Sửa đổi, bổ sung mục 4.4 của QCVN 09:2015/BCT như sau:
+“4.4. Các tổ chức đánh giá sự phù hợp cho sản phẩm khăn giấy, giấy vệ sinh và giấy tissue sau khi được Bộ Công Thương chỉ định chịu trách nhiệm:
+- Lập danh sách các lô hàng đã tiến hành đánh giá và báo cáo Bộ Công Thương vào tuần cuối cùng của hàng quý;
+- Thực hiện đánh giá sự phù hợp theo quy định của Quy chuẩn kỹ thuật này.”</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 42/2019/TT-BCT · hiệu lực 2020-02-05
+a) Khoản 6 Điều 1 Thông tư số 33/2016/TT-BCT ngày 23 tháng 12 năm 2016 của Bộ trưởng Bộ Công Thương sửa đổi, bổ sung một số điều của Thông tư số 36/2015/TT-BCT ngày 28 tháng 10 năm 2015 ban hành Quy chuẩn kỹ thuật quốc gia đối với sản phẩm khăn giấy và giấy vệ sinh.
+b) Điều 4 Thông tư số 51/2018/TT-BCT ngày 19 tháng 12 năm 2018 của Bộ trưởng Bộ Công Thương sửa đổi, bổ sung một số điều của Thông tư liên tịch số 47/2011/TTLT-BCT-BTNMT ngày 30 tháng 12 năm 2011 của Bộ trưởng Bộ Công Thương và Bộ trưởng Bộ Tài nguyên và Môi trường quy định việc quản lý nhập khẩu, xuất khẩu và tạm nhập - tái xuất các chất làm suy giảm tầng ô-dôn theo quy định của Nghị định thư Montreal về các chất làm suy giảm tầng ô-dôn.
+c) Khoản 20 Điều 1 Thông tư số 31/2018/TT-BCT ngày 05 tháng 10 năm 2018 của Bộ trưởng Công Thương sửa đổi, bổ sung một số điều của Thông tư số 27/2013/TT-BCT ngày 31 tháng 10 năm 2013 quy định về kiểm tra hoạt động điện lực và sử dụng điện, giải quyết tranh chấp hợp đồng mua bán điện.
+d) Điều 29 Thông tư số 43/2013/TT-BCT ngày 31 tháng 12 năm 2013 của Bộ trưởng Bộ Công Thương quy định nội dung, trình tự, thủ tục lập, thẩm định, phê duyệt và điều chỉnh Quy hoạch phát triển điện lực
+3. Các chế độ báo cáo định kỳ trong lĩnh vực Công Thương hiện hành phải đảm bảo thời gian chốt số liệu báo cáo theo quy định tại Điều 12 của Nghị định số 09/2019/NĐ-CP .
+4. Trong quá trình thực hiện nếu có vướng mắc, các tổ chức, cá nhân phản ánh về Bộ Công Thương để được hướng dẫn, giải quyết./.
+BỘ TRƯỞNG
+(Đã ký)
+Trần Tuấn Anh</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1747,9 +1959,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=4ca06a80-8c80-11f1-941a-e377a12e0bfa</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1760,14 +1969,41 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>136/2024/QH15 · hiệu lực 2025-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 7. Cơ cấu tổ chức, chế độ làm việc, nhiệm vụ, quyền hạn của Ủy ban nhân dân quận
+3. Ủy ban nhân dân quận có nhiệm vụ, quyền hạn sau đây:
+a) Thực hiện nhiệm vụ, quyền hạn của đơn vị dự toán ngân sách trực thuộc Ủy ban nhân dân Thành phố theo quy định của Luật Ngân sách nhà nước;
+b) Đề xuất chủ trương đầu tư chương trình, dự án đầu tư công sử dụng vốn ngân sách nhà nước với Ủy ban nhân dân Thành phố; tham gia ý kiến về chủ trương đầu tư dự án thuộc thẩm quyền quyết định của cơ quan, cá nhân có thẩm quyền mà Luật Đầu tư công quy định phải có sự tham gia ý kiến của Hội đồng nhân dân cấp huyện; tổ chức thực hiện chương trình, dự án đầu tư công và các quy hoạch trên địa bàn quận theo phân cấp quản lý;
+c) Quy định tổ chức bộ máy và nhiệm vụ, quyền hạn cụ thể của cơ quan chuyên môn thuộc Ủy ban nhân dân quận phù hợp với tình hình thực tiễn của công tác quản lý nhà nước tại đô thị trên địa bàn Thành phố;
+d) Chịu trách nhiệm về hiệu lực, hiệu quả hoạt động của hệ thống hành chính nhà nước từ quận đến cơ sở, bảo đảm tính thống nhất, thông suốt của nền hành chính; thực hiện cải cách hành chính và cải cách công vụ, công chức trong hệ thống hành chính nhà nước ở địa phương;
+đ) Đề xuất, phối hợp với cơ quan có thẩm quyền thực hiện nhiệm vụ về quốc phòng, an ninh, biện pháp bảo đảm trật tự, an toàn xã hội, đấu tranh phòng, chống tội phạm và các hành vi vi phạm pháp luật khác trên địa bàn theo phân cấp quản lý;
+e) Thực hiện nhiệm vụ về tổ chức và bảo đảm việc thi hành Hiến pháp, pháp luật, xây dựng chính quyền và địa giới hành chính, giáo dục, đào tạo, khoa học, công nghệ, văn hóa, thông tin, thể dục, thể thao, y tế, lao động, chính sách xã hội, chính sách dân tộc, chính sách tôn giáo, hành chính tư pháp, bổ trợ tư pháp, các biện pháp bảo vệ môi trường, phòng, chống cháy, nổ, phòng, chống thiên tai, dịch bệnh, quản lý dân cư và các nhiệm vụ, quyền hạn khác theo quy định của pháp luật trên địa bàn;
+g) Quản lý và tổ chức sử dụng công sở, tài sản, phương tiện làm việc và ngân sách nhà nước được giao theo quy định của pháp luật;
+h) Tổ chức việc thanh tra, kiểm tra, giải quyết khiếu nại, tố cáo, xử lý vi phạm pháp luật, tiếp công dân theo quy định của pháp luật;
+i) Thực hiện nhiệm vụ, quyền hạn do cơ quan nhà nước cấp trên phân cấp, ủy quyền;
+k) Phân cấp, ủy quyền cho Ủy ban nhân dân phường; ủy quyền cho cơ quan chuyên môn, cơ quan hành chính khác, đơn vị sự nghiệp công lập thuộc Ủy ban nhân dân quận thực hiện các nhiệm vụ, quyền hạn của Ủy ban nhân dân quận theo quy định của pháp luật;
+l) Ban hành văn bản quy phạm pháp luật để quy định những vấn đề được luật, nghị quyết của Quốc hội giao và thực hiện phân cấp theo quy định tại điểm k khoản này. Đình chỉ việc thi hành, bãi bỏ một phần hoặc toàn bộ văn bản trái pháp luật của cơ quan chuyên môn thuộc Ủy ban nhân dân quận và văn bản trái pháp luật của Ủy ban nhân dân phường;
+m) Quyết định đối với nhiệm vụ mà theo quy định của pháp luật phải trình Hội đồng nhân dân quận thông qua trước khi quyết định; trình Ủy ban nhân dân Thành phố quyết định đối với nhiệm vụ thuộc thẩm quyền của Hội đồng nhân dân quận quyết định theo quy định của pháp luật;
+n) Thực hiện nhiệm vụ, quyền hạn khác theo quy định của pháp luật mà không trái với quy định của Nghị quyết này.</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 72/2025/QH15 · hiệu lực 2025-06-16
+c) Bãi bỏ Điều 7 và Điều 8 của Nghị quyết số 136/2024/QH15 ngày 26 tháng 6 năm 2024 của Quốc hội về tổ chức chính quyền đô thị và thí điểm một số cơ chế, chính sách đặc thù phát triển thành phố Đà Nẵng;
+CHUYỂN TIẾP: Điều 54. Quy định chuyển tiếp
+1. Chậm nhất là ngày 01 tháng 3 năm 2027, các văn bản quy phạm pháp luật có nội dung quy định về tổ chức, nhiệm vụ, quyền hạn và quy định khác có liên quan của chính quyền địa phương các cấp phải được sửa đổi, bổ sung để bảo đảm phù hợp với tổ chức đơn vị hành chính, các nguyên tắc và các nhiệm vụ, quyền hạn của chính quyền địa phương các cấp quy định tại Luật này.
+Kể từ ngày Luật này có hiệu lực thi hành, để kịp thời thực hiện tổ chức chính quyền địa phương cấp tỉnh, cấp xã theo quy định tại Luật này và đẩy mạnh phân quyền, phân cấp cho chính quyền địa phương trong một số lĩnh vực ưu tiên, cấp bách, giao Chính phủ ban hành văn bản quy phạm pháp luật thuộc thẩm quyền phân định lại nhiệm vụ, quyền hạn của chính quyền địa phương và điều chỉnh các quy định khác có liên quan đến việc thực hiện nhiệm vụ, quyền hạn của chính quyền địa phương để thống nhất áp dụng trong thời gian chưa sửa đổi, bổ sung các luật, pháp lệnh, nghị quyết của Quốc hội, Ủy ban Thường vụ Quốc hội và định kỳ báo cáo Ủy ban Thường vụ Quốc hội; trường hợp liên quan đến luật, nghị quyết của Quốc hội thì báo cáo Quốc hội tại kỳ họp gần nhất.
+2. Trong thời gian cơ quan có thẩm quyền chưa ban hành văn bản quy phạm pháp luật để điều chỉnh nhiệm vụ, quyền hạn của chính quyền địa phương theo quy định tại khoản 1 Điều này thì các quy định của pháp luật hiện hành liên quan đến trách nhiệm trong thực hiện nhiệm vụ, quyền hạn của chính quyền địa phương được tiếp tục thực hiện cho đến khi cơ quan có thẩm quyền ban hành văn bản quy phạm pháp luật sửa đổi, bổ sung hoặc thay thế.
+3. Kể từ ngày 01 tháng 7 năm 2025, Ủy ban nhân dân cấp tỉnh kế thừa các thỏa thuận quốc tế do Ủy ban nhân dân cấp huyện ký kết trước ngày 01 tháng 7 năm 2025; chịu trách nhiệm thực hiện việc điều chỉnh, cập nhật tên gọi mới của đơn vị hành chính trong các thỏa thuận quốc tế do Ủy ban nhân dân cấp huyện ký kết trước ngày 01 tháng 7 năm 2025.
+4. Khi chính quyền địa phương cấp huyện kết thúc hoạt động theo quy định tại khoản 3 Điều 51 của Luật này thì Thường trực Hội đồng nhân dân cấp tỉnh có trách nhiệm xác định các đại biểu Hội đồng nhân dân cấp huyện nhiệm kỳ 2021 - 2026 được bầu hoặc đang thực hiện nhiệm vụ đại biểu ở phần địa giới hành chính thuộc đơn vị hành chính cấp xã hình thành sau sắp xếp hoặc được cơ quan có thẩm quyền điều động, bố trí công tác tại các cơ quan, tổ chức, đơn vị ở đơn vị hành chính cấp xã đó để làm đại biểu của Hội đồng nhân dân nhiệm kỳ 2021 - 2026 của đơn vị hành chính cấp xã tương ứng, trừ trường hợp quy định tại khoản 5 Điều này.
+5. Đại biểu Hội đồng nhân dân cấp huyện, cấp xã ở các đơn vị hành chính thực hiện sắp xếp để hình thành đặc khu thuộc trường hợp quy định tại khoản 1 Điều 28 của Luật này kết thúc hoạt động kể từ ngày 01 tháng 7 năm 2025.
+6. Kể từ ngày Luật này có hiệu lực thi hành, số lượng Phó Chủ tịch Hội đồng nhân dân, Phó Chủ tịch Ủy ban nhân dân, cấp phó của người đứng đầu các cơ quan, đơn vị trực thuộc Hội đồng nhân dân, Ủy ban nhân dân tại các đơn vị hành chính cấp tỉnh hình thành sau sắp xếp có thể nhiều hơn số lượng so với quy định. Chậm nhất là 05 năm kể từ ngày Luật này có hiệu lực thi hành, số lượng và việc bố trí lãnh đạo, quản lý ở đơn vị hành chính sau sắp xếp được thực hiện theo quy định.
+7. Chậm nhất là ngày 30 tháng 6 năm 2025, Thường trực Hội đồng nhân dân, các cơ quan thuộc Hội đồng nhân dân, Ủy ban nhân dân, Chủ tịch Ủy ban nhân dân, các cơ quan chuyên môn thuộc Ủy ban nhân dân cấp huyện phải hoàn thành việc bàn giao công việc, hồ sơ, tài liệu, tài chính, ngân sách, trụ sở, tài sản, cơ sở vật chất khác có liên quan cho các cơ quan, tổ chức, đơn vị có thẩm quyền bảo đảm hoạt động bình thường, liên tục, thông suốt của các cơ quan, không để gián đoạn công việc, không để chồng chéo, trùng lặp hoặc bỏ sót nhiệm vụ, lĩnh vực, địa bàn, không làm ảnh hưởng đến nhiệm vụ phát triển kinh tế - xã hội, hoạt động bình thường của xã hội, người dân, doanh nghiệp, bảo đảm quốc phòng, an ninh, trật tự, an toàn xã hội trên địa bàn [...cắt bớt]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1820,9 +2056,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150226</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1833,14 +2066,94 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>58/2015/TT-BTNMT · hiệu lực 2016-01-23 → nay · lúc thu thập: Còn hiệu lực
+Điều 18. Đối với phần mềm ứng dụng tài nguyên và môi trường
+3. Chi tiết các bước kiểm tra, nghiệm thu phần mềm ứng dụng tài nguyên và môi trường
+a) Lập kế hoạch kiểm tra, nghiệm thu
+Thực hiện tương tự bước “Lập kế hoạch kiểm tra, nghiệm thu” tại Điểm a, Khoản 3, Điều 17 của Thông tư này.
+Trường hợp trong dự án có cả hai hạng mục xây dựng cơ sở dữ liệu tài nguyên và môi trường và xây dựng phần mềm ứng dụng hỗ trợ việc quản lý, khai thác cơ sở dữ liệu trên thì bước này chỉ được thực hiện một lần cho cả hai hạng mục.
+b) Tiếp nhận hồ sơ, sản phẩm
+Thực hiện tương tự bước “Tiếp nhận hồ sơ, sản phẩm” tại Điểm b, Khoản 3, Điều 17 của Thông tư này.
+Trường hợp trong dự án có cả hai hạng mục xây dựng cơ sở dữ liệu tài nguyên và môi trường và xây dựng phần mềm ứng dụng hỗ trợ việc quản lý, khai thác cơ sở dữ liệu trên thì bước này chỉ được thực hiện một lần cho cả hai hạng mục.
+c) Kiểm tra rà soát, phân tích phục vụ xây dựng cơ sở dữ liệu
+c.1. Yêu cầu: Đảm bảo các sản phẩm bước “Thu thập yêu cầu phần mềm và phân tích dữ liệu” đạt yêu cầu chất lượng theo thiết kế kỹ thuật của dự án đã được phê duyệt.
+c.2. Các bước thực hiện
+Kiểm tra các nội dung, sản phẩm của bước “Thu thập yêu cầu phần mềm và phân tích nội dung thông tin dữ liệu” tại Điểm 2.1, Khoản 2, Chương II, Phần II Thông tư số 26/2014/TT-BTNMT bao gồm:
+- Kiểm tra về thu thập yêu cầu phần mềm:
++ Kiểm tra các yêu cầu chức năng;
++ Kiểm tra các yêu cầu phi chức năng;
++ Kiểm tra tính phù hợp giữa các yêu cầu phi chức năng với yêu cầu chức năng;
++ Kiểm tra các tác nhân phần mềm;
++ Kiểm tra các trường hợp sử dụng;
++ Kiểm tra danh mục trường hợp sử dụng;
++ Kiểm tra phương pháp quy đổi trường hợp sử dụng.
+- Kiểm tra sản phẩm phân tích nội dung thông tin dữ liệu:
+Thực hiện tương tự bước “Kiểm tra rà soát, phân tích phục vụ xây dựng cơ sở dữ liệu” tại Điểm c, Khoản 3, Điều 17 của Thông tư này.
+Trường hợp trong dự án có cả hai hạng mục xây dựng cơ sở dữ liệu tài nguyên và môi trường và xây dựng phần mềm ứng dụng hỗ trợ việc quản lý, khai thác cơ sở dữ liệu trên thì bước này chỉ được thực hiện một lần cho cả hai hạng mục.
+c.3. Kết quả
+- Phiếu ý kiến kiểm tra báo cáo thu thập yêu cầu phần mềm theo Mẫu 2.05 - Phụ lục 2.
+- Phiếu ý kiến kiểm tra kết quả rà soát, phân tích thông tin dữ liệu theo Mẫu 2.02 - Phụ lục 2 (nếu có).
+d) Kiểm tra mô hình hóa chi tiết nghiệp vụ
+d.1. Yêu cầu: Đảm bảo các sản phẩm của bước mô hình hóa chi tiết nghiệp vụ đạt yêu cầu chất lượng theo Thiết kế kỹ thuật và Báo cáo xác định yêu cầu phần mềm (nếu có).
+d.2. Các bước thực hiện:
+Kiểm tra các nội dung, sản phẩm của bước “Mô hình hóa chi tiết nghiệp vụ” tại Điểm 2.2, Khoản 2, Chương II, Phần II Thông tư số 26/2014/TT-BTNMT bao gồm:
+- Kiểm tra tài liệu mô hình hóa chi tiết quy trình nghiệp vụ:
++ Danh mục và mô tả các quy trình nghiệp vụ;
++ Chi tiết mô hình nghiệp vụ.
+- Kiểm tra tài liệu mô tả biểu đồ trường hợp sử dụng nghiệp vụ:
++ Danh mục các tác nhân hệ thống;
++ Danh mục các trường hợp sử dụng nghiệp vụ và thông tin mô tả;
++ Biểu đồ trường hợp sử dụng nghiệp vụ;
++ Chi tiết các trường hợp sử dụng nghiệp vụ.
+d.3. Kết quả:
+- Phiếu ý kiến kiểm tra mô hình hóa chi tiết nghiệp vụ theo Mẫu 2.06 - Phụ lục 2.
+đ) Kiểm tra thiết kế chi tiết phần mềm
+đ.1. Yêu cầu: Đảm bảo các sản phẩm thiết kế phần mềm theo đúng mục tiêu và yêu cầu về kỹ thuật đã phê duyệt.
+đ.2. Các bước thực hiện:
+Kiểm tra các nội dung, sản phẩm của bước “Thiết kế” tại Điểm 2.3, Khoản 2, Chương II, Phần II Thông tư số 26/2014/TT-BTNMT bao gồm:
+- Kiểm tra thuyết minh kiến trúc phần mềm:
++ Kiến trúc phần mềm (so với kiến trúc tổng thể của hệ thống đã được phê duyệt);
++ Kiến trúc ứng dụng (mô hình phân lớp của phần mềm; chức năng của mỗi lớp và phương thức làm việc/trao đổi dữ liệu giữa các lớp);
++ Kiến trúc dữ liệu;
++ Kiến trúc cơ sở hạ tầng công nghệ thông tin (yêu cầu phần hạ tầng kỹ thuật, an ninh, an toàn để sử dụng vận hành phần mềm).
+- Kiểm tra thuyết minh biểu đồ trường hợp sử dụng;
++ Số lượng tác nhân trong tài liệu (số lượng tác nhân so với thiết kế kỹ thuật và so với các tài liệu của bước trước);
++ Kiểm đếm số lượng, kiểm tra thông tin các use-case trong tài liệu so với thiết kế kỹ thuật;
++ Xem xét biểu đồ use-case theo chuẩn thiết kế ngôn ngữ mô hình hóa thống nhất (UML).
+- Kiểm tra thuyết minh biểu đồ hoạt động và tuần tự:
++ Số lượng Use case;
++ Biểu đồ hoạt động;
++ Biểu đồ tuần tự.
+- Kiểm tra thuyết minh biểu đồ lớp:
++ Biểu đồ lớp theo chuẩn thiết kế UML;
++ Chi tiết các lớp (trùng lặp class; thuộc tính và phương thức của class).
+- Kiểm tra thiết kế mô hình dữ liệu: Thực hiện tương tự bước “Kiểm tra thiết kế mô hình dữ liệu” thuộc bước “Kiểm tra thiết kế mô hình cơ sở dữ liệu” tại Điểm d, Khoản 3, Điều 17 của Thông tư này. Trường hợp trong dự án có cả hai hạng mục xây dựng cơ sở dữ liệu tài nguyên và môi trường và xây dựng phần mềm ứng dụng hỗ trợ việc quản lý, khai thác cơ sở dữ liệu trên thì bước này chỉ được thực hiện một lần cho cả hai hạng mục.
+- Thiết kế giao diện của phần mềm:
++ Giao diện phù hợp với chức năng và nghiệp vụ thực hiện;
++ Tính đầy đủ, trình bày hợp lý của các thành phần của giao diện...
+đ.3. Kết quả
+Phiếu ý kiến kiểm tra thuyết minh thiết kế phần mềm theo Mẫu 2.07 - Phụ lục 2.
+e) Kiểm tra mã nguồn phần mềm
+e.1. Yêu cầu: Đảm bảo mã nguồn được xây dựng theo đúng thiết kế và theo đúng các quy chuẩn, tiêu chuẩn công nghệ lập trình được phê duyệt của dự án.
+e.2. Các bước thực hiện:
+Kiểm tra các nội dung, sản phẩm của bước “Lập trình” tại Điểm 2.4, Khoản 2. Chương II, Phần II Thông tư số 26/2014/TT-BTNMT bao gồm:
+- Kiểm tra mã nguồn:
++ Sử dụng công nghệ phát triển (.Net, Java …) theo phê duyệt;
++ Lập trình theo đúng kiến trúc phần mềm đã phê duyệt;
++ Trình bày mã nguồn đúng quy tắc lập trình quy định theo tiêu chuẩn, quy chuẩn kỹ thuật và phương án kỹ thuật được phê duyệt;
++ Số lượng lớp (class) trong lập trình hướng đối tượng (căn cứ tài liệu thiết kế).
+- Kiểm tra chi tiết các lớp (lập trình hướng đối tượng) trong mã nguồn:
++ Kh</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 20/2019/TT-BTNMT · hiệu lực 2020-02-05
+Thông tư này bãi bỏ một số nội dung của các Thông tư sau: Chương II Phần II Thông tư số 26/2014/TT-BTNMT ngày 28 tháng 5 năm 2014 của Bộ trưởng Bộ Tài nguyên và Môi trường ban hành Quy trình và Định mức kinh tế - kỹ thuật xây dựng cơ sở dữ liệu tài nguyên và môi trường; Điều 18 Thông tư số 58/2015/TT-BTNMT ngày 8 tháng 12 năm 2015 của Bộ trưởng Bộ Tài nguyên và Môi trường quy định thẩm định, kiểm tra và nghiệm thu dự án ứng dụng công nghệ thông tin tài nguyên và môi trường kể từ khi Thông tư này có hiệu lực.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1868,7 +2181,6 @@
           <t>2026-08-13 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -1889,9 +2201,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168261</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1907,17 +2216,38 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 49/2025/TT-NHNN Điều 7 "Thay đổi địa điểm đặt trụ sở chính" (hồ sơ khoản 1, thủ tục cùng địa bàn khoản 2, khác địa bàn khoản 3); cùng NHNN, cùng thông tư bãi bỏ Điều 2 TT 30/2024</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>30/2024/TT-NHNN · hiệu lực 2024-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 2. Sửa đổi, bổ sung một số điều của Thông tư số 25/2017/TT-NHNN ngày 29 tháng 12 năm 2017 của Thống đốc Ngân hàng Nhà nước Việt Nam quy định về hồ sơ, trình tự, thủ tục chấp thuận những thay đổi của tổ chức tín dụng phi ngân hàng
+6. Sửa đổi, bổ sung Điều 6 như sau:
+“Điều 6. Thay đổi địa điểm đặt trụ sở chính</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 49/2025/TT-NHNN · hiệu lực 2026-02-06
+b) Điều 2 Thông tư số 30/2024/TT-NHNN ngày 30/6/2024 của Thống đốc Ngân hàng Nhà nước Việt Nam sửa đổi, bổ sung một số điều của các Thông tư quy định về hồ sơ, thủ tục chấp thuận những thay đổi và mạng lưới hoạt động của tổ chức tín dụng phi ngân hàng.
+CHUYỂN TIẾP: Điều 19. Điều khoản chuyển tiếp
+Tổ chức tín dụng phi ngân hàng đã nộp đủ hồ sơ hợp lệ đề nghị chấp thuận thay đổi một hoặc một số nội dung quy định tại khoản 1 Điều 1 Thông tư này trước ngày Thông tư này có hiệu lực thi hành và phù hợp với quy định của pháp luật tại thời điểm đó được tiếp tục thực hiện theo quy định tại Thông tư số 25/2017/TT-NHNN ngày 29 tháng 12 năm 2017 của Thống đốc Ngân hàng Nhà nước Việt Nam quy định về hồ sơ, trình tự, thủ tục chấp thuận những thay đổi của tổ chức tín dụng phi ngân hàng đã được sửa đổi, bổ sung năm 2024./.
+Nơi nhận:
+- Như Điều 17;
+- Ban Lãnh đạo NHNN;
+- Văn phòng Chính phủ;
+- Bộ Tư pháp (để kiểm tra);
+- Công báo;
+- Lưu: VP, PC, ATHT1 (03 bản).
+KT. THỐNG ĐỐC
+PHÓ THỐNG ĐỐC
+(Đã ký)
+Đoàn Thái Sơn</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1945,7 +2275,6 @@
           <t>2025-08-26 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -1966,9 +2295,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27071</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1979,18 +2305,33 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>23/2024/TT-BTTTT chỉ bãi bỏ khoản 1 Điều 17 TT 30/2011, không có quy định kế thừa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>30/2011/TT-BTTTT · hiệu lực 2012-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 17. Hồ sơ công bố hợp quy và địa điểm tiếp nhận hồ sơ
+1. Hồ sơ đăng ký công bố hợp quy bao gồm:
+a) Bản công bố hợp quy;
+b) Giấy tờ chứng minh tư cách pháp nhân: Bản sao có chứng thực một trong các loại giấy tờ sau: Giấy chứng nhận đăng ký kinh doanh; Quyết định/Giấy phép thành lập, Giấy chứng nhận đầu tư/Giấy phép đầu tư (với trường hợp là tổ chức); Chứng minh nhân dân hoặc hộ chiếu (với trường hợp là cá nhân). Trường hợp nộp hồ sơ trực tiếp có thể nộp bản sao kèm bản gốc để đối chiếu;
+c) Mẫu dấu hợp quy sử dụng cho sản phẩm;
+d) Bản sao Giấy chứng nhận hợp quy do Tổ chức chứng nhận hợp quy cấp còn hiệu lực (Trường hợp công bố hợp quy theo phương thức nêu tại khoản 1 Điều 15 của Thông tư này);
+đ) Kết quả đo kiểm sản phẩm của đơn vị đo kiểm có đủ thẩm quyền quy định tại khoản 2 Điều 5 của Thông tư này và được cấp trong vòng hai (02) năm tính đến ngày nhận đủ hồ sơ hợp lệ; Tài liệu kỹ thuật của sản phẩm thể hiện đầy đủ các nội dung: Tên, ký hiệu và các thông tin kỹ thuật của sản phẩm, ảnh chụp bên ngoài, hãng sản xuất (Trường hợp công bố hợp quy theo phương thức nêu tại khoản 2 Điều 15 của Thông tư này);</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 23/2024/TT-BTTTT · hiệu lực 2024-12-31
+b. Khoản 1 Điều 17 (được sửa đổi bởi khoản 4 Điều 1 Thông tư số 10/2020/TT-BTTTT ngày 07 tháng 5 năm 2020 của Bộ trưởng Bộ Thông tin và Truyền thông sửa đổi, bổ sung một số nội dung của Thông tư số 30/2011/TT-BTTTT ngày 31 tháng 10 năm 2011 của Bộ trưởng Bộ Thông tin và Truyền thông quy định về chứng nhận hợp quy và công bố hợp quy đối với sản phẩm, hàng hóa chuyên ngành công nghệ thông tin và truyền thông);
+c. Điều 18 (được sửa đổi bởi khoản 5 Điều 1 Thông tư số 10/2020/TT-BTTTT ngày 07 tháng 5 năm 2020 của Bộ trưởng Bộ Thông tin và Truyền thông sửa đổi, bổ sung một số nội dung của Thông tư số 30/2011/TT-BTTTT ngày 31 tháng 10 năm 2011 của Bộ trưởng Bộ Thông tin và Truyền thông quy định về chứng nhận hợp quy và công bố hợp quy đối với sản phẩm, hàng hóa chuyên ngành công nghệ thông tin và truyền thông);
+d. Điều 19, Điều 20, Phụ lục V và VI;
+đ) Phụ lục II (được sửa đổi, bổ sung bởi khoản 9 Điều 1 Thông tư số 10/2020/TT-BTTTT ngày 07 tháng 5 năm 2020 của Bộ trưởng Bộ Thông tin và Truyền thông sửa đổi, bổ sung một số nội dung của Thông tư số 30/2011/TT-BTTTT ngày 31 tháng 10 năm 2011 của Bộ trưởng Bộ Thông tin và Truyền thông quy định về chứng nhận hợp quy và công bố hợp quy đối với sản phẩm, hàng hóa chuyên ngành công nghệ thông tin và truyền thông);
+e. Phụ lục IV (được sửa đổi, bổ sung bởi khoản 15 Điều 1 Thông tư số 15/2018/TT-BTTTT ngày 15 tháng 11 năm 2018 của Bộ trưởng Bộ Thông tin và Truyền thông sửa đổi, bổ sung một số nội dung của Thông tư số 30/2011/TT-BTTTT ngày 31 tháng 10 năm 2011 của Bộ trưởng Bộ Thông tin và Truyền thông quy định về chứng nhận hợp quy và công bố hợp quy đối với sản phẩm, hàng hóa chuyên ngành công nghệ thông tin và truyền thông và khoản 8 Điều 1 Thông tư số 10/2020/TT-BTTTT ngày 07 tháng 5 năm 2020 của Bộ trưởng Bộ Thông tin và Truyền thông sửa đổi, bổ sung một số nội dung của Thông tư số 30/2011/TT-BTTTT ngày 31 tháng 10 năm 2011 của Bộ trưởng Bộ Thông tin và Truyền thông quy định về chứng nhận hợp quy và công bố hợp quy đối với sản phẩm, hàng hóa chuyên ngành công nghệ thông tin và truyền thông).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2043,9 +2384,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145900</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2056,14 +2394,24 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>32/2020/TT-BGTVT · hiệu lực 2021-01-29 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Sửa đổi, bổ sung một số điều của Thông tư số 29/2018/TT-BGTVT ngày 14 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về việc kiểm tra chất lượng, an toàn kỹ thuật và bảo vệ môi trường phương tiện giao thông đường sắt (sau đây gọi tắt là Thông tư số 29/2018/TT-BGTVT) như sau:
+6. Điều 10 được sửa đổi, bổ sung như sau:
+"Điều 10. Cấp giấy chứng nhận và tem kiểm định</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 01/2024/TT-BGTVT · hiệu lực 2024-03-15
+a) Điều 1 và khoản 1, khoản 2, khoản 3 Điều 3 của Thông tư số 32/2020/TT-BGTVT ngày 14 tháng 12 năm 2020 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 29/2018/TT-BGTVT ngày 14 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về việc kiểm tra chất lượng, an toàn kỹ thuật và bảo vệ môi trường phương tiện giao thông đường sắt và Thông tư số 31/2018/TT-BGTVT ngày 15 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về thực hiện đánh giá, chứng nhận an toàn hệ thống đối với đường sắt đô thị.
+b) Điều 1 của Thông tư số 01/2022/TT-BGTVT ngày 12 tháng 01 năm 2022 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều Thông tư số 29/2018/TT-BGTVT ngày 14 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về kiểm tra chất lượng, an toàn kỹ thuật và bảo vệ môi trường phương tiện giao thông đường sắt và Thông tư số 18/2019/TT-BGTVT ngày 20 tháng 5 năm 2019 của Bộ trưởng Bộ Giao thông vận tải hướng dẫn thực hiện Nghị định số 139/2018/NĐ-CP ngày 08 tháng 10 năm 2018 của Chính phủ quy định về kinh doanh dịch vụ kiểm định xe cơ giới.
+CHUYỂN TIẾP: Điều 21. Quy định chuyển tiếp
+1. Các Giấy chứng nhận và tem kiểm định đã cấp cho phương tiện, thiết bị tín hiệu đuôi tàu trước ngày Thông tư này có hiệu lực vẫn có giá trị cho đến hết thời hạn còn hiệu lực.
+2. Khi các quy định được dẫn chiếu tại Thông tư này có sửa đổi, bổ sung hoặc được thay thế thì thực hiện theo quy định tại văn bản mới.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2091,7 +2439,6 @@
           <t>2026-05-07 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -2112,9 +2459,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145900</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2130,17 +2474,29 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 01/2024/TT-BGTVT điểm b của các Điều 11–14 (sản xuất lắp ráp, nhập khẩu, hoán cải, định kỳ): Cơ quan kiểm tra ra thông báo không đạt trong 01 ngày làm việc theo Phụ lục X; với nhập khẩu gửi cơ quan hải quan; cùng Bộ GTVT, cùng thông tư bãi bỏ Điều 1 TT 32/2020. Một quy định tách thành bốn điều: người audit xem lại yếu tố 4</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>32/2020/TT-BGTVT · hiệu lực 2021-01-29 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Sửa đổi, bổ sung một số điều của Thông tư số 29/2018/TT-BGTVT ngày 14 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về việc kiểm tra chất lượng, an toàn kỹ thuật và bảo vệ môi trường phương tiện giao thông đường sắt (sau đây gọi tắt là Thông tư số 29/2018/TT-BGTVT) như sau:
+6. Điều 10 được sửa đổi, bổ sung như sau:
+"Điều 10. Cấp giấy chứng nhận và tem kiểm định</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 01/2024/TT-BGTVT · hiệu lực 2024-03-15
+a) Điều 1 và khoản 1, khoản 2, khoản 3 Điều 3 của Thông tư số 32/2020/TT-BGTVT ngày 14 tháng 12 năm 2020 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 29/2018/TT-BGTVT ngày 14 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về việc kiểm tra chất lượng, an toàn kỹ thuật và bảo vệ môi trường phương tiện giao thông đường sắt và Thông tư số 31/2018/TT-BGTVT ngày 15 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về thực hiện đánh giá, chứng nhận an toàn hệ thống đối với đường sắt đô thị.
+b) Điều 1 của Thông tư số 01/2022/TT-BGTVT ngày 12 tháng 01 năm 2022 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều Thông tư số 29/2018/TT-BGTVT ngày 14 tháng 5 năm 2018 của Bộ trưởng Bộ Giao thông vận tải quy định về kiểm tra chất lượng, an toàn kỹ thuật và bảo vệ môi trường phương tiện giao thông đường sắt và Thông tư số 18/2019/TT-BGTVT ngày 20 tháng 5 năm 2019 của Bộ trưởng Bộ Giao thông vận tải hướng dẫn thực hiện Nghị định số 139/2018/NĐ-CP ngày 08 tháng 10 năm 2018 của Chính phủ quy định về kinh doanh dịch vụ kiểm định xe cơ giới.
+CHUYỂN TIẾP: Điều 21. Quy định chuyển tiếp
+1. Các Giấy chứng nhận và tem kiểm định đã cấp cho phương tiện, thiết bị tín hiệu đuôi tàu trước ngày Thông tư này có hiệu lực vẫn có giá trị cho đến hết thời hạn còn hiệu lực.
+2. Khi các quy định được dẫn chiếu tại Thông tư này có sửa đổi, bổ sung hoặc được thay thế thì thực hiện theo quy định tại văn bản mới.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2168,7 +2524,6 @@
           <t>2020-11-11 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -2189,9 +2544,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25402</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2207,17 +2559,36 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 59/2017/NĐ-CP khoản 4 Điều 8 "Nộp hồ sơ đề nghị cấp Giấy phép tiếp cận nguồn gen tới cơ quan nhà nước có thẩm quyền" (cách gửi ở khoản 1 Điều 12); cùng Chính phủ, cùng nghị định bãi bỏ Điều 18 NĐ 65/2010</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>65/2010/NĐ-CP · hiệu lực 2010-07-30 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Trình tự, thủ tục tiếp cận nguồn gen và cấp giấy phép tiếp cận nguồn gen
+2. Trình tự, thủ tục tiếp cận nguồn gen được quy định như sau:
+a) Tổ chức, cá nhân có nhu cầu tiếp cận nguồn gen phải đăng ký bằng văn bản với Ủy ban nhân dân cấp tỉnh nơi có nguồn gen;
+b) Sau khi đã được Ủy ban nhân dân cấp tỉnh chấp nhận việc đăng ký tiếp cận nguồn gen, tổ chức, cá nhân tiến hành ký văn bản thoả thuận về việc tiếp cận nguồn gen và chia sẻ lợi ích với tổ chức, hộ gia đình, cá nhân được giao quản lý nguồn gen. Văn bản thỏa thuận về việc tiếp cận nguồn gen và chia sẻ lợi ích phải có xác nhận của Ủy ban nhân dân cấp xã nơi thực hiện việc tiếp cận nguồn gen;
+c) Gửi hồ sơ đề nghị cơ quan có thẩm quyền quy định tại khoản 3 Điều này cấp giấy phép tiếp cận nguồn gen.</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 59/2017/NĐ-CP · hiệu lực 2017-07-01
+2. Bãi bỏ Điều 18, Điều 19 và Điều 20 Nghị định số 65/2010/NĐ-CP ngày 11 tháng 6 năm 2010 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật đa dạng sinh học.
+3. Bộ trưởng, Thủ trưởng cơ quan ngang Bộ, Thủ trưởng cơ quan thuộc Chính phủ, Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương chịu trách nhiệm thi hành Nghị định này./.
+TM. CHÍNH PHỦ
+THỦ TƯỚNG
+đã ký
+Nguyễn Xuân Phúc
+CHUYỂN TIẾP: Điều 27. Quy định chuyển tiếp
+1. Hồ sơ đề nghị cấp Giấy phép tiếp cận nguồn gen được gửi đến cơ quan nhà nước có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành được xem xét, thẩm định theo quy định tại Nghị định số 65/2010/NĐ-CP ngày 11 tháng 6 năm 2010 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật đa dạng sinh học.
+2. Ủy ban nhân dân cấp tỉnh có trách nhiệm chuyển giao hồ sơ của các trường hợp đã được cấp phép tiếp cận nguồn gen cho Bộ Tài nguyên và Môi trường trước ngày 31 tháng 12 năm 2017 để quản lý.
+3. Tổ chức, cá nhân có nhu cầu tiếp tục sử dụng nguồn gen đã tiếp cận từ ngày 01 tháng 7 năm 2009 đến trước ngày Nghị định này có hiệu lực thi hành mà chưa được cấp Giấy phép tiếp cận nguồn gen phải thực hiện việc đăng ký và đề nghị cấp Giấy phép tiếp cận nguồn gen theo quy định tại Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2270,9 +2641,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30460</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2283,14 +2651,24 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>45/2013/NĐ-CP · hiệu lực 2013-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Sử dụng người lao động cao tuổi làm công việc nặng nhọc, độc hại, nguy hiểm
+1. Việc sử dụng người lao động cao tuổi làm công việc nặng nhọc, độc hại, nguy hiểm chỉ được thực hiện khi có đủ các điều kiện sau đây:
+a) Người lao động cao tuổi có kinh nghiệm, tay nghề cao với thâm niên nghề nghiệp từ đủ 15 năm trở lên; được cấp chứng nhận hoặc chứng chỉ nghề hoặc được công nhận là nghệ nhân theo quy định của pháp luật;
+b) Người lao động cao tuổi có đủ sức khỏe theo tiêu chuẩn do Bộ trưởng Bộ Y tế ban hành đối với nghề, công việc;
+c) Sử dụng có tính thời điểm; không quá 05 năm đối với từng người lao động;
+d) Phải khám sức khỏe định kỳ ít nhất 02 lần trong một năm;
+đ) Có ít nhất 01 người lao động không phải là người lao động cao tuổi cùng làm việc.</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 39/2016/NĐ-CP · hiệu lực 2016-07-01
+2. Các quy định tại Điều 9, 10, 11, 12, 13 và 14 của Nghị định số 45/2013/NĐ-CP ngày 10 tháng 5 năm 2013 của Chính phủ quy định chi Tiết một số Điều của Bộ luật lao động về thời giờ làm việc, thời giờ nghỉ ngơi và an toàn lao động, vệ sinh lao động, Điểm a, b và c Khoản 6 Điều 34 Nghị định số 59/2015/NĐ-CP ngày 18 tháng 6 năm 2015 của Chính phủ về quản lý dự án đầu tư xây dựng hết hiệu lực kể từ ngày Nghị định này có hiệu lực.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2318,7 +2696,6 @@
           <t>2019-08-29 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -2339,9 +2716,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30460</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2357,17 +2731,29 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 39/2016/NĐ-CP điểm d khoản 1 Điều 29 "Chỉ sử dụng không quá 05 năm đối với từng người lao động cao tuổi" (bỏ cụm "có tính thời điểm"); cùng Chính phủ, cùng nghị định chấm dứt Điều 9–14 NĐ 45/2013</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>45/2013/NĐ-CP · hiệu lực 2013-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Sử dụng người lao động cao tuổi làm công việc nặng nhọc, độc hại, nguy hiểm
+1. Việc sử dụng người lao động cao tuổi làm công việc nặng nhọc, độc hại, nguy hiểm chỉ được thực hiện khi có đủ các điều kiện sau đây:
+a) Người lao động cao tuổi có kinh nghiệm, tay nghề cao với thâm niên nghề nghiệp từ đủ 15 năm trở lên; được cấp chứng nhận hoặc chứng chỉ nghề hoặc được công nhận là nghệ nhân theo quy định của pháp luật;
+b) Người lao động cao tuổi có đủ sức khỏe theo tiêu chuẩn do Bộ trưởng Bộ Y tế ban hành đối với nghề, công việc;
+c) Sử dụng có tính thời điểm; không quá 05 năm đối với từng người lao động;
+d) Phải khám sức khỏe định kỳ ít nhất 02 lần trong một năm;
+đ) Có ít nhất 01 người lao động không phải là người lao động cao tuổi cùng làm việc.</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 39/2016/NĐ-CP · hiệu lực 2016-07-01
+2. Các quy định tại Điều 9, 10, 11, 12, 13 và 14 của Nghị định số 45/2013/NĐ-CP ngày 10 tháng 5 năm 2013 của Chính phủ quy định chi Tiết một số Điều của Bộ luật lao động về thời giờ làm việc, thời giờ nghỉ ngơi và an toàn lao động, vệ sinh lao động, Điểm a, b và c Khoản 6 Điều 34 Nghị định số 59/2015/NĐ-CP ngày 18 tháng 6 năm 2015 của Chính phủ về quản lý dự án đầu tư xây dựng hết hiệu lực kể từ ngày Nghị định này có hiệu lực.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2420,9 +2806,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155601</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2433,14 +2816,21 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>13/2022/TT-BTTTT · hiệu lực 2022-10-10 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Biên tập viên hạng I – Mã số: V.11.01.01
+5. Yêu cầu đối với viên chức dự thi hoặc xét thăng hạng lên biên tập viên hạng I
+a) Có thời gian giữ chức danh nghề nghiệp biên tập viên hạng II hoặc tương đương tối thiểu là 06 năm (đủ 72 tháng). Trường hợp có thời gian tương đương thì phải có ít nhất 01 năm (đủ 12 tháng) giữ chức danh nghề nghiệp biên tập viên hạng II tính đến ngày hết thời hạn nộp hồ sơ đăng ký dự thi hoặc xét thăng hạng;
+b) Trong thời gian giữ chức danh nghề nghiệp biên tập viên hạng II hoặc tương đương đã chủ trì hoặc tham gia biên tập ít nhất 02 (hai) tác phẩm đạt giải thưởng cấp bộ, ngành hoặc tương đương trở lên hoặc giải thưởng do cơ quan Đảng ở Trung ương, tổ chức chính trị - xã hội ở Trung ương, Hội nhà báo Việt Nam tổ chức; hoặc chủ trì hoặc tham gia ít nhất 02 (hai) đề tài, chương trình nghiên cứu khoa học chuyên ngành cấp bộ, cấp tỉnh hoặc tương đương trở lên đã được cấp có thẩm quyền ban hành hoặc nghiệm thu.</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 12/2024/TT-BTTTT · hiệu lực 2024-11-07
+3. Bãi bỏ Khoản 5 Điều 4, Khoản 5 Điều 5, Khoản 4 Điều 7, Khoản 4 Điều 8, Khoản 4 Điều 10, Khoản 4 Điều 11, Khoản 4 Điều 13, Khoản 4 Điều 14 Thông tư số 13/2022/TT-BTTTT ngày 26 tháng 8 năm 2022 của Bộ trưởng Bộ Thông tin và Truyền thông quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương đối với viên chức biên tập viên, phóng viên, biên dịch viên, đạo diễn truyền hình thuộc chuyên ngành thông tin và truyền thông.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2493,9 +2883,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=7969</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2506,14 +2893,25 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>14/1998/NĐ-CP · hiệu lực 1998-03-21 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 13. Việc điều chuyển tài sản nhà nước khu vực hành chính sự nghiệp được thực hiện theo quy định sau:
+2. Thẩm quyền điều chuyển tài sản nhà nước được quy định như sau:
+a) Thủ tướng Chính phủ quyết định điều chuyển tài sản nhà nước là đất đai và nhà, công trình xây dựng khác gắn liền với đất đai giữa các Bộ, cơ quan, tổ chức ở trung ương với nhau, giữa các cơ quan hành chính sự nghiệp trung ương với các tổ chức khác theo đề nghị của Bộ trưởng Bộ Tài chính và Bộ trưởng, thủ trưởng cơ quan liên quan.
+Trong trường hợp cần thiết Thủ tướng Chính phủ quyết định điều chuyển tài sản là nhà, đất đai, công trình xây dựng khác gắn liền với đất đai và các tài sản quan trọng khác giữa cơ quan hành chính sự nghiệp trung ương với cơ quan hành chính sự nghiệp địa phương theo đề nghị của Bộ trưởng Bộ Tài chính, Bộ trưởng, thủ trưởng cơ quan liên quan ở Trung ương và Chủ tịch ủy ban nhân dân cấp tỉnh;
+b) Bộ trưởng Bộ Tài chính quyết định điều chuyển các loại tài sản nhà nước còn lại giữa các Bộ, cơ quan, tổ chức ở trung ương với nhau, giữa cơ quan hành chính sự nghiệp trung ương với các tổ chức khác theo đề nghị của Bộ, cơ quan liên quan.
+Trong trường hợp cần thiết, Bộ Tài chính quyết định điều chuyển tài sản Nhà nước còn lại giữa các cơ quan hành chính sự nghiệp trung ương với cơ quan hành chính sự nghiệp địa phương theo đề nghị của Bộ, cơ quan liên quan ở Trung ương và Chủ tịch Uỷ ban nhân dân cấp tỉnh;
+c) Bộ trưởng các Bộ, thủ trưởng các cơ quan ngang Bộ, cơ quan thuộc Chính phủ quyết định điều chuyển tài sản nhà nước giữa các đơn vị hành chính sự nghiệp thụ hưởng ngân sách thuộc nội bộ ngành trực tiếp quản lý, đồng thời báo cáo Bộ Tài chính theo quy định tại Nghị định này;
+d) Chủ tịch ủy ban nhân dân cấp tỉnh quyết định điều chuyển tài sản nhà nước giữa các cơ quan hành chính sự nghiệp của địa phương theo đề nghị của Giám đốc Sở Tài chính - Vật giá và thủ trưởng các cơ quan, đơn vị có tài sản điều chuyển, tiếp nhận.</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 137/2006/NĐ-CP · hiệu lực 2006-12-09
+Nghị định này có hiệu lực thi hành sau 15 ngày, kể từ ngày đăng Công báo. Bãi bỏ Điều 9, Điều 13 và Điều 14 Nghị định số 14/1998/NĐ-CP ngày 06 tháng 3 năm 1998 của Chính phủ về quản lý tài sản nhà nước.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2541,7 +2939,6 @@
           <t>2025-12-21 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -2562,9 +2959,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141055</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2580,17 +2974,38 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 53/2024/NĐ-CP khoản 3 Điều 63 "Trường hợp đang thực hiện việc nạo vét mà có hiện tượng sạt lở bờ thì phải tạm dừng việc nạo vét …", gần giống từng chữ; cùng Chính phủ, cùng nghị định bãi bỏ Điều 14–22 NĐ 23/2020</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>23/2020/NĐ-CP · hiệu lực 2020-04-10 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 17. Yêu cầu đối với hoạt động mở mới và nạo vét, khơi thông luồng, tuyến giao thông thủy thuộc vùng nước đường thủy nội địa
+3. Trường hợp đang thực hiện việc nạo vét mà có hiện tượng sạt, lở bờ thì phải tạm dừng việc nạo vét, đồng thời báo cáo ngay cho chính quyền địa phương và Sở Tài nguyên và Môi trường nơi có hoạt động nạo vét để kiểm tra, xác định nguyên nhân, mức độ tác động tới lòng, bờ bãi sông, báo cáo Ủy ban nhân dân cấp tỉnh xem xét, quyết định.</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 53/2024/NĐ-CP · hiệu lực 2024-07-01
+3. Bãi bỏ các Điều 14, 15, 16, 17, 18, 19, 20, 21, 22 và khoản 5 Điều 33 Nghị định số 23/2020/NĐ-CP ngày 24 tháng 02 năm 2020 của Chính phủ quy định về quản lý cát, sỏi lòng sông và bảo vệ lòng, bờ, bãi sông.
+CHUYỂN TIẾP: Điều 97. Quy định chuyển tiếp
+1. Đối với các hoạt động điều tra cơ bản tài nguyên nước: trường hợp Đề cương dự án có hoạt động điều tra cơ bản tài nguyên nước đã phê duyệt trước ngày Nghị định này có hiệu lực thi hành thì tùy vào điều kiện thực tế, cơ quan có thẩm quyền xem xét, quyết định việc tiếp tục thực hiện theo Đề cương dự án đã được phê duyệt nếu phù hợp với quy định của Nghị định này. Trường hợp không phù hợp với Nghị định này thì rà soát, điều chỉnh để phù hợp.
+2. Đối với quy định về hành lang bảo vệ nguồn nước:
+a) Đối với các hồ chứa thủy điện đã thực hiện cắm mốc giới hoặc đã phê duyệt phương án cắm mốc giới hành lang bảo vệ nguồn nước trước ngày Nghị định này có hiệu lực thì tiếp tục thực hiện việc cắm mốc theo phương án được phê duyệt và được quản lý, bảo vệ mốc giới theo quy định của Nghị định này;
+b) Đối với các hồ chứa thủy điện đã nộp phương án cắm mốc giới hành lang bảo vệ nguồn nước trước ngày Nghị định này có hiệu lực thì trình tự thẩm định, phê duyệt phương án cắm mốc giới hành lang bảo vệ nguồn nước tiếp tục thực hiện theo quy định của Nghị định số 43/2015/NĐ-CP ngày 06 tháng 5 năm 2015 của Chính phủ về lập, quản lý hành lang bảo vệ nguồn nước, quy định tại Điều 1. của Nghị định số 22/2023/NĐ-CP ngày 12 tháng 5 năm 2023 của Chính phủ về sửa đổi, bổ sung một số điều của các nghị định liên quan đến hoạt động kinh doanh trong lĩnh vực tài nguyên và môi trường và thực hiện cắm mốc theo phương án được phê duyệt;
+c) Đối với các địa phương đã phê duyệt, công bố Danh mục nguồn nước phải lập hành lang bảo vệ nguồn nước trước ngày Nghị định này có hiệu lực thì có kế hoạch thể hiện phạm vi hành lang bảo vệ nguồn nước trên bản đồ địa chính hoặc bản đồ hiện trạng sử dụng đất theo quy định tại Điều 27 của Nghị định này. Trường hợp nội dung Danh mục không đáp ứng điều kiện để thể hiện phạm vi trên bản đồ địa chính hoặc bản đồ hiện trạng sử dụng đất thì rà soát, điều chỉnh, cập nhật Danh mục theo quy định của Nghị định này;
+d) Đối với các địa phương đã phê duyệt phương án cắm mốc hành lang bảo vệ nguồn nước đối với các nguồn nước theo quy định tại Điều 13 của Nghị định số 43/2015/NĐ-CP ngày 06 tháng 5 năm 2015 thì phải rà soát, điều chỉnh, cập nhật theo quy định của Nghị định này;
+đ) Đối với các địa phương đang thực hiện lập Danh mục nguồn nước phải lập hành lang bảo vệ nguồn nước trước ngày Nghị định này có hiệu lực thì phải rà soát, điều chỉnh, cập nhật theo quy định của Nghị định này.
+3. Đối với quy định các quy hoạch tổng hợp lưu vực sông liên tỉnh đã được phê duyệt mà chưa quy định ngưỡng khai thác nước dưới đất thì được rà soát, cập nhật, bổ sung khi thực hiện quy hoạch được điều chỉnh.
+4. Đối với các dự án có hoạt động chuyển nước quy định tại khoản 1 Điều 47 của Nghị định này đang trong quá trình thẩm định chấp thuận chủ trương đầu tư đối với các dự án thực hiện theo quy định của pháp luật về đầu tư hoặc thẩm định quyết định đầu tư đối với các dự án thực hiện theo quy định của pháp luật về đầu tư công trước ngày Nghị định này có hiệu lực thì tiếp tục thực hiện.
+5. Đối với việc lập danh mục hồ, ao, đầm, phá không được san lấp: Danh mục hồ, ao, đầm, phá không được san lấp đã được phê duyệt trước ngày Nghị định này có hiệu lực thi hành thì tiếp tục thực hiện. Ủy ban nhân dân tỉnh tổ chức rà soát, cập nhật, công bố hoặc điều chỉnh danh mục theo quy định của Nghị định này hoàn thành trước ngày 01 tháng 7 năm 2026.
+6. Đối với quy định về bảo vệ, phòng, chống sạt lở, lòng, bờ bãi sông, hồ: trường hợp Hồ sơ đánh giá tác động môi trường của các dự án có hoạt động tại khoản 1 Điều 60 của Nghị định này được tiếp nhận trước ngày Nghị định này có hiệu lực thì tiếp tục được giải quyết theo quy định của Nghị định số 23/2020/NĐ-CP ngày 24 tháng 02 năm 2020 của Chính phủ quy định về quản lý cát, sỏi lòng sông và về bảo vệ lòng, bờ, bãi sông.
+7. Đối với quy định về quan trắc, giám sát tài nguyên nước
+a) Đối với các mạng quan trắc tài nguyên nước mặt, tài nguyên nước dưới đất của trung ương và địa phương đã được quy hoạch trong cá [...cắt bớt]</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2643,9 +3058,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140152</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2661,17 +3073,29 @@
           <t>question_leaks</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Câu hỏi chép gần nguyên đáp án (xây dựng bến xe, bãi đỗ xe, trạm dừng nghỉ không bảo đảm tiêu chuẩn kỹ thuật) và khung phạt</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>100/2019/NĐ-CP · hiệu lực 2020-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 14. Xử phạt các hành vi vi phạm về xây dựng bến xe, bãi đỗ xe, trạm dừng nghỉ, trạm thu phí đường bộ
+1. Phạt tiền từ 15.000.000 đồng đến 20.000.000 đồng đối với cá nhân, từ 30.000.000 đồng đến 40.000.000 đồng đối với tổ chức thực hiện một trong các hành vi vi phạm sau đây:
+a) Xây dựng hoặc thành lập bến xe, bãi đỗ xe, trạm dừng nghỉ, trạm thu phí đường bộ khi chưa được cơ quan quản lý nhà nước về giao thông vận tải đồng ý theo quy định;
+b) Xây dựng bến xe, bãi đỗ xe, trạm dừng nghỉ, trạm thu phí đường bộ không bảo đảm tiêu chuẩn kỹ thuật theo quy định.</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 336/2025/NĐ-CP · hiệu lực 2026-03-01
+2. Bãi bỏ Điều 13, 14, 15.
+CHUYỂN TIẾP: Điều 27. Điều khoản chuyển tiếp
+1. Trường hợp hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra và kết thúc trước ngày Nghị định này có hiệu lực thi hành sau đó mới bị phát hiện hoặc đang xem xét giải quyết thì áp dụng Nghị định đang có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử phạt.
+2. Đối với hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra trước thời điểm Nghị định này có hiệu lực nhưng vẫn đang diễn ra khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này để xử phạt.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2699,7 +3123,6 @@
           <t>2026-08-12 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -2720,9 +3143,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140152</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2738,17 +3158,29 @@
           <t>question_leaks</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Như dòng trước. 336/2025/NĐ-CP không có hành vi này, không chuyển chỗ</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>100/2019/NĐ-CP · hiệu lực 2020-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 14. Xử phạt các hành vi vi phạm về xây dựng bến xe, bãi đỗ xe, trạm dừng nghỉ, trạm thu phí đường bộ
+1. Phạt tiền từ 15.000.000 đồng đến 20.000.000 đồng đối với cá nhân, từ 30.000.000 đồng đến 40.000.000 đồng đối với tổ chức thực hiện một trong các hành vi vi phạm sau đây:
+a) Xây dựng hoặc thành lập bến xe, bãi đỗ xe, trạm dừng nghỉ, trạm thu phí đường bộ khi chưa được cơ quan quản lý nhà nước về giao thông vận tải đồng ý theo quy định;
+b) Xây dựng bến xe, bãi đỗ xe, trạm dừng nghỉ, trạm thu phí đường bộ không bảo đảm tiêu chuẩn kỹ thuật theo quy định.</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 336/2025/NĐ-CP · hiệu lực 2026-03-01
+2. Bãi bỏ Điều 13, 14, 15.
+CHUYỂN TIẾP: Điều 27. Điều khoản chuyển tiếp
+1. Trường hợp hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra và kết thúc trước ngày Nghị định này có hiệu lực thi hành sau đó mới bị phát hiện hoặc đang xem xét giải quyết thì áp dụng Nghị định đang có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử phạt.
+2. Đối với hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra trước thời điểm Nghị định này có hiệu lực nhưng vẫn đang diễn ra khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này để xử phạt.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2801,9 +3233,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140152</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2814,14 +3243,24 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>100/2019/NĐ-CP · hiệu lực 2020-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 15. Xử phạt các hành vi vi phạm quy định về quản lý, khai thác, bảo trì, bảo vệ kết cấu hạ tầng giao thông đường bộ
+9. Phạt tiền từ 50.000.000 đồng đến 70.000.000 đồng đối với tổ chức quản lý, vận hành trạm thu phí đường bộ thực hiện một trong các hành vi vi phạm sau đây:
+a) Vi phạm khoản 6, khoản 7, khoản 8 Điều này mà không chấp hành yêu cầu của cơ quan quản lý nhà nước có thẩm quyền về việc triển khai các giải pháp để khắc phục ùn tắc giao thông tại khu vực trạm thu phí;
+b) Không thực hiện việc kết nối, chia sẻ dữ liệu từ trạm thu phí cho cơ quan quản lý nhà nước có thẩm quyền theo quy định.</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 336/2025/NĐ-CP · hiệu lực 2026-03-01
+2. Bãi bỏ Điều 13, 14, 15.
+CHUYỂN TIẾP: Điều 27. Điều khoản chuyển tiếp
+1. Trường hợp hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra và kết thúc trước ngày Nghị định này có hiệu lực thi hành sau đó mới bị phát hiện hoặc đang xem xét giải quyết thì áp dụng Nghị định đang có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử phạt.
+2. Đối với hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra trước thời điểm Nghị định này có hiệu lực nhưng vẫn đang diễn ra khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này để xử phạt.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2874,9 +3313,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140152</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2887,14 +3323,38 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>100/2019/NĐ-CP · hiệu lực 2020-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 28. Xử phạt các hành vi vi phạm quy định về vận tải đường bộ, dịch vụ hỗ trợ vận tải đường bộ
+6. Phạt tiền từ 5.000.000 đồng đến 6.000.000 đồng đối với cá nhân, từ 10.000.000 đồng đến 12.000.000 đồng đối với tổ chức kinh doanh vận tải, dịch vụ hỗ trợ vận tải thực hiện một trong các hành vi vi phạm sau đây:
+a) Tổ chức hoạt động khai thác bến xe, bãi đỗ xe, trạm dừng nghỉ khi chưa được cơ quan có thẩm quyền cho phép theo quy định;
+b) Để xe ô tô không đủ điều kiện kinh doanh vận tải khách vào bến xe ô tô khách đón khách;
+c) Không thực hiện việc cung cấp, cập nhật, truyền, lưu trữ, quản lý các thông tin từ thiết bị giám sát hành trình theo quy định; không cung cấp tên đăng nhập, mật khẩu truy cập vào phần mềm xử lý dữ liệu từ thiết bị giám sát hành trình của các xe ô tô thuộc đơn vị cho cơ quan nhà nước có thẩm quyền;
+d) Không thực hiện đúng các nội dung đã đăng ký, niêm yết về: Hành trình chạy xe; điểm đầu, điểm cuối của tuyến; giá cước; giá dịch vụ; tiêu chuẩn chất lượng dịch vụ vận tải, dịch vụ hỗ trợ vận tải;
+đ) Sử dụng phương tiện kinh doanh vận tải không gắn thiết bị giám sát hành trình của xe (đối với hình thức kinh doanh vận tải có quy định phương tiện phải gắn thiết bị) hoặc gắn thiết bị nhưng thiết bị không hoạt động, không đúng quy chuẩn theo quy định hoặc sử dụng biện pháp kỹ thuật, trang thiết bị ngoại vi, các biện pháp khác làm sai lệch dữ liệu của thiết bị giám sát hành trình của xe ô tô;
+e) Sử dụng xe trung chuyển chở hành khách không đúng quy định;
+g) Sử dụng lái xe điều khiển xe khách giường nằm hai tầng chưa đủ số năm kinh nghiệm theo quy định;
+h) Không có bộ phận quản lý, theo dõi các điều kiện về an toàn giao thông theo quy định hoặc có nhưng bộ phận này không thực hiện đầy đủ các nhiệm vụ theo quy định;
+i) Sử dụng phương tiện kinh doanh vận tải có chất lượng, niên hạn sử dụng không bảo đảm điều kiện của hình thức kinh doanh đã đăng ký;
+k) Không lưu trữ theo quy định các hồ sơ, tài liệu có liên quan trong quá trình quản lý, điều hành hoạt động vận tải của đơn vị;
+l) Không lập hoặc có lập nhưng không cập nhật đầy đủ, chính xác lý lịch phương tiện, lý lịch hành nghề của lái xe theo quy định;
+m) Sử dụng xe kinh doanh vận tải hành khách theo hợp đồng, xe kinh doanh vận tải khách du lịch mà trên xe không có hợp đồng vận chuyển (hợp đồng lữ hành), danh sách hành khách kèm theo, thiết bị để truy cập nội dung hợp đồng điện tử và danh sách hành khách theo quy định hoặc có hợp đồng vận chuyển (hợp đồng lữ hành), danh sách hành khách, thiết bị để truy cập nhưng không bảo đảm yêu cầu theo quy định, chở người không có tên trong danh sách hành khách hoặc vận chuyển không đúng đối tượng theo quy định (đối với xe kinh doanh vận tải hành khách theo hợp đồng vận chuyển học sinh, sinh viên, cán bộ công nhân viên đi học, đi làm việc);
+n) Sử dụng xe taxi chở hành khách không lắp đồng hồ tính tiền (đối với loại xe đăng ký sử dụng đồng hồ tính tiền) hoặc lắp đồng hồ tính tiền không đúng quy định; không có thiết bị in hóa đơn (phiếu thu tiền) được kết nối với đồng hồ tính tiền theo quy định hoặc có nhưng không sử dụng được hoặc in ra phiếu thu tiền nhưng không có đầy đủ các thông tin theo quy định;
+o) Sử dụng xe ô tô kinh doanh vận tải không lắp camera theo quy định (đối với loại xe có quy định phải lắp camera) hoặc có lắp camera nhưng không ghi, không lưu trữ được hành ảnh trên xe, người lái xe trong quá trình xe tham gia giao thông theo quy định;
+p) Không thực hiện việc truyền, lưu trữ hình ảnh từ camera lắp trên xe ô tô về máy chủ của đơn vị, không cung cấp tài khoản truy cập vào máy chủ của đơn vị cho cơ quan nhà nước có thẩm quyền theo quy định;
+q) Sử dụng xe taxi chở hành khách mà trên xe không có thiết bị để kết nối trực tiếp với hành khách theo quy định (đối với loại xe đăng ký sử dụng phần mềm tính tiền) hoặc sử dụng phần mềm tính tiền không bảo đảm các yêu cầu theo quy định.</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 336/2025/NĐ-CP · hiệu lực 2026-03-01
+5. Bãi bỏ điểm a, b, c, d, đ, i khoản 2; điểm b, c khoản 3; điểm b, c, d, đ, h, i, k, l, m, n, o, p, r, t khoản 4; điểm a, b, c, d, h, i, k, l, n, q khoản 6; điểm a, b, c, d, e, g, k khoản 7; điểm c, d khoản 8; điểm a, b khoản 10; điểm a, b, d, đ, e, g, h, k và điểm l khoản 11 Điều 28.
+CHUYỂN TIẾP: Điều 27. Điều khoản chuyển tiếp
+1. Trường hợp hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra và kết thúc trước ngày Nghị định này có hiệu lực thi hành sau đó mới bị phát hiện hoặc đang xem xét giải quyết thì áp dụng Nghị định đang có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử phạt.
+2. Đối với hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra trước thời điểm Nghị định này có hiệu lực nhưng vẫn đang diễn ra khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này để xử phạt.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2947,9 +3407,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140152</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2965,17 +3422,43 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 336/2025/NĐ-CP điểm d một khoản của Điều 12 "Sử dụng xe taxi chở hành khách không lắp đồng hồ tính tiền … không có thiết bị in hóa đơn …", giống từng chữ; cùng Chính phủ, cùng nghị định bãi bỏ điểm n khoản 6 Điều 28 NĐ 100/2019. Người audit đối chiếu khung phạt mới (đổi mức vẫn là chuyển chỗ)</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>100/2019/NĐ-CP · hiệu lực 2020-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 28. Xử phạt các hành vi vi phạm quy định về vận tải đường bộ, dịch vụ hỗ trợ vận tải đường bộ
+6. Phạt tiền từ 5.000.000 đồng đến 6.000.000 đồng đối với cá nhân, từ 10.000.000 đồng đến 12.000.000 đồng đối với tổ chức kinh doanh vận tải, dịch vụ hỗ trợ vận tải thực hiện một trong các hành vi vi phạm sau đây:
+a) Tổ chức hoạt động khai thác bến xe, bãi đỗ xe, trạm dừng nghỉ khi chưa được cơ quan có thẩm quyền cho phép theo quy định;
+b) Để xe ô tô không đủ điều kiện kinh doanh vận tải khách vào bến xe ô tô khách đón khách;
+c) Không thực hiện việc cung cấp, cập nhật, truyền, lưu trữ, quản lý các thông tin từ thiết bị giám sát hành trình theo quy định; không cung cấp tên đăng nhập, mật khẩu truy cập vào phần mềm xử lý dữ liệu từ thiết bị giám sát hành trình của các xe ô tô thuộc đơn vị cho cơ quan nhà nước có thẩm quyền;
+d) Không thực hiện đúng các nội dung đã đăng ký, niêm yết về: Hành trình chạy xe; điểm đầu, điểm cuối của tuyến; giá cước; giá dịch vụ; tiêu chuẩn chất lượng dịch vụ vận tải, dịch vụ hỗ trợ vận tải;
+đ) Sử dụng phương tiện kinh doanh vận tải không gắn thiết bị giám sát hành trình của xe (đối với hình thức kinh doanh vận tải có quy định phương tiện phải gắn thiết bị) hoặc gắn thiết bị nhưng thiết bị không hoạt động, không đúng quy chuẩn theo quy định hoặc sử dụng biện pháp kỹ thuật, trang thiết bị ngoại vi, các biện pháp khác làm sai lệch dữ liệu của thiết bị giám sát hành trình của xe ô tô;
+e) Sử dụng xe trung chuyển chở hành khách không đúng quy định;
+g) Sử dụng lái xe điều khiển xe khách giường nằm hai tầng chưa đủ số năm kinh nghiệm theo quy định;
+h) Không có bộ phận quản lý, theo dõi các điều kiện về an toàn giao thông theo quy định hoặc có nhưng bộ phận này không thực hiện đầy đủ các nhiệm vụ theo quy định;
+i) Sử dụng phương tiện kinh doanh vận tải có chất lượng, niên hạn sử dụng không bảo đảm điều kiện của hình thức kinh doanh đã đăng ký;
+k) Không lưu trữ theo quy định các hồ sơ, tài liệu có liên quan trong quá trình quản lý, điều hành hoạt động vận tải của đơn vị;
+l) Không lập hoặc có lập nhưng không cập nhật đầy đủ, chính xác lý lịch phương tiện, lý lịch hành nghề của lái xe theo quy định;
+m) Sử dụng xe kinh doanh vận tải hành khách theo hợp đồng, xe kinh doanh vận tải khách du lịch mà trên xe không có hợp đồng vận chuyển (hợp đồng lữ hành), danh sách hành khách kèm theo, thiết bị để truy cập nội dung hợp đồng điện tử và danh sách hành khách theo quy định hoặc có hợp đồng vận chuyển (hợp đồng lữ hành), danh sách hành khách, thiết bị để truy cập nhưng không bảo đảm yêu cầu theo quy định, chở người không có tên trong danh sách hành khách hoặc vận chuyển không đúng đối tượng theo quy định (đối với xe kinh doanh vận tải hành khách theo hợp đồng vận chuyển học sinh, sinh viên, cán bộ công nhân viên đi học, đi làm việc);
+n) Sử dụng xe taxi chở hành khách không lắp đồng hồ tính tiền (đối với loại xe đăng ký sử dụng đồng hồ tính tiền) hoặc lắp đồng hồ tính tiền không đúng quy định; không có thiết bị in hóa đơn (phiếu thu tiền) được kết nối với đồng hồ tính tiền theo quy định hoặc có nhưng không sử dụng được hoặc in ra phiếu thu tiền nhưng không có đầy đủ các thông tin theo quy định;
+o) Sử dụng xe ô tô kinh doanh vận tải không lắp camera theo quy định (đối với loại xe có quy định phải lắp camera) hoặc có lắp camera nhưng không ghi, không lưu trữ được hành ảnh trên xe, người lái xe trong quá trình xe tham gia giao thông theo quy định;
+p) Không thực hiện việc truyền, lưu trữ hình ảnh từ camera lắp trên xe ô tô về máy chủ của đơn vị, không cung cấp tài khoản truy cập vào máy chủ của đơn vị cho cơ quan nhà nước có thẩm quyền theo quy định;
+q) Sử dụng xe taxi chở hành khách mà trên xe không có thiết bị để kết nối trực tiếp với hành khách theo quy định (đối với loại xe đăng ký sử dụng phần mềm tính tiền) hoặc sử dụng phần mềm tính tiền không bảo đảm các yêu cầu theo quy định.</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 336/2025/NĐ-CP · hiệu lực 2026-03-01
+5. Bãi bỏ điểm a, b, c, d, đ, i khoản 2; điểm b, c khoản 3; điểm b, c, d, đ, h, i, k, l, m, n, o, p, r, t khoản 4; điểm a, b, c, d, h, i, k, l, n, q khoản 6; điểm a, b, c, d, e, g, k khoản 7; điểm c, d khoản 8; điểm a, b khoản 10; điểm a, b, d, đ, e, g, h, k và điểm l khoản 11 Điều 28.
+CHUYỂN TIẾP: Điều 27. Điều khoản chuyển tiếp
+1. Trường hợp hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra và kết thúc trước ngày Nghị định này có hiệu lực thi hành sau đó mới bị phát hiện hoặc đang xem xét giải quyết thì áp dụng Nghị định đang có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử phạt.
+2. Đối với hành vi vi phạm hành chính trong hoạt động đường bộ xảy ra trước thời điểm Nghị định này có hiệu lực nhưng vẫn đang diễn ra khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này để xử phạt.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3028,9 +3511,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178223</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3041,14 +3521,34 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>140/2025/NĐ-CP · hiệu lực 2025-07-01 → 2027-03-01 · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Nhiệm vụ, thẩm quyền về giấy phép xây dựng
+2. Thẩm quyền chấp thuận về địa điểm xây dựng quy định tại khoản 9 Điều 53 Nghị định số 175/2024/NĐ-CP ngày 30 tháng 12 năm 2024 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng do Ủy ban nhân dân cấp xã thực hiện.</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 217/2026/NĐ-CP · hiệu lực 2026-07-01
+b) Điều 4, 5, 6 và 7, khoản 3 Điều 29 Nghị định số 140/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ quy định về phân định thẩm quyền của chính quyền địa phương 02 cấp trong lĩnh vực quản lý nhà nước của Bộ Xây dựng;
+c) Khoản 1 Điều 4, Điều 10, Điều 11, Phụ lục III ban hành kèm theo Nghị định số 144/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ quy định về phân quyền, phân cấp trong lĩnh vực quản lý nhà nước của Bộ Xây dựng;
+d) Điều 24 Nghị định số 14/2026/NĐ-CP ngày 13 tháng 01 năm 2026 của Chính phủ sửa đổi, bổ sung một số điều của các nghị định để cắt giảm, đơn giản hóa thủ tục hành chính liên quan đến hoạt động sản xuất, kinh doanh thuộc phạm vi quản lý của Bộ Xây dựng;
+đ) Khoản 1 Điều 28 Nghị định số 178/2025/NĐ-CP ngày 01 tháng 7 năm 2025 của Chính phủ quy định chi tiết một số điều của Luật Quy hoạch đô thị và nông thôn.
+4. Các Bộ trưởng, Thủ trưởng cơ quan ngang bộ, Chủ tịch Ủy ban nhân dân các tỉnh, thành phố chịu trách nhiệm thi hành Nghị định này.
+CHUYỂN TIẾP: Điều 76. Điều khoản chuyển tiếp
+1. Dự án, công trình xây dựng đã được cơ quan chuyên môn về xây dựng thông báo kết quả thẩm định thiết kế cơ sở, Báo cáo nghiên cứu khả thi hoặc thẩm định Báo cáo nghiên cứu khả thi một phần theo giai đoạn thực hiện của dự án trước ngày Nghị định này có hiệu lực thì không phải thẩm định lại theo quy định của Nghị định này. Việc thẩm định Báo cáo nghiên cứu khả thi các giai đoạn còn lại của dự án, điều chỉnh dự án thực hiện theo quy định của Nghị định này.
+2. Dự án đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định Báo cáo nghiên cứu khả thi điều chỉnh trước ngày Nghị định này có hiệu lực thi hành và đủ điều kiện thẩm định nhưng chưa có thông báo kết quả thẩm định thì cơ quan chuyên môn về xây dựng tiếp tục thẩm định theo quy định của Nghị định số 175/2024/NĐ-CP ngày 30 tháng 12 năm 2024 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng. Trường hợp không đủ điều kiện thẩm định hoặc kết quả thẩm định là chưa đủ điều kiện để tổng hợp, trình phê duyệt thì việc thẩm định Báo cáo nghiên cứu khả thi thực hiện theo quy định của Nghị định này.
+3. Công trình hoặc một phần công trình xây dựng đã được cơ quan chuyên môn về xây dựng thông báo kết quả thẩm định thiết kế xây dựng triển khai sau thiết kế cơ sở, thiết kế xây dựng điều chỉnh và được phê duyệt đúng quy định trước ngày Nghị định này có hiệu lực thì việc triển khai các bước tiếp theo của công trình hoặc các phần còn lại của công trình (bao gồm cả việc điều chỉnh thiết kế xây dựng triển khai sau khi dự án được phê duyệt) thực hiện theo quy định của Nghị định này.
+4. Công trình hoặc một phần công trình xây dựng đã được cơ quan chuyên môn về xây dựng thẩm định thiết kế xây dựng triển khai sau thiết kế cơ sở, thiết kế xây dựng điều chỉnh trước ngày Nghị định này có hiệu lực nhưng chưa được phê duyệt thì việc phê duyệt và triển khai các bước tiếp theo thực hiện theo quy định tại Nghị định này.
+5. Công trình hoặc một phần công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định thiết kế xây dựng triển khai sau thiết kế cơ sở hoặc thiết kế xây dựng điều chỉnh mà đến ngày Nghị định này có hiệu lực chưa có thông báo kết quả thẩm định thì cơ quan chuyên môn về xây dựng dừng việc thẩm định và có văn bản gửi chủ đầu tư để nhận lại hồ sơ trình thẩm định. Chủ đầu tư thực hiện thẩm định thiết kế xây dựng triển khai sau khi dự án được phê duyệt, thiết kế xây dựng điều chỉnh và triển khai các bước tiếp theo theo quy định tại Luật Xây dựng năm 2025 và Nghị định này.
+6. Quy hoạch vùng liên huyện trong thời hạn hiệu lực của quy hoạch theo quy định của pháp luật về quy hoạch và đô thị nông thôn được sử dụng làm căn cứ lập Báo cáo nghiên cứu khả thi dự án hạ tầng kỹ thuật khung. Quy hoạch có tính chất kỹ thuật chuyên ngành còn hiệu lực theo pháp luật về quy hoạch được sử dụng làm căn cứ lập Báo cáo nghiên cứu khả thi dự án thuộc lĩnh vực kết cấu hạ tầng được xác định tại quy hoạch này.
+7. Dự án đã được cơ quan chuyên môn về xây dựng thẩm định thiết kế cơ sở, Báo cáo nghiên cứu khả thi, Báo cáo nghiên cứu khả thi điều chỉnh toàn bộ hoặc một phần theo giai đoạn thực hiện trước ngày Nghị định này có hiệu lực thi hành thì thẩm quyền thẩm định được quy định như sau:
+a) Cơ quan chuyên môn về xây dựng đã thực hiện thẩm định thiết kế cơ sở, Báo cáo nghiên cứu khả thi, Báo cáo nghiên cứu khả thi điều chỉnh thì cơ quan này tiếp tục thực hiện thẩm định Báo cáo nghiên cứu khả thi các giai đoạn còn lại của dự án hoặc thẩm định Báo cáo nghiên cứu khả thi điều chỉnh của dự án. Trường hợp đã được cả cơ quan chuyên môn về xây dựng thuộc bộ quản lý công trình xây dựng chuyên ngành và cơ quan chuyên môn về xây dựng thuộc Ủy ban nhân dân cấp tỉnh thẩm định thì thẩm quyền thẩm định thực hiện theo quy định tại Điều 32, Điều 33 Nghị định này;
+b) Riêng đối với dự án đầu tư xây dựng thuộc địa bàn thành phố Hà Nội, Thành phố Hồ Chí Minh thì thẩm quyền thẩm định Báo cáo nghiên cứu khả thi các giai đoạn còn lại c [...cắt bớt]
+14. Việc chuyển tiếp thực hiện dự án áp dụng loại hợp đồng Xây dựng - Chuyển giao (BT) được thực hiện theo quy định của pháp luật về đầu tư theo phương thức đối tác công tư. Trường hợp dự án BT được chuyển tiếp theo quy định của pháp luật về đầu tư theo phương thức đối tác công tư thì khi triển khai các bước tiếp theo (bao gồm cả việc điều chỉnh), thẩm quyền, nội dung và trình tự thẩm định Báo cáo nghiên cứu khả thi, Báo cáo nghiên cứu khả thi điều chỉnh của cơ quan chuyên môn về xây dựng được thực hiện theo quy định đối với dự án PPP của Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3076,7 +3576,6 @@
           <t>2026-08-17 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -3097,9 +3596,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178223</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3110,18 +3606,39 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>unclear: 217/2026/NĐ-CP khoản 9 Điều 55 nhắc "văn bản chấp thuận về địa điểm xây dựng của Ủy ban nhân dân cấp huyện (trước đây) hoặc Ủy ban nhân dân cấp xã" như một loại giấy tờ đất đai, không giao thẩm quyền rõ như Điều 4 NĐ 140/2025; chưa đủ để kết luận chuyển chỗ</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>140/2025/NĐ-CP · hiệu lực 2025-07-01 → 2027-03-01 · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Nhiệm vụ, thẩm quyền về giấy phép xây dựng
+2. Thẩm quyền chấp thuận về địa điểm xây dựng quy định tại khoản 9 Điều 53 Nghị định số 175/2024/NĐ-CP ngày 30 tháng 12 năm 2024 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng do Ủy ban nhân dân cấp xã thực hiện.</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 217/2026/NĐ-CP · hiệu lực 2026-07-01
+b) Điều 4, 5, 6 và 7, khoản 3 Điều 29 Nghị định số 140/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ quy định về phân định thẩm quyền của chính quyền địa phương 02 cấp trong lĩnh vực quản lý nhà nước của Bộ Xây dựng;
+c) Khoản 1 Điều 4, Điều 10, Điều 11, Phụ lục III ban hành kèm theo Nghị định số 144/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ quy định về phân quyền, phân cấp trong lĩnh vực quản lý nhà nước của Bộ Xây dựng;
+d) Điều 24 Nghị định số 14/2026/NĐ-CP ngày 13 tháng 01 năm 2026 của Chính phủ sửa đổi, bổ sung một số điều của các nghị định để cắt giảm, đơn giản hóa thủ tục hành chính liên quan đến hoạt động sản xuất, kinh doanh thuộc phạm vi quản lý của Bộ Xây dựng;
+đ) Khoản 1 Điều 28 Nghị định số 178/2025/NĐ-CP ngày 01 tháng 7 năm 2025 của Chính phủ quy định chi tiết một số điều của Luật Quy hoạch đô thị và nông thôn.
+4. Các Bộ trưởng, Thủ trưởng cơ quan ngang bộ, Chủ tịch Ủy ban nhân dân các tỉnh, thành phố chịu trách nhiệm thi hành Nghị định này.
+CHUYỂN TIẾP: Điều 76. Điều khoản chuyển tiếp
+1. Dự án, công trình xây dựng đã được cơ quan chuyên môn về xây dựng thông báo kết quả thẩm định thiết kế cơ sở, Báo cáo nghiên cứu khả thi hoặc thẩm định Báo cáo nghiên cứu khả thi một phần theo giai đoạn thực hiện của dự án trước ngày Nghị định này có hiệu lực thì không phải thẩm định lại theo quy định của Nghị định này. Việc thẩm định Báo cáo nghiên cứu khả thi các giai đoạn còn lại của dự án, điều chỉnh dự án thực hiện theo quy định của Nghị định này.
+2. Dự án đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định Báo cáo nghiên cứu khả thi điều chỉnh trước ngày Nghị định này có hiệu lực thi hành và đủ điều kiện thẩm định nhưng chưa có thông báo kết quả thẩm định thì cơ quan chuyên môn về xây dựng tiếp tục thẩm định theo quy định của Nghị định số 175/2024/NĐ-CP ngày 30 tháng 12 năm 2024 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng. Trường hợp không đủ điều kiện thẩm định hoặc kết quả thẩm định là chưa đủ điều kiện để tổng hợp, trình phê duyệt thì việc thẩm định Báo cáo nghiên cứu khả thi thực hiện theo quy định của Nghị định này.
+3. Công trình hoặc một phần công trình xây dựng đã được cơ quan chuyên môn về xây dựng thông báo kết quả thẩm định thiết kế xây dựng triển khai sau thiết kế cơ sở, thiết kế xây dựng điều chỉnh và được phê duyệt đúng quy định trước ngày Nghị định này có hiệu lực thì việc triển khai các bước tiếp theo của công trình hoặc các phần còn lại của công trình (bao gồm cả việc điều chỉnh thiết kế xây dựng triển khai sau khi dự án được phê duyệt) thực hiện theo quy định của Nghị định này.
+4. Công trình hoặc một phần công trình xây dựng đã được cơ quan chuyên môn về xây dựng thẩm định thiết kế xây dựng triển khai sau thiết kế cơ sở, thiết kế xây dựng điều chỉnh trước ngày Nghị định này có hiệu lực nhưng chưa được phê duyệt thì việc phê duyệt và triển khai các bước tiếp theo thực hiện theo quy định tại Nghị định này.
+5. Công trình hoặc một phần công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định thiết kế xây dựng triển khai sau thiết kế cơ sở hoặc thiết kế xây dựng điều chỉnh mà đến ngày Nghị định này có hiệu lực chưa có thông báo kết quả thẩm định thì cơ quan chuyên môn về xây dựng dừng việc thẩm định và có văn bản gửi chủ đầu tư để nhận lại hồ sơ trình thẩm định. Chủ đầu tư thực hiện thẩm định thiết kế xây dựng triển khai sau khi dự án được phê duyệt, thiết kế xây dựng điều chỉnh và triển khai các bước tiếp theo theo quy định tại Luật Xây dựng năm 2025 và Nghị định này.
+6. Quy hoạch vùng liên huyện trong thời hạn hiệu lực của quy hoạch theo quy định của pháp luật về quy hoạch và đô thị nông thôn được sử dụng làm căn cứ lập Báo cáo nghiên cứu khả thi dự án hạ tầng kỹ thuật khung. Quy hoạch có tính chất kỹ thuật chuyên ngành còn hiệu lực theo pháp luật về quy hoạch được sử dụng làm căn cứ lập Báo cáo nghiên cứu khả thi dự án thuộc lĩnh vực kết cấu hạ tầng được xác định tại quy hoạch này.
+7. Dự án đã được cơ quan chuyên môn về xây dựng thẩm định thiết kế cơ sở, Báo cáo nghiên cứu khả thi, Báo cáo nghiên cứu khả thi điều chỉnh toàn bộ hoặc một phần theo giai đoạn thực hiện trước ngày Nghị định này có hiệu lực thi hành thì thẩm quyền thẩm định được quy định như sau:
+a) Cơ quan chuyên môn về xây dựng đã thực hiện thẩm định thiết kế cơ sở, Báo cáo nghiên cứu khả thi, Báo cáo nghiên cứu khả thi điều chỉnh thì cơ quan này tiếp tục thực hiện thẩm định Báo cáo nghiên cứu khả thi các giai đoạn còn lại của dự án hoặc thẩm định Báo cáo nghiên cứu khả thi điều chỉnh của dự án. Trường hợp đã được cả cơ quan chuyên môn về xây dựng thuộc bộ quản lý công trình xây dựng chuyên ngành và cơ quan chuyên môn về xây dựng thuộc Ủy ban nhân dân cấp tỉnh thẩm định thì thẩm quyền thẩm định thực hiện theo quy định tại Điều 32, Điều 33 Nghị định này;
+b) Riêng đối với dự án đầu tư xây dựng thuộc địa bàn thành phố Hà Nội, Thành phố Hồ Chí Minh thì thẩm quyền thẩm định Báo cáo nghiên cứu khả thi các giai đoạn còn lại c [...cắt bớt]
+14. Việc chuyển tiếp thực hiện dự án áp dụng loại hợp đồng Xây dựng - Chuyển giao (BT) được thực hiện theo quy định của pháp luật về đầu tư theo phương thức đối tác công tư. Trường hợp dự án BT được chuyển tiếp theo quy định của pháp luật về đầu tư theo phương thức đối tác công tư thì khi triển khai các bước tiếp theo (bao gồm cả việc điều chỉnh), thẩm quyền, nội dung và trình tự thẩm định Báo cáo nghiên cứu khả thi, Báo cáo nghiên cứu khả thi điều chỉnh của cơ quan chuyên môn về xây dựng được thực hiện theo quy định đối với dự án PPP của Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3174,9 +3691,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118307</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3187,14 +3701,28 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>03/2017/NĐ-CP · hiệu lực 2017-03-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 58. Thẩm quyền xử phạt vi phạm hành chính và thẩm quyền lập biên bản vi phạm hành chính
+2. Chánh thanh tra Sở Tài chính có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện được sử dụng để vi phạm hành chính có giá trị không vượt quá mức tiền phạt quy định tại điểm b khoản này;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại khoản 3 Điều 44 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 137/2021/NĐ-CP · hiệu lực 2022-01-01
+b) Chương VII Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino;
+c) Chương VII Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài;
+d) Khoản 13, khoản 14 và khoản 15 Điều 1 Nghị định số 175/2016/NĐ-CP ngày 30 tháng 12 năm 2016 của Chính phủ sửa đổi, bổ sung một số điều quy định tại Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài.
+CHUYỂN TIẾP: Điều 63. Điều khoản chuyển tiếp
+1. Đối với hành vi vi phạm xảy ra trước thời điểm Nghị định này có hiệu lực mà bị phát hiện hoặc xem xét ra quyết định xử phạt khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn.
+2. Đối với các quyết định xử phạt vi phạm hành chính trong lĩnh vực đặt cược và trò chơi có thưởng đã được ban hành hoặc được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 06/2017/NĐ-CP ngày 24 tháng 01 năm 2017 của Chính phủ về kinh doanh đặt cược đua ngựa, đua chó và bóng đá quốc tế, Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino và Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài để giải quyết.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3222,7 +3750,6 @@
           <t>2022-10-23 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -3243,9 +3770,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118307</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3261,17 +3785,33 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 137/2021/NĐ-CP điểm d khoản 2 Điều 57 "Chánh Thanh tra Sở Tài chính có quyền: … d) Áp dụng các biện pháp khắc phục hậu quả quy định tại Điều 4 Nghị định này"; cùng Chính phủ, cùng nghị định bãi bỏ Chương VII NĐ 03/2017 (yếu tố 7)</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>03/2017/NĐ-CP · hiệu lực 2017-03-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 58. Thẩm quyền xử phạt vi phạm hành chính và thẩm quyền lập biên bản vi phạm hành chính
+2. Chánh thanh tra Sở Tài chính có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện được sử dụng để vi phạm hành chính có giá trị không vượt quá mức tiền phạt quy định tại điểm b khoản này;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại khoản 3 Điều 44 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 137/2021/NĐ-CP · hiệu lực 2022-01-01
+b) Chương VII Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino;
+c) Chương VII Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài;
+d) Khoản 13, khoản 14 và khoản 15 Điều 1 Nghị định số 175/2016/NĐ-CP ngày 30 tháng 12 năm 2016 của Chính phủ sửa đổi, bổ sung một số điều quy định tại Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài.
+CHUYỂN TIẾP: Điều 63. Điều khoản chuyển tiếp
+1. Đối với hành vi vi phạm xảy ra trước thời điểm Nghị định này có hiệu lực mà bị phát hiện hoặc xem xét ra quyết định xử phạt khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn.
+2. Đối với các quyết định xử phạt vi phạm hành chính trong lĩnh vực đặt cược và trò chơi có thưởng đã được ban hành hoặc được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 06/2017/NĐ-CP ngày 24 tháng 01 năm 2017 của Chính phủ về kinh doanh đặt cược đua ngựa, đua chó và bóng đá quốc tế, Nghị định số 03/2017/NĐ-CP ngày 16 tháng 01 năm 2017 của Chính phủ về kinh doanh casino và Nghị định số 86/2013/NĐ-CP ngày 29 tháng 7 năm 2013 của Chính phủ về kinh doanh trò chơi điện tử có thưởng dành cho người nước ngoài để giải quyết.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3299,7 +3839,6 @@
           <t>2026-07-23 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -3320,9 +3859,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=40180</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3338,17 +3874,61 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 09/2025/TT-BNV khoản 2 Điều 15 "Ủy ban nhân dân cấp xã trong thời gian 15 ngày … gửi Bộ Chỉ huy quân sự cấp tỉnh hoặc cơ quan có thẩm quyền theo quy định của Bộ Công an"; Bộ Nội vụ kế thừa Bộ LĐTBXH, cùng thông tư bãi bỏ Điều 26 TT 05/2013. Nơi nhận đổi từ cấp huyện sang cấp tỉnh do bỏ cấp huyện</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>05/2013/TT-BLĐTBXH · hiệu lực 2013-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 26. Thủ tục xác nhận và giải quyết chế độ
+2. Người mắc bệnh quy định tại Điểm h Khoản 1 Điều 33 của Nghị định
+a) Người mắc bệnh hoặc thân nhân làm đơn đề nghị giải quyết chế độ kèm giấy tờ quy định tại Điểm a, b, c Khoản 2 Điều 25 của Thông tư này gửi Ủy ban nhân dân cấp xã;
+b) Ủy ban nhân dân cấp xã trong thời gian 15 ngày kể từ ngày nhận đơn có trách nhiệm xác minh, lập biên bản đề nghị xác nhận bệnh binh kèm giấy tờ quy định tại Điểm a Khoản này gửi Ban Chỉ huy quân sự huyện hoặc cơ quan có thẩm quyền theo quy định của Bộ Công an;
+c) Ban Chỉ huy quân sự huyện hoặc cơ quan có thẩm quyền theo quy định của Bộ Công an trong thời gian 15 ngày kể từ ngày nhận đủ giấy tờ hợp lệ quy định tại Điểm b Khoản này, có trách nhiệm kiểm tra, cấp giấy xác nhận về thời gian phục vụ trong quân đội, công an (trong trường hợp không còn quyết định phục viên hoặc xuất ngũ); chuyển các giấy tờ đến cơ quan, đơn vị có thẩm quyền cấp giấy chứng nhận bệnh tật theo quy định của Bộ Quốc phòng hoặc Bộ Công an;
+d) Cơ quan, đơn vị có thẩm quyền theo quy định của Bộ Quốc phòng hoặc Bộ Công an có trách nhiệm cấp giấy chứng nhận bệnh tật và giới thiệu ra Hội đồng giám định y khoa có thẩm quyền;
+đ) Cơ quan có thẩm quyền của Bộ Quốc phòng hoặc Bộ Công an căn cứ biên bản kết luận của Hội đồng giám định y khoa để ra quyết định cấp giấy chứng nhận bệnh binh và trợ cấp, phụ cấp; chuyển đến cơ quan Lao động - Thương binh và Xã hội nơi bệnh binh cư trú để thực hiện chế độ ưu đãi.</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 09/2025/TT-BNV · hiệu lực 2025-07-01
+n) Điều 26 Thông tư số 05/2013/TT-BLĐTBXH ngày 15 tháng 5 năm 2013 của Bộ trưởng Bộ Lao động - Thương binh và Xã hội hướng dẫn về thủ tục lập hồ sơ, quản lý hồ sơ, thực hiện chế độ ưu đãi người có công với cách mạng và thân nhân.
+CHUYỂN TIẾP: Điều 19. Điều khoản chuyển tiếp và trách nhiệm thi hành
+1. Điều khoản chuyển tiếp
+a) Đối với các hồ sơ đã nộp trước ngày Thông tư này có hiệu lực, cơ quan tiếp nhận hồ sơ tiếp tục giải quyết theo các quy định hiện hành cho đến khi kết thúc thủ tục hành chính;
+b) Trường hợp điều kiện thực hiện nhiệm vụ quy định tại Điều 16 Thông tư này tại địa phương chưa bảo đảm được thì Bộ Nội vụ (Cục Việc làm) tiếp tục thực hiện trách nhiệm tiếp nhận, xử lý hồ sơ đăng ký kiểm tra chất lượng sản phẩm, hàng hóa nhập khẩu theo đề nghị của tổ chức, cá nhân sản xuất, kinh doanh, nhập khẩu sản phẩm, hàng hóa đến hết ngày 31 tháng 12 năm 2025.
+2. Trách nhiệm thi hành
+a) Ủy ban nhân dân các cấp có trách nhiệm chỉ đạo các cơ quan chức năng có liên quan kiểm tra, thực hiện Thông tư này;
+b) Trường hợp phát sinh vướng mắc trong quá trình thực hiện, các cơ quan, tổ chức, đơn vị, cá nhân liên quan có trách nhiệm phản ánh về Bộ Nội vụ để xem xét, hướng dẫn theo quy định của pháp luật./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc TW;
+- Văn phòng TW Đảng và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Hội đồng dân tộc và các Ủy ban của Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- Cục kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Công báo; Cổng Thông tin điện tử của Chính phủ; Cổng thông tin điện tử của Bộ Nội vụ;
+- Bộ Nội vụ: Bộ trưởng, các Thứ trưởng; các đơn vị thuộc, trực thuộc Bộ Nội vụ;
+- Lưu: VT, PC.
+BỘ TRƯỞNG
+(đã ký)
+Phạm Thị Thanh Trà
+1. Điều khoản chuyển tiếp
+a) Đối với các hồ sơ đã nộp trước ngày Thông tư này có hiệu lực, cơ quan tiếp nhận hồ sơ tiếp tục giải quyết theo các quy định hiện hành cho đến khi kết thúc thủ tục hành chính;
+b) Trường hợp điều kiện thực hiện nhiệm vụ quy định tại Điều 16 Thông tư này tại địa phương chưa bảo đảm được thì Bộ Nội vụ (Cục Việc làm) tiếp tục thực hiện trách nhiệm tiếp nhận, xử lý hồ sơ đăng ký kiểm tra chất lượng sản phẩm, hàng hóa nhập khẩu theo đề nghị của tổ chức, cá nhân sản xuất, kinh doanh, nhập khẩu sản phẩm, hàng hóa đến hết ngày 31 tháng 12 năm 2025.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3376,7 +3956,6 @@
           <t>2022-12-21 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -3397,9 +3976,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43494</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3410,18 +3986,26 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>unclear: TT 03/2022/TT-BTNMT bãi bỏ Chương III TT 12/2013 và ban hành định mức kỹ thuật lưu trữ; chưa đối chiếu được nguyên văn để tìm trách nhiệm kiểm tra định kỳ của Trung tâm Thông tin Lưu trữ Địa chất</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>12/2013/TT-BTNMT · hiệu lực 2013-07-22 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Thống kê, xác định giá trị dữ liệu
+1. Kiểm tra định kỳ hàng năm, thống kê số lượng, chất lượng dữ liệu được lưu trữ, bảo quản.</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 03/2022/TT-BTNMT (1) · hiệu lực 2022-04-15
+c) Bãi bỏ Chương III Thông tư số 12/2013/TT-BTNMT ngày 05 tháng 6 năm 2013 của Bộ trưởng Bộ Tài nguyên và Môi trường quy định về việc giao nộp, thu nhận, lưu giữ, bảo quản và cung cấp dữ liệu về địa chất, khoáng sản;
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Các nhiệm vụ, dự án chuyên môn về thu nhận, lưu trữ, bảo quản và cung cấp thông tin, dữ liệu tài nguyên và môi trường được phê duyệt và thực hiện trước ngày Thông tư này có hiệu lực thì tiếp tục thực hiện theo các căn cứ đã được phê duyệt, trừ trường hợp có yêu cầu thực hiện theo quy định của Thông tư này.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3449,7 +4033,6 @@
           <t>2019-08-01 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -3470,9 +4053,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=66786</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3483,18 +4063,55 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>57/2018/TT-BTC bãi bỏ Điều 13–19 TT 203/2014; không thấy quy định Cục trưởng Cục Hải quan quyết định chi theo thực tế phát sinh</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>203/2014/TT-BTC · hiệu lực 2015-02-05 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Mức chi
+4. Đối với những khoản chi quy định tại Điều 17 Thông tư này mà không thuộc phạm vi quy định tại các khoản 1, 2 và 3 Điều này, Cục trưởng Cục Hải quan quyết định chi trên cơ sở thực tế phát sinh, hợp đồng với đơn vị cung cấp dịch vụ và chuyên gia (nếu có) và khả năng kinh phí thực hiện xử lý tài sản, đồng thời chịu trách nhiệm về quyết định của mình.</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 57/2018/TT-BTC · hiệu lực 2018-08-20
+c) Điều 13, 14, 15, 16, 17, 18 và 19 Thông tư số 203/2014/TT-BTC ngày 22 tháng 12 năm 2014 của Bộ Tài chính hướng dẫn xử lý hàng hóa tồn đọng thuộc địa bàn hoạt động hải quan.
+Trong quá trình thực hiện, nếu phát sinh vướng mắc, đề nghị các cơ quan, tổ chức, đơn vị phản ánh kịp thời về Bộ Tài chính để phối hợp giải quyết./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng bí thư;
+- Văn phòng Quốc hội;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Chính phủ;
+- Viện Kiểm sát nhân dân tối cao;
+- Toà án nhân dân tối cao;
+- Kiểm toán Nhà nước;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc Chính phủ;
+- Cơ quan Trung ương của các đoàn thể;
+- HĐND, UBND tỉnh, thành phố trực thuộc Trang ương;
+- Sờ Tài chính, Kho bạc Nhà nước các tỉnh, thành phố trực thuộc Trung ương;
+- Cục Kiểm tra văn bản QPPL (Bộ Tư pháp);
+- Công báo; cổng TTĐT Chính phủ;
+- Cổng TTĐT Bộ Tài chính;
+- Các đơn vị thuộc Bộ Tài chính; -
+Lưu: VT, QLCS.(360)
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(đã ký)
+Trần Xuân Hà
+CHUYỂN TIẾP: Điều 14. Xử lý chuyển tiếp
+1. Đối với tài sản được xác lập quyền sở hữu toàn dân trước ngày Nghị định số 29/2018/NĐ-CP có hiệu lực thi hành (trừ tài sản quy định tại Khoản 2 Điều này) nhưng chưa được cơ quan, người có thẩm quyền phê duyệt phương án xử lý thì thực hiện việc quản lý, xử lý theo quy định tại Nghị định số 29/2018/NĐ-CP và Thông tư này (trong đó đối với tang vật, phương tiện vi phạm hành chính đang tổ chức thực hiện bán, thanh lý, tiêu hủy theo quy định của pháp luật tại thời điểm Nghị định số 29/2018/NĐ-CP có hiệu lực thi hành thì phải bổ sung quyết định phê duyệt phương án để thực hiện các bước tiếp theo).
+Trường hợp tài sản đã có quyết định phê duyệt phương án xử lý đang thực hiện xử lý theo quy định của pháp luật trước ngày Nghị định số 29/2018/NĐ-CP có hiệu lực thi hành nhưng chưa hoàn thành việc thực hiện xử lý thì tiếp tục thực hiện các bước xử lý chưa hoàn thành và quản lý, sử dụng số tiền thu được từ xử lý tài sản theo quy định tại Nghị định số 29/2018/NĐ-CP và Thông tư này.
+2. Đối với tài sản là hàng hóa tồn đọng thuộc địa bàn hoạt động hải quan đã được xác lập quyền sở hữu của Nhà nước (nay là xác lập quyền sở hữu toàn dân) và đã được cấp có thẩm quyền quyết định phương án xử lý theo quy định tại Thông tư 203/2014/TT-BTC ngày 22 tháng 12 năm 2014 của Bộ Tài chính hướng dẫn xử lý hàng hóa tồn đọng thuộc địa bàn hoạt động hải quan thì tiếp tục thực hiện và quản lý, sử dụng số tiền thu được từ xử lý tài sản theo quy định tại Thông tư số 203/2014/TT-BTC.
+3. Đối với tài sản là hàng hóa tồn đọng thuộc địa bàn hoạt động hải quan chưa được xác lập hoặc đã xác lập quyền sở hữu của Nhà nước (nay là xác lập quyền sở hữu toàn dân) nhưng chưa có phương án xử lý thì thực hiện xác lập quyền sở hữu toàn dân, thực hiện xử lý và quản lý, sử dụng số tiền thu được từ xử lý tài sản theo quy định tại Nghị định số 29/2018/NĐ-CP và Thông tư này.
+4. Đối với số tiền thu được từ xử lý tài sản là hàng hóa tồn đọng thuộc địa bàn hoạt động hải quan còn lại (nếu có) trên tài khoản tạm giữ do Cục trưởng Cục Hải quan làm chủ tài khoản, Cục Hải quan thực hiện chuyển vào tài khoản tạm giữ do Sở Tài chính làm chủ tài khoản quy định tại Điểm b Khoản 1 Điều 13 Thông tư này và hoàn thành trước ngày 01 tháng 01 năm 2019.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3547,9 +4164,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=150957</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3565,17 +4179,24 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 74/2022/TT-BTC khoản 3 Điều 3 "Tổ chức thu phí kê khai, nộp tiền phí thu được vào ngân sách nhà nước theo tháng …, quyết toán năm"; cùng Bộ Tài chính, cùng thông tư bãi bỏ khoản 2 Điều 5 TT 02/2021</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>02/2021/TT-BTC · hiệu lực 2021-02-22 → nay · lúc thu thập: Còn hiệu lực
+Điều 5. Kê khai, nộp phí
+2. Tổ chức thu phí thực hiện kê khai, nộp phí theo tháng và quyết toán theo năm theo quy định tại Luật Quản lý thuế số 38/2019/QH14 và Nghị định số 126/2020/NĐ-CP ngày 19/10/2020 của Chính phủ quy định chi tiết một số điều của Luật Quản lý thuế.</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 74/2022/TT-BTC · hiệu lực 2022-12-22
+109. Bãi bỏ khoản 2 Điều 5 Thông tư số 02/2021/TT-BTC ngày 08 tháng 01 năm 2021 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí kiểm định phương tiện phòng cháy và chữa cháy.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3628,9 +4249,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147402</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3646,17 +4264,48 @@
           <t>question_ambiguous</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>TT 40/2020 có yêu cầu về sách phục vụ đào tạo ở cả Điều 6 điểm d khoản 3 (giảng viên chính: chủ trì hoặc tham gia) và Điều 7 điểm đ khoản 3 (giảng viên cao cấp: chủ trì); câu hỏi không nêu chức danh</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>40/2020/TT-BGDĐT · hiệu lực 2020-12-12 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 6. Giảng viên chính (hạng II) - Mã số: V.07.01.02
+3. Tiêu chuẩn về năng lực chuyên môn, nghiệp vụ:
+a) Có kiến thức vững vàng về các môn học được phân công giảng dạy và kiến thức cơ bản của một số môn học có liên quan trong chuyên ngành đào tạo được giao đảm nhiệm;
+b) Hiểu và thực hiện có hiệu quả mục tiêu, kế hoạch, nội dung, chương trình các môn học được phân công đảm nhiệm; nắm bắt kịp thời yêu cầu thực tiễn đối với chuyên ngành đào tạo;
+c) Chủ trì thực hiện ít nhất 01 (một) nhiệm vụ khoa học và công nghệ cấp cơ sở hoặc cấp cao hơn đã nghiệm thu với kết quả từ đạt yêu cầu trở lên;
+d) Chủ trì hoặc tham gia biên soạn ít nhất 01 (một) sách phục vụ đào tạo, được hội đồng khoa học (do thủ trưởng cơ sở giáo dục đại học hoặc cấp có thẩm quyền phê duyệt thành lập) thẩm định, nghiệm thu và đưa vào sử dụng trong đào tạo, bồi dưỡng từ trình độ đại học trở lên phù hợp với ngành, chuyên ngành giảng dạy hoặc đào tạo của giảng viên và có mã số chuẩn quốc tế ISBN;
+đ) Tác giả của ít nhất 03 (ba) bài báo khoa học là công trình nghiên cứu khoa học của giảng viên đã được công bố trên tạp chí khoa học có mã số chuẩn quốc tế ISSN;
+e) Có khả năng ứng dụng công nghệ thông tin và sử dụng ngoại ngữ trong thực hiện các nhiệm vụ của chức danh giảng viên chính (hạng II);
+g) Viên chức dự thi hoặc xét thăng hạng từ chức danh nghề nghiệp giảng viên (hạng III), mã số V.07.01.03 lên chức danh nghề nghiệp giảng viên chính (hạng II), mã số V.07.01.02 phải có thời gian giữ chức danh nghề nghiệp giảng viên (hạng III), mã số V.07.01.03 hoặc tương đương tối thiểu đủ 09 (chín) năm đối với người có bằng thạc sĩ, đủ 06 (sáu) năm đối với người có bằng tiến sĩ; trong đó phải có ít nhất 01 năm (đủ 12 tháng) giữ hạng chức danh nghề nghiệp giảng viên (hạng III), mã số V.07.01.03 tính đến ngày hết thời hạn nộp hồ sơ đăng ký dự thi hoặc xét thăng hạng.</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 26/2026/TT-BGDĐT · hiệu lực 2026-04-09
+2. Điều 3, Điều 5, Điều 6 và Điều 7 của Thông tư số 40/2020/TT-BGDĐT quy định mã số, tiêu chuẩn chức danh nghề nghiệp, bổ nhiệm và xếp lương đối với viên chức giảng dạy trong các cơ sở giáo dục đại học công lập; Điều 2 của Thông tư số 04/2022/TT-BGDĐT sửa đổi, bổ sung một số điều của Thông tư số 35/2020/TT-BGDĐT quy định mã số, tiêu chuẩn chức danh nghề nghiệp, bổ nhiệm và xếp lương đối với viên chức giảng dạy trong các trường cao đẳng sư phạm công lập và Thông tư số 40/2020/TT-BGDĐT hết hiệu lực kể từ ngày Thông tư này có hiệu lực thi hành.
+3. Bộ trưởng, Thủ trưởng cơ quan ngang Bộ, Thủ trưởng cơ quan thuộc Chính phủ, Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương; cơ sở giáo dục đại học và các cơ quan, tổ chức, cá nhân có liên quan chịu trách nhiệm thi hành Thông tư này.
+4. Trường hợp các văn bản dẫn chiếu tại Thông tư này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo các văn bản mới.
+5. Trong quá trình thực hiện nếu có vướng mắc, đề nghị phản ánh về Bộ Giáo dục và Đào tạo để được hướng dẫn hoặc xem xét, giải quyết .
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+Phạm Ngọc Thưởng
+\
+\
+469372
+CHUYỂN TIẾP: Điều 8. Điều khoản chuyển tiếp
+1. Chứng chỉ bồi dưỡng theo tiêu chuẩn chức danh nghề nghiệp các hạng của giảng viên đại học hoặc chứng chỉ bồi dưỡng theo tiêu chuẩn chức danh nghề nghiệp giảng viên đại học theo quy định của pháp luật được cấp trước ngày 31 tháng 12 năm 2026 được xác định tương đương với chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học quy định tại Thông tư này.
+2. Giảng viên trong cơ sở giáo dục đại học được tuyển dụng, tiếp nhận hoặc thay đổi vị trí việc làm sang vị trí việc làm giảng viên đại học trước ngày Thông tư này có hiệu lực thi hành thì không yêu cầu đáp ứng tiêu chuẩn có chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học.
+3. Người được tuyển dụng, tiếp nhận hoặc thay đổi vị trí việc làm sang vị trí việc làm giảng viên đại học kể từ ngày Thông tư này có hiệu lực thi hành:
+a) Trường hợp đã có chứng chỉ bồi dưỡng quy định tại khoản 1 Điều này thì được xác định đáp ứng tiêu chuẩn có chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học;
+b) Trường hợp chưa có chứng chỉ bồi dưỡng quy định tại khoản 1 Điều này thì phải hoàn thiện đáp ứng yêu cầu về chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học trong thời hạn 12 tháng kể từ ngày chương trình bồi dưỡng chuẩn nghề nghiệp giảng viên đại học có hiệu lực thi hành;
+c) Sau 12 tháng kể từ ngày chương trình bồi dưỡng chuẩn nghề nghiệp giảng viên đại học có hiệu lực thi hành thì phải đáp ứng đầy đủ yêu cầu về chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học theo quy định.
+4. Các trường hợp thuộc đối tượng tuyển dụng, tiếp nhận, xét thăng hạng chức danh nghề nghiệp giảng viên đại học trong cơ sở giáo dục đại học công lập theo đề án, kế hoạch của cấp có thẩm quyền phê duyệt trước ngày 30 tháng 6 năm 2026 thực hiện theo quy định tại khoản 1 Điều 25 Nghị định số 93/2026/NĐ-CP ngày 31 tháng 3 năm 2026 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Nhà giáo.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3684,7 +4333,6 @@
           <t>2026-07-25 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -3705,9 +4353,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147402</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3723,17 +4368,48 @@
           <t>question_ambiguous,gold_wrong</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Như dòng trước. Chuyển chỗ: 26/2026/TT-BGDĐT điểm d Điều 6 (chuẩn nghề nghiệp giảng viên chính), gần giống từng chữ; cùng Bộ GDĐT, cùng thông tư chấm dứt Điều 3, 5, 6, 7 TT 40/2020. Từ "tiêu chuẩn chức danh" sang "chuẩn nghề nghiệp": người audit xem lại yếu tố 4</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>40/2020/TT-BGDĐT · hiệu lực 2020-12-12 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 6. Giảng viên chính (hạng II) - Mã số: V.07.01.02
+3. Tiêu chuẩn về năng lực chuyên môn, nghiệp vụ:
+a) Có kiến thức vững vàng về các môn học được phân công giảng dạy và kiến thức cơ bản của một số môn học có liên quan trong chuyên ngành đào tạo được giao đảm nhiệm;
+b) Hiểu và thực hiện có hiệu quả mục tiêu, kế hoạch, nội dung, chương trình các môn học được phân công đảm nhiệm; nắm bắt kịp thời yêu cầu thực tiễn đối với chuyên ngành đào tạo;
+c) Chủ trì thực hiện ít nhất 01 (một) nhiệm vụ khoa học và công nghệ cấp cơ sở hoặc cấp cao hơn đã nghiệm thu với kết quả từ đạt yêu cầu trở lên;
+d) Chủ trì hoặc tham gia biên soạn ít nhất 01 (một) sách phục vụ đào tạo, được hội đồng khoa học (do thủ trưởng cơ sở giáo dục đại học hoặc cấp có thẩm quyền phê duyệt thành lập) thẩm định, nghiệm thu và đưa vào sử dụng trong đào tạo, bồi dưỡng từ trình độ đại học trở lên phù hợp với ngành, chuyên ngành giảng dạy hoặc đào tạo của giảng viên và có mã số chuẩn quốc tế ISBN;
+đ) Tác giả của ít nhất 03 (ba) bài báo khoa học là công trình nghiên cứu khoa học của giảng viên đã được công bố trên tạp chí khoa học có mã số chuẩn quốc tế ISSN;
+e) Có khả năng ứng dụng công nghệ thông tin và sử dụng ngoại ngữ trong thực hiện các nhiệm vụ của chức danh giảng viên chính (hạng II);
+g) Viên chức dự thi hoặc xét thăng hạng từ chức danh nghề nghiệp giảng viên (hạng III), mã số V.07.01.03 lên chức danh nghề nghiệp giảng viên chính (hạng II), mã số V.07.01.02 phải có thời gian giữ chức danh nghề nghiệp giảng viên (hạng III), mã số V.07.01.03 hoặc tương đương tối thiểu đủ 09 (chín) năm đối với người có bằng thạc sĩ, đủ 06 (sáu) năm đối với người có bằng tiến sĩ; trong đó phải có ít nhất 01 năm (đủ 12 tháng) giữ hạng chức danh nghề nghiệp giảng viên (hạng III), mã số V.07.01.03 tính đến ngày hết thời hạn nộp hồ sơ đăng ký dự thi hoặc xét thăng hạng.</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 26/2026/TT-BGDĐT · hiệu lực 2026-04-09
+2. Điều 3, Điều 5, Điều 6 và Điều 7 của Thông tư số 40/2020/TT-BGDĐT quy định mã số, tiêu chuẩn chức danh nghề nghiệp, bổ nhiệm và xếp lương đối với viên chức giảng dạy trong các cơ sở giáo dục đại học công lập; Điều 2 của Thông tư số 04/2022/TT-BGDĐT sửa đổi, bổ sung một số điều của Thông tư số 35/2020/TT-BGDĐT quy định mã số, tiêu chuẩn chức danh nghề nghiệp, bổ nhiệm và xếp lương đối với viên chức giảng dạy trong các trường cao đẳng sư phạm công lập và Thông tư số 40/2020/TT-BGDĐT hết hiệu lực kể từ ngày Thông tư này có hiệu lực thi hành.
+3. Bộ trưởng, Thủ trưởng cơ quan ngang Bộ, Thủ trưởng cơ quan thuộc Chính phủ, Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương; cơ sở giáo dục đại học và các cơ quan, tổ chức, cá nhân có liên quan chịu trách nhiệm thi hành Thông tư này.
+4. Trường hợp các văn bản dẫn chiếu tại Thông tư này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo các văn bản mới.
+5. Trong quá trình thực hiện nếu có vướng mắc, đề nghị phản ánh về Bộ Giáo dục và Đào tạo để được hướng dẫn hoặc xem xét, giải quyết .
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+Phạm Ngọc Thưởng
+\
+\
+469372
+CHUYỂN TIẾP: Điều 8. Điều khoản chuyển tiếp
+1. Chứng chỉ bồi dưỡng theo tiêu chuẩn chức danh nghề nghiệp các hạng của giảng viên đại học hoặc chứng chỉ bồi dưỡng theo tiêu chuẩn chức danh nghề nghiệp giảng viên đại học theo quy định của pháp luật được cấp trước ngày 31 tháng 12 năm 2026 được xác định tương đương với chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học quy định tại Thông tư này.
+2. Giảng viên trong cơ sở giáo dục đại học được tuyển dụng, tiếp nhận hoặc thay đổi vị trí việc làm sang vị trí việc làm giảng viên đại học trước ngày Thông tư này có hiệu lực thi hành thì không yêu cầu đáp ứng tiêu chuẩn có chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học.
+3. Người được tuyển dụng, tiếp nhận hoặc thay đổi vị trí việc làm sang vị trí việc làm giảng viên đại học kể từ ngày Thông tư này có hiệu lực thi hành:
+a) Trường hợp đã có chứng chỉ bồi dưỡng quy định tại khoản 1 Điều này thì được xác định đáp ứng tiêu chuẩn có chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học;
+b) Trường hợp chưa có chứng chỉ bồi dưỡng quy định tại khoản 1 Điều này thì phải hoàn thiện đáp ứng yêu cầu về chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học trong thời hạn 12 tháng kể từ ngày chương trình bồi dưỡng chuẩn nghề nghiệp giảng viên đại học có hiệu lực thi hành;
+c) Sau 12 tháng kể từ ngày chương trình bồi dưỡng chuẩn nghề nghiệp giảng viên đại học có hiệu lực thi hành thì phải đáp ứng đầy đủ yêu cầu về chứng chỉ bồi dưỡng chuẩn nghề nghiệp giảng viên đại học theo quy định.
+4. Các trường hợp thuộc đối tượng tuyển dụng, tiếp nhận, xét thăng hạng chức danh nghề nghiệp giảng viên đại học trong cơ sở giáo dục đại học công lập theo đề án, kế hoạch của cấp có thẩm quyền phê duyệt trước ngày 30 tháng 6 năm 2026 thực hiện theo quy định tại khoản 1 Điều 25 Nghị định số 93/2026/NĐ-CP ngày 31 tháng 3 năm 2026 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Nhà giáo.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3786,9 +4462,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152516</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3799,14 +4472,19 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>112/2021/TT-BTC · hiệu lực 2022-02-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 5. Kê khai, nộp phí
+2. Tổ chức thu phí thực hiện kê khai, nộp số tiền phí thu được theo tháng, quyết toán năm theo quy định tại Luật Quản lý thuế và Nghị định số 126/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định chi tiết một số điều của Luật Quản lý thuế.</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 74/2022/TT-BTC · hiệu lực 2022-12-22
+117. Bãi bỏ khoản 2 Điều 5 Thông tư số 112/2021/TT-BTC ngày 15 tháng 12 năm 2021 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí trong lĩnh vực quản lý nuôi trồng thủy sản.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3859,9 +4537,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152516</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3877,17 +4552,24 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 74/2022/TT-BTC khoản 3 Điều 3 "Tổ chức thu phí kê khai, nộp tiền phí thu được vào ngân sách nhà nước theo tháng …, quyết toán năm"; cùng Bộ Tài chính, cùng thông tư bãi bỏ khoản 2 Điều 5 TT 112/2021</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>112/2021/TT-BTC · hiệu lực 2022-02-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 5. Kê khai, nộp phí
+2. Tổ chức thu phí thực hiện kê khai, nộp số tiền phí thu được theo tháng, quyết toán năm theo quy định tại Luật Quản lý thuế và Nghị định số 126/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định chi tiết một số điều của Luật Quản lý thuế.</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 74/2022/TT-BTC · hiệu lực 2022-12-22
+117. Bãi bỏ khoản 2 Điều 5 Thông tư số 112/2021/TT-BTC ngày 15 tháng 12 năm 2021 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí trong lĩnh vực quản lý nuôi trồng thủy sản.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3915,7 +4597,6 @@
           <t>2025-10-19 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -3936,9 +4617,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14476</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3954,17 +4632,30 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 47/2024/NĐ-CP khoản 2 Điều 3 "Cơ sở dữ liệu quốc gia là cơ sở dữ liệu của một hoặc một số lĩnh vực kinh tế - xã hội được xây dựng, cập nhật và duy trì … phục vụ lợi ích công cộng"; cùng Chính phủ, cùng nghị định bãi bỏ Điều 11 NĐ 64/2007</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>64/2007/NĐ-CP · hiệu lực 2007-05-18 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Xây dựng cơ sở dữ liệu quốc gia
+1. Cơ sở dữ liệu quốc gia là tập hợp thông tin của một hoặc một số lĩnh vực kinh tế - xã hội được xây dựng, cập nhật và duy trì đáp ứng yêu cầu truy nhập và sử dụng thông tin của các ngành kinh tế và phục vụ lợi ích xã hội.</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 47/2024/NĐ-CP · hiệu lực 2024-05-09
+b) Điều 11 Nghị định số 64/2007/NĐ-CP ngày 10 tháng 4 năm 2007 của Chính phủ quy định về ứng dụng công nghệ thông tin trong hoạt động của cơ quan nhà nước.
+3. Kể từ ngày Nghị định này có hiệu lực, các quy định về việc xây dựng, cập nhật, duy trì, khai thác và sử dụng cơ sở dữ liệu quốc gia chưa phù hợp với các quy định tại Nghị định này thì thống nhất áp dụng quy định tại Nghị định này.
+CHUYỂN TIẾP: Điều 26. Quy định chuyển tiếp
+1. Đối với các cơ sở dữ liệu quốc gia đã xây dựng trước thời điểm Trung tâm dữ liệu quốc gia quy định tại Điều 14 Nghị định này đi vào hoạt động:
+a) Chuyển hệ thống thông tin cơ sở dữ liệu quốc gia về Trung tâm dữ liệu quốc gia đối với hệ thống thông tin cơ sở dữ liệu quốc gia đang đặt tại hạ tầng trung tâm dữ liệu của chủ quản cơ sở dữ liệu quốc gia không đáp ứng yêu cầu tối thiểu hạng II (hoặc tương đương) theo tiêu chuẩn quốc gia về trung tâm dữ liệu chậm nhất quý IV năm 2025. Trường hợp không đáp ứng được yêu cầu trên, cơ quan chủ quản cơ sở dữ liệu quốc gia báo cáo Thủ tướng Chính phủ quyết định;
+b) Đối với cơ sở dữ liệu quốc gia hoạt động trên hạ tầng trung tâm dữ liệu đang thuê ngoài: chuyển hệ thống thông tin cơ sở dữ liệu quốc gia về Trung tâm dữ liệu quốc gia khi kết thúc hợp đồng thuê ngoài.
+2. Đối với các cơ sở dữ liệu quốc gia đang được quy định tại các Luật và Nghị định hiện hành, chưa được cập nhật vào Danh mục cơ sở dữ liệu quốc gia: Trong vòng 01 năm kể từ ngày Nghị định này có hiệu lực, chủ quản cơ sở dữ liệu quốc gia chủ động rà soát, đáp ứng các yêu cầu quy định tại khoản 1 Điều 6 Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4017,9 +4708,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27474</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4030,14 +4718,61 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>08/2012/TTLT-BLĐTBXH-BNV-BTC · hiệu lực 2012-06-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 5. Trình tự, thời hạn giải quyết chế độ trợ cấp
+1. Đối tượng TNXP hoặc thân nhân của TNXP (trường hợp TNXP đã từ trần) thực hiện nộp 01 bộ hồ sơ theo quy định tại Điều 4 Thông tư này cho Ủy ban nhân dân cấp xã nơi đăng ký hộ khẩu thường trú.</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[repeal_ancestor] 09/2025/TT-BNV · hiệu lực 2025-07-01
+b) Điều 4, 5 Thông tư liên tịch số 08/2012/TTLT-BLĐTBXH-BNV-BTC ngày 16 tháng 04 năm 2012 của Bộ trưởng Bộ Lao động – Thương binh và Xã hội, Bộ Nội vụ, Bộ Tài chính hướng dẫn thực hiện chế độ trợ cấp đối với thanh niên xung phong đã hoàn thành nhiệm vụ trong kháng chiến theo Quyết định số 40/2011/QĐ-TTg ngày 27 tháng 7 năm 2011 của Thủ tướng Chính phủ;
+c) Khoản 2, 3 Điều 4 Thông tư liên tịch số 17/2014/TTLT-BLĐTBXH-BTC ngày 01 tháng 8 năm 2014 của Bộ trưởng Bộ Lao động – Thương binh và Xã hội, Bộ Tài chính hướng dẫn thực hiện trợ cấp một lần đối với người được cử làm chuyên gia sang giúp Lào và Campuchia theo Quyết định số 57/2013/QĐ-TTg ngày 14 tháng 10 năm 2013 của Thủ tướng Chính phủ;
+d) Khoản 6 Điều 12 Thông tư số 11/2022/TT-BLĐTBXH ngày 30 tháng 6 năm 2022 của Bộ trưởng Bộ Lao động – Thương binh và Xã hội hướng dẫn một số nội dung thực hiện hỗ trợ việc làm bền vững thuộc Chương trình mục tiêu quốc gia giảm nghèo bền vững giai đoạn 2021-2025;
+đ) Mẫu số 05, Mẫu số 06, Mẫu số 07, Mẫu số 08, Mẫu số 09, Mẫu số 10, Mẫu số 11, Mẫu số 12, Mẫu số 13, Mẫu số 14, Mẫu số 15 Phụ lục I của Thông tư số 08/2023/TT-BLĐTBXH ngày 29 tháng 8 năm 2023 của Bộ trưởng Bộ Lao động – Thương binh và Xã hội sửa đổi, bổ sung, bãi bỏ một số điều của các Thông tư, Thông tư liên tịch có quy định liên quan đến việc nộp, xuất trình sổ hộ khẩu giấy, sổ tạm trú giấy hoặc giấy tờ có yêu cầu xác nhận nơi cư trú khi thực hiện thủ tục hành chính thuộc lĩnh vực quản lý nhà nước của Bộ Lao động - Thương binh và Xã hội;
+e) Điều 3 Thông tư số 21/2021/TT-BLĐTBXH ngày 15 tháng 12 năm 2021 của Bộ trưởng Bộ Lao động – Thương binh và Xã hội quy định chi tiết một số điều của Luật Người lao động Việt Nam đi làm việc ở nước ngoài theo hợp đồng;
+g) Khoản 1 Điều 1 Thông tư số 02/2024/TT-BLĐTBXH ngày 23 tháng 02 năm 2024 của Bộ trưởng Bộ Lao động – Thương binh và Xã hội sửa đổi, bổ sung một số điều của Thông tư số 21/2021/TT-BLĐTBXH ngày 15 tháng 12 năm 2021 của Bộ trưởng Bộ lao động - Thương binh và Xã hội quy định chi tiết một số điều của Luật người lao động Việt Nam đi làm việc ở nước ngoài theo hợp đồng;
+h) Điểm a khoản 1, khoản 2 Điều 1; điểm b, d khoản 1, khoản 2 Điều 2; khoản 2 Điều 3, khoản 2 Điều 4 Thông tư số 08/2014/TT-BNV ngày 19 tháng 09 năm 2014 của Bộ trưởng Bộ Nội vụ quy định về Ban công tác người cao tuổi tỉnh, thành phố trực thuộc Trung ương và Ban công tác người cao tuổi huyện, quận, thị xã, thành phố thuộc tỉnh;
+i) Điểm a khoản 5 Điều 1; điểm c khoản 1, điểm b khoản 2 Điều 6 Thông tư số 01/2024/TT-BNV ngày 24 tháng 02 năm 2024 của Bộ trưởng Bộ Nội vụ quy định biện pháp thi hành Luật Thi đua, khen thưởng và Nghị định số 98/2023/NĐ-CP ngày 31 tháng 12 năm 2023 của Chính phủ quy định chi tiết thi hành một số điều của Luật Thi đua, khen thưởng;
+k) Khoản 2 Điều 4 Thông tư số 02/2024/TT-BNV ngày 12 tháng 6 năm 2024 của Bộ trưởng Bộ Nội vụ quy định biện pháp thi hành Nghị định quy định chi tiết trình tự, thủ tục xét tặng, truy tặng “Huy chương Thanh niên xung phong vẻ vang” và việc khen thưởng tổng kết thành tích kháng chiến;
+l) Khoản 1, 2 Điều 5 Thông tư liên tịch số 02/2013/TTLT-BNV-BLĐTBXH-BTC-BYT ngày 09 tháng 7 năm 2013 của Bộ trưởng Bộ Nội vụ, Bộ Lao động - Thương binh và Xã hội, Bộ Tài chính, Bộ Y tế hướng dẫn quy trình, thủ tục, hồ sơ, mức hỗ trợ người đang trực tiếp tham gia hoạt động chữ thập đỏ bị tai nạn dẫn đến thiệt hại về sức khỏe;
+m) Khoản 1, 2 Mục III Thông tư liên tịch số 17/1999/TTLT-BLĐTBXH-BTC-BTCCBCP của Bộ trưởng Bộ Lao động - Thương binh và Xã hội, Bộ Tài chính, Trưởng Ban Tổ chức cán bộ Chính phủ hướng dẫn thi hành Nghị định số 23/1999/NĐ-CP ngày 15 tháng 4 năm 1999 của Chính phủ về chế độ đối với quân nhân, cán bộ đi chiến trường B, C, K trong thời kỳ chống Mỹ cứu nước không có thân nhân phải trực tiếp nuôi dưỡng và quân nhân, cán bộ được Đảng cử ở lại miền nam hoạt động sau Hiệp định Giơnevơ năm 1954;
+n) Điều 26 Thông tư số 05/2013/TT-BLĐTBXH ngày 15 tháng 5 năm 2013 của Bộ trưởng Bộ Lao động - Thương binh và Xã hội hướng dẫn về thủ tục lập hồ sơ, quản lý hồ sơ, thực hiện chế độ ưu đãi người có công với cách mạng và thân nhân.
+CHUYỂN TIẾP: Điều 19. Điều khoản chuyển tiếp và trách nhiệm thi hành
+1. Điều khoản chuyển tiếp
+a) Đối với các hồ sơ đã nộp trước ngày Thông tư này có hiệu lực, cơ quan tiếp nhận hồ sơ tiếp tục giải quyết theo các quy định hiện hành cho đến khi kết thúc thủ tục hành chính;
+b) Trường hợp điều kiện thực hiện nhiệm vụ quy định tại Điều 16 Thông tư này tại địa phương chưa bảo đảm được thì Bộ Nội vụ (Cục Việc làm) tiếp tục thực hiện trách nhiệm tiếp nhận, xử lý hồ sơ đăng ký kiểm tra chất lượng sản phẩm, hàng hóa nhập khẩu theo đề nghị của tổ chức, cá nhân sản xuất, kinh doanh, nhập khẩu sản phẩm, hàng hóa đến hết ngày 31 tháng 12 năm 2025.
+2. Trách nhiệm thi hành
+a) Ủy ban nhân dân các cấp có trách nhiệm chỉ đạo các cơ quan chức năng có liên quan kiểm tra, thực hiện Thông tư này;
+b) Trường hợp phát sinh vướng mắc trong quá trình thực hiện, các cơ quan, tổ chức, đơn vị, cá nhân liên quan có trách nhiệm phản ánh về Bộ Nội vụ để xem xét, hướng dẫn theo quy định của pháp luật./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc TW;
+- Văn phòng TW Đảng và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Hội đồng dân tộc và các Ủy ban của Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- Cục kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Công báo; Cổng Thông tin điện tử của Chính phủ; Cổng thông tin điện tử của Bộ Nội vụ;
+- Bộ Nội vụ: Bộ trưởng, các Thứ trưởng; các đơn vị thuộc, trực thuộc Bộ Nội vụ;
+- Lưu: VT, PC.
+BỘ TRƯỞNG
+(đã ký)
+Phạm Thị Thanh Trà
+1. Điều khoản chuyển tiếp
+a) Đối với các hồ sơ đã nộp trước </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4065,7 +4800,6 @@
           <t>2026-08-07 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4086,9 +4820,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159058</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4099,18 +4830,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>17/2024/TT-BGTVT khoản 2 Điều 4 quy định lại tiêu chuẩn thăng hạng I cho chuyên ngành thông tin an ninh hàng hải bằng các phương án lựa chọn khác (yếu tố 3 không đạt), không chuyển chỗ</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>38/2022/TT-BGTVT · hiệu lực 2023-03-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 7. Thông tin an ninh hàng hải hạng I - Mã số: V.12.47.01
+4. Tiêu chuẩn, điều kiện đăng ký dự thi hoặc xét thăng hạng lên chức danh nghề nghiệp Thông tin an ninh hàng hải hạng I Viên chức được đăng ký dự thi hoặc xét thăng hạng lên chức danh nghề nghiệp Thông tin an ninh hàng hải hạng I khi có đủ các tiêu chuẩn, điều kiện theo quy định tại Điều 32 Nghị định số 115/2020/NĐ-CP và các tiêu chuẩn, điều kiện sau:
+a) Có thời gian giữ chức danh nghề nghiệp Thông tin an ninh hàng hải hạng II hoặc tương đương từ đủ 06 năm trở lên. Trường hợp có thời gian tương đương thì phải có ít nhất 01 năm (đủ 12 tháng) giữ chức danh nghề nghiệp Thông tin an ninh hàng hải hạng II tính đến ngày hết thời hạn nộp hồ sơ đăng ký dự thi hoặc xét thăng hạng.
+b) Trong thời gian giữ hạng chức danh nghề nghiệp Thông tin an ninh hàng hải hạng II và tương đương đã tham gia xây dựng ít nhất 02 (hai) văn bản quy phạm pháp luật, đề tài, đề án, dự án, sáng kiến cấp bộ, cấp ban, cấp ngành hoặc cấp tỉnh mà cơ quan sử dụng viên chức được giao nghiên cứu, xây dựng đã được cấp có thẩm quyền ban hành hoặc nghiệm thu.</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 17/2024/TT-BGTVT · hiệu lực 2024-07-15
+a) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 7, khoản 4 Điều 8 Thông tư số 38/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành tìm kiếm cứu nạn hàng hải, thông tin an ninh hàng hải;
+b) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6 Thông tư số 39/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành cảng vụ đường thuỷ nội địa;
+c) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6, khoản 4 Điều 8 Thông tư số 40/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành cảng vụ hàng hải;
+d) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6 Thông tư số 41/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành quản lý dự án hàng hải;
+đ) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6 Thông tư số 43/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành quản lý dự án đường thuỷ;
+e) Điểm c khoản 2 Điều 1, điểm c khoản 3 Điều 1, điểm c khoản 4 Điều 1, điểm c khoản 5 Điều 1 Thông tư số 44/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 11/2020/TT-BGTVT ngày 21 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành cảng vụ hàng không;
+g) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6, khoản 4 Điều 7 Thông tư số 45/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành đăng kiểm;
+h) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6 Thông tư số 46/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành quản lý dự án đường bộ;
+i) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6, khoản 4 Điều 8 Thông tư số 47/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành kỹ thuật đường bộ, chuyên ngành kỹ thuật bến phà;
+k) Khoản 4 Điều 4, khoản 4 Điều 5, khoản 4 Điều 6 Thông tư số 49/2022/TT-BGTVT ngày 30 tháng 12 năm 2022 của Bộ trưởng Bộ Giao thông vận tải quy định mã số, tiêu chuẩn chức danh nghề nghiệp và xếp lương viên chức chuyên ngành quản lý dự án đường sắt.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4138,7 +4886,6 @@
           <t>2026-06-09 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4159,9 +4906,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=100624</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4172,18 +4916,48 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>14/2026/NĐ-CP bãi bỏ khoản 1 Điều 23 NĐ 23/2016 để cắt giảm điều kiện năng lực, không có quy định kế thừa</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>23/2016/NĐ-CP · hiệu lực 2016-05-27 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 23. Trách nhiệm đơn vị quản lý vận hành cơ sở hỏa táng
+1. Đơn vị quản lý vận hành cơ sở hỏa táng phải có các điều kiện về năng lực như sau:
+a) Có cán bộ quản lý vận hành có trình độ kỹ sư (hoặc tương đương) thuộc một trong các ngành hóa, vật lý, sinh học, công nghệ môi trường, điện;
+b) Có công nhân kỹ thuật ngành cơ điện bậc 03 trở lên để trực tiếp vận hành lò hỏa táng;
+c) Người lao động phải có hợp đồng lao động và đóng bảo hiểm theo quy định;
+d) Các trang thiết bị, phương tiện kỹ thuật phải đảm bảo yêu cầu về môi trường và an toàn lao động.</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 14/2026/NĐ-CP · hiệu lực 2026-01-15
+2. Bãi bỏ khoản 1 Điều 23 của Nghị định số 23/2016/NĐ-CP ngày 05 tháng 4 năm 2016 của Chính phủ về xây dựng, quản lý, sử dụng nghĩa trang và cơ sở hỏa táng.
+CHUYỂN TIẾP: Điều 4. Điều khoản chuyển tiếp
+Hồ sơ cấp, cấp lại Giấy phép kinh doanh vận tải đa phương thức quốc tế đã nộp tại cơ quan có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành thì việc giải quyết thủ tục hành chính tiếp tục được thực hiện theo quy định tại Nghị định số 87/2009/NĐ-CP ngày 19 tháng 10 năm 2009 của Chính phủ về vận tải đa phương thức (được sửa đổi, bổ sung bởi Nghị định số 144/2018/NĐ-CP ngày 16 tháng 10 năm 2018 của Chính phủ sửa đổi, bổ sung các Nghị định về vận tải đa phương thức).
+Điều 21. Điều khoản chuyển tiếp
+Hồ sơ đề nghị giải quyết thủ tục hành chính nộp trước thời điểm Nghị định này có hiệu lực thi hành thì thời hạn ra văn bản giải quyết thủ tục hành chính của cơ quan chuyên môn về xây dựng thực hiện theo quy định tại Nghị định số 06/2021/NĐ-CP ngày 26 tháng 01 năm 2021 của Chính phủ quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng (được sửa đổi, bổ sung bởi Nghị định số 35/2023/NĐ-CP ngày 20 tháng 6 năm 2023 và Nghị định số 175/2024/NĐ-CP ngày 30 tháng 12 năm 2024 của Chính phủ).
+Điều 25. Điều khoản chuyển tiếp
+Cá nhân đã nộp hồ sơ đề nghị chuyển đổi chứng chỉ hành nghề trước thời điểm Nghị định này có hiệu lực thi hành thì được xét cấp theo quy định tại Nghị định số 175/2024/NĐ-CP ngày 30 tháng 12 năm 2024 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng.
+Điều 46. Điều khoản chuyển tiếp
+Hồ sơ đề nghị giải quyết thủ tục hành chính đã nộp tại cơ quan có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành thì tiếp tục thực hiện theo quy định tại Nghị định số 58/2017/NĐ-CP ngày 10 tháng 5 năm 2017 của Chính phủ quy định chi tiết một số điều của Bộ luật Hàng hải Việt Nam về quản lý hoạt động hàng hải (được sửa đổi, bổ sung bởi Nghị định số 76/2021/NĐ-CP ngày 28 tháng 7 năm 2021; Nghị định số 69/2022/NĐ-CP ngày 23 tháng 9 năm 2022; Nghị định số 74/2023/NĐ-CP ngày 11 tháng 10 năm 2023; Nghị định số 34/2025/NĐ-CP ngày 25 tháng 01 năm 2025 của Chính phủ).
+Điều 65. Điều khoản chuyển tiếp
+Hồ sơ cấp hoặc cấp lại Giấy chứng nhận cơ sở đủ Điều kiện kinh doanh dịch vụ đào tạo thuyền viên, người lái phương tiện thủy nội địa đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì việc giải quyết thủ tục hành chính tiếp tục được thực hiện theo quy định của Nghị định số 78/2016/NĐ-CP .
+Điều 89. Điều khoản chuyển tiếp
+Hồ sơ đưa cơ sở phá dỡ tàu biển vào hoạt động đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì việc giải quyết thủ tục hành chính tiếp tục được thực hiện theo quy định của Nghị định số 82/2019/NĐ-CP .
+Điều 113. Điều khoản chuyển tiếp
+Hồ sơ cấp, cấp lại, gia hạn chứng chỉ hành nghề kiến trúc và công nhận, chuyển đổi chứng chỉ hành nghề kiến trúc của người nước ngoài hành nghề kiến trúc ở Việt Nam đã nộp tại cơ quan có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành thì thực hiện theo quy định của Nghị định số 85/2020/NĐ-CP ngày 17 tháng 7 năm 2020 của Chính phủ quy định chi tiết một số điều của Luật Kiến trúc .”.
+Điều 130. Điều khoản chuyển tiếp
+1. Giấy phép nhân viên vận hành thiết bị hàng không, phương tiện hoạt động tại khu vực hạn chế của cảng hàng không, sân bay đã cấp hết hiệu lực kể từ ngày Nghị định này có hiệu lực thi hành.
+2. Cơ quan có thẩm quyền dừng tiếp nhận hồ sơ cấp Giấy phép nhân viên vận hành thiết bị hàng không, phương tiện hoạt động tại khu vực hạn chế của cảng hàng không, sân bay kể từ ngày Nghị định này có hiệu lực thi hành. Trường hợp đã tiếp nhận hồ sơ nhưng chưa cấp Giấy phép, cơ quan có thẩm quyền hoàn trả các nghĩa vụ phí, lệ phí mà người nộp hồ sơ đã thực hiện theo quy định của pháp luật.
+2. Hồ sơ giải quyết thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì tiếp tục được giải quyết theo quy định tại Nghị định số 05/2021/NĐ-CP ngày 25 tháng 01 năm 2021 của Chính phủ về quản lý, khai thác cảng hàng không, sân bay (đã được sửa đổi, bổ sung bởi Nghị định số 20/2024/NĐ-CP ngày 23 tháng 02 năm 2024 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 05/2021/NĐ-CP ngày 25 tháng 02 năm 2021 của Chính phủ về quản lý, khai thác cảng hàng không, sân bay và Nghị định số 64/2022/NĐ-CP ngày 15 tháng 9 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định quy định liên quan đến hoạt động kinh doanh trong lĩnh vực hàng không dân dụng).
+Điều 136. Điều khoản chuyển tiếp
+Giấy phép cung cấp dịch vụ hàng không loại hình: dịch vụ khai thác khu bay, dịch vụ sửa chữa, bảo dưỡng phương tiện, trang thiết bị hàng không, dịch vụ kỹ thuật hàng không hết hiệu lực thi hành kể từ ngày Nghị định này có hiệu lực thi hành.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4236,9 +5010,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119167</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4254,17 +5025,24 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 74/2022/TT-BTC khoản 3 Điều 3 "Tổ chức thu phí kê khai, nộp tiền phí thu được vào ngân sách nhà nước theo tháng …, quyết toán năm"; cùng Bộ Tài chính, cùng thông tư bãi bỏ khoản 2 Điều 5 TT 224/2016 (như ví dụ TT 225/2016 ở §4 hướng dẫn)</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>224/2016/TT-BTC · hiệu lực 2017-01-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 5. Kê khai, nộp phí, lệ phí
+2. Tổ chức thu phí, lệ phí thực hiện kê khai, nộp số tiền phí, lệ phí thu được theo tháng, quyết toán năm theo hướng dẫn tại khoản 3 Điều 19, khoản 2 Điều 26 Thông tư số 156/2013/TT-BTC ngày 06 tháng 11 năm 2013 của Bộ trưởng Bộ Tài chính hướng dẫn thi hành một số điều của Luật quản lý thuế; Luật sửa đổi, bổ sung một số điều của Luật quản lý thuế và Nghị định số 83/2013/NĐ-CP ngày 22 tháng 7 năm 2013 của Chính phủ.</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 74/2022/TT-BTC · hiệu lực 2022-12-22
+54. Bãi bỏ khoản 2 Điều 5 Thông tư số 224/2016/TT-BTC ngày 10 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí thẩm định tiêu chuẩn, điều kiện hành nghề, hoạt động quản lý, thanh lý tài sản; lệ phí cấp chứng chỉ hành nghề quản tài viên.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4292,7 +5070,6 @@
           <t>2026-01-23 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4313,9 +5090,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143024</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4331,17 +5105,33 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 282/2025/NĐ-CP điểm d khoản 3 Điều 29 "Truy cập trái phép, trộm cắp, phá hoại dữ liệu lý lịch tư pháp điện tử", cùng khung 7.000.000–10.000.000 đồng; cùng Chính phủ, cùng nghị định bãi bỏ Điều 47 NĐ 82/2020</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>82/2020/NĐ-CP · hiệu lực 2020-09-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 47. Hành vi vi phạm quy định về sử dụng và khai thác cơ sở dữ liệu lý lịch tư pháp; yêu cầu cấp phiếu lý lịch tư pháp; sử dụng phiếu lý lịch tư pháp
+3. Phạt tiền từ 7.000.000 đồng đến 10.000.000 đồng đối với một trong các hành vi sau:
+a) Sử dụng phiếu lý lịch tư pháp của người khác trái pháp luật, xâm phạm đời tư của cá nhân;
+b) Sử dụng giấy tờ của người khác để yêu cầu cấp phiếu lý lịch tư pháp trái pháp luật;
+c) Khai thác, sử dụng trái phép, làm sai lệch, hủy hoại hồ sơ lý lịch tư pháp bằng giấy;
+d) Truy cập trái phép, trộm cắp, phá hoại dữ liệu lý lịch tư pháp điện tử;
+đ) Phát tán chương trình tin học gây hại cho mạng máy tính, hệ thống thông tin dữ liệu lý lịch tư pháp điện tử.</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 282/2025/NĐ-CP · hiệu lực 2025-12-15
+5. Bãi bỏ Điều 47 Nghị định số 82/2020/NĐ-CP ngày 15 tháng 7 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực bổ trợ tư pháp; hành chính tư pháp; hôn nhân và gia đình; thi hành án dân sự; phá sản doanh nghiệp, hợp tác xã (đã được sửa đổi, bổ sung tại Nghị định số 117/2024/NĐ-CP ngày 18 tháng 9 năm 2024 của Chính phủ).
+CHUYỂN TIẾP: Điều 70. Điều khoản chuyển tiếp
+1. Đối với hành vi vi phạm hành chính trong lĩnh vực an ninh, trật tự, an toàn xã hội; phòng, chống tệ nạn xã hội; phòng, chống bạo lực gia đình; hàng không dân dụng xảy ra và kết thúc trước thời điểm Nghị định này có hiệu lực mà bị phát hiện hoặc đang xem xét, giải quyết khi Nghị định này đã có hiệu lực thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính và các văn bản quy phạm pháp luật có liên quan có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý.
+2. Đối với hành vi vi phạm hành chính trong lĩnh vực an ninh, trật tự, an toàn xã hội; phòng, chống tệ nạn xã hội; phòng, chống bạo lực gia đình; hàng không dân dụng xảy ra trước thời điểm Nghị định này có hiệu lực nhưng vẫn đang diễn ra khi Nghị định này đã có hiệu lực thì áp dụng quy định của Nghị định này để xử lý.
+3. Đối với quyết định xử phạt vi phạm hành chính đã được ban hành hoặc đã được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành, mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Luật Xử lý vi phạm hành chính, Nghị định của Chính phủ về xử phạt vi phạm hành chính và các văn bản quy phạm pháp luật có liên quan có hiệu lực tại thời điểm ban hành quyết định xử phạt vi phạm hành chính để xử lý.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4369,7 +5159,6 @@
           <t>2021-09-03 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4390,9 +5179,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26637</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4403,18 +5189,24 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>150/2018/NĐ-CP bãi bỏ Điều 18 NĐ 47/2011 để cắt giảm thủ tục, không có quy định kế thừa</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>47/2011/NĐ-CP · hiệu lực 2011-08-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Nhập khẩu tem bưu chính
+1. Tổ chức, cá nhân nhập khẩu tem bưu chính với số lượng từ 500 con trở lên và không thuộc danh mục các loại tem bưu chính quy định tại khoản 3 Điều 37 Luật bưu chính phải có giấy phép nhập khẩu tem bưu chính do Bộ Thông tin và Truyền thông cấp.</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 150/2018/NĐ-CP · hiệu lực 2018-12-24
+3. Bãi bỏ Điều 18.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4467,9 +5259,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=4ca06a80-8c80-11f1-941a-e377a12e0bfa</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4480,14 +5269,37 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>136/2024/QH15 · hiệu lực 2025-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Cơ cấu tổ chức, chế độ làm việc, nhiệm vụ, quyền hạn của Ủy ban nhân dân phường; quản lý cán bộ, công chức phường, xã
+3. Ủy ban nhân dân phường có các nhiệm vụ, quyền hạn sau đây:
+a) Thực hiện nhiệm vụ, quyền hạn của đơn vị dự toán ngân sách trực thuộc Ủy ban nhân dân quận theo quy định của Luật Ngân sách nhà nước;
+b) Đề xuất chủ trương đầu tư chương trình, dự án đầu tư công sử dụng vốn ngân sách nhà nước với Ủy ban nhân dân quận để trình cấp có thẩm quyền quyết định chủ trương đầu tư; tham gia ý kiến về chủ trương đầu tư dự án thuộc thẩm quyền quyết định của cơ quan, cá nhân có thẩm quyền mà Luật Đầu tư công quy định phải có sự tham gia ý kiến của Hội đồng nhân dân cấp xã; tổ chức thực hiện chương trình, dự án đầu tư công theo phân cấp quản lý;
+c) Đề xuất, phối hợp với cơ quan có thẩm quyền thực hiện nhiệm vụ về quốc phòng, an ninh, biện pháp bảo đảm trật tự, an toàn xã hội, đấu tranh phòng, chống tội phạm và các hành vi vi phạm pháp luật khác trên địa bàn theo phân cấp quản lý;
+d) Phối hợp với Ủy ban Mặt trận Tổ quốc Việt Nam cùng cấp thành lập Tổ bầu cử đại biểu Quốc hội, Tổ bầu cử đại biểu Hội đồng nhân dân;
+đ) Thực hiện nhiệm vụ, quyền hạn do cơ quan nhà nước cấp trên phân cấp, ủy quyền;
+e) Thực hiện nhiệm vụ về tổ chức và bảo đảm việc thi hành Hiến pháp, pháp luật, các văn bản của cơ quan nhà nước cấp trên tại địa bàn phường;
+g) Quyết định theo thẩm quyền đối với nhiệm vụ mà theo quy định của pháp luật phải trình Hội đồng nhân dân phường thông qua trước khi quyết định; trình Ủy ban nhân dân quận quyết định đối với nhiệm vụ thuộc thẩm quyền của Hội đồng nhân dân phường quyết định theo quy định của pháp luật;
+h) Không có thẩm quyền ban hành văn bản quy phạm pháp luật;
+i) Thực hiện nhiệm vụ, quyền hạn khác theo quy định của pháp luật mà không trái với quy định của Nghị quyết này.</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 72/2025/QH15 · hiệu lực 2025-06-16
+c) Bãi bỏ Điều 7 và Điều 8 của Nghị quyết số 136/2024/QH15 ngày 26 tháng 6 năm 2024 của Quốc hội về tổ chức chính quyền đô thị và thí điểm một số cơ chế, chính sách đặc thù phát triển thành phố Đà Nẵng;
+CHUYỂN TIẾP: Điều 54. Quy định chuyển tiếp
+1. Chậm nhất là ngày 01 tháng 3 năm 2027, các văn bản quy phạm pháp luật có nội dung quy định về tổ chức, nhiệm vụ, quyền hạn và quy định khác có liên quan của chính quyền địa phương các cấp phải được sửa đổi, bổ sung để bảo đảm phù hợp với tổ chức đơn vị hành chính, các nguyên tắc và các nhiệm vụ, quyền hạn của chính quyền địa phương các cấp quy định tại Luật này.
+Kể từ ngày Luật này có hiệu lực thi hành, để kịp thời thực hiện tổ chức chính quyền địa phương cấp tỉnh, cấp xã theo quy định tại Luật này và đẩy mạnh phân quyền, phân cấp cho chính quyền địa phương trong một số lĩnh vực ưu tiên, cấp bách, giao Chính phủ ban hành văn bản quy phạm pháp luật thuộc thẩm quyền phân định lại nhiệm vụ, quyền hạn của chính quyền địa phương và điều chỉnh các quy định khác có liên quan đến việc thực hiện nhiệm vụ, quyền hạn của chính quyền địa phương để thống nhất áp dụng trong thời gian chưa sửa đổi, bổ sung các luật, pháp lệnh, nghị quyết của Quốc hội, Ủy ban Thường vụ Quốc hội và định kỳ báo cáo Ủy ban Thường vụ Quốc hội; trường hợp liên quan đến luật, nghị quyết của Quốc hội thì báo cáo Quốc hội tại kỳ họp gần nhất.
+2. Trong thời gian cơ quan có thẩm quyền chưa ban hành văn bản quy phạm pháp luật để điều chỉnh nhiệm vụ, quyền hạn của chính quyền địa phương theo quy định tại khoản 1 Điều này thì các quy định của pháp luật hiện hành liên quan đến trách nhiệm trong thực hiện nhiệm vụ, quyền hạn của chính quyền địa phương được tiếp tục thực hiện cho đến khi cơ quan có thẩm quyền ban hành văn bản quy phạm pháp luật sửa đổi, bổ sung hoặc thay thế.
+3. Kể từ ngày 01 tháng 7 năm 2025, Ủy ban nhân dân cấp tỉnh kế thừa các thỏa thuận quốc tế do Ủy ban nhân dân cấp huyện ký kết trước ngày 01 tháng 7 năm 2025; chịu trách nhiệm thực hiện việc điều chỉnh, cập nhật tên gọi mới của đơn vị hành chính trong các thỏa thuận quốc tế do Ủy ban nhân dân cấp huyện ký kết trước ngày 01 tháng 7 năm 2025.
+4. Khi chính quyền địa phương cấp huyện kết thúc hoạt động theo quy định tại khoản 3 Điều 51 của Luật này thì Thường trực Hội đồng nhân dân cấp tỉnh có trách nhiệm xác định các đại biểu Hội đồng nhân dân cấp huyện nhiệm kỳ 2021 - 2026 được bầu hoặc đang thực hiện nhiệm vụ đại biểu ở phần địa giới hành chính thuộc đơn vị hành chính cấp xã hình thành sau sắp xếp hoặc được cơ quan có thẩm quyền điều động, bố trí công tác tại các cơ quan, tổ chức, đơn vị ở đơn vị hành chính cấp xã đó để làm đại biểu của Hội đồng nhân dân nhiệm kỳ 2021 - 2026 của đơn vị hành chính cấp xã tương ứng, trừ trường hợp quy định tại khoản 5 Điều này.
+5. Đại biểu Hội đồng nhân dân cấp huyện, cấp xã ở các đơn vị hành chính thực hiện sắp xếp để hình thành đặc khu thuộc trường hợp quy định tại khoản 1 Điều 28 của Luật này kết thúc hoạt động kể từ ngày 01 tháng 7 năm 2025.
+6. Kể từ ngày Luật này có hiệu lực thi hành, số lượng Phó Chủ tịch Hội đồng nhân dân, Phó Chủ tịch Ủy ban nhân dân, cấp phó của người đứng đầu các cơ quan, đơn vị trực thuộc Hội đồng nhân dân, Ủy ban nhân dân tại các đơn vị hành chính cấp tỉnh hình thành sau sắp xếp có thể nhiều hơn số lượng so với quy định. Chậm nhất là 05 năm kể từ ngày Luật này có hiệu lực thi hành, số lượng và việc bố trí lãnh đạo, quản lý ở đơn vị hành chính sau sắp xếp được thực hiện theo quy định.
+7. Chậm nhất là ngày 30 tháng 6 năm 2025, Thường trực Hội đồng nhân dân, các cơ quan thuộc Hội đồng nhân dân, Ủy ban nhân dân, Chủ tịch Ủy ban nhân dân, các cơ quan chuyên môn thuộc Ủy ban nhân dân cấp huyện phải hoàn thành việc bàn giao công việc, hồ sơ, tài liệu, tài chính, ngân sách, trụ sở, tài sản, cơ sở vật chất khác có liên quan cho các cơ quan, tổ chức, đơn vị có thẩm quyền bảo đảm hoạt động bình thường, liên tục, thông suốt của các cơ quan, không để gián đoạn công việc, không để chồng chéo, trùng lặp hoặc bỏ sót nhiệm vụ, lĩnh vực, địa bàn, không làm ảnh hưởng đến nhiệm vụ phát triển kinh tế - xã hội, hoạt động bình thường của xã hội, người dân, doanh nghiệp, bảo đảm quốc phòng, an ninh, trật tự, an toàn xã hội trên địa bàn [...cắt bớt]</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4540,9 +5352,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4553,14 +5362,36 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>36/2020/TT-BGTVT · hiệu lực 2021-02-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Sửa đổi, bổ sung Điều 64 của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ như sau:
+1. Báo cáo tình hình hoạt động vận tải của đơn vị
+a) Tên báo cáo: Báo cáo kết quả hoạt động của bến xe.
+b) Nội dung yêu cầu báo cáo: Kết quả hoạt động của bến xe khách, bến xe hàng.
+c) Đối tượng thực hiện báo cáo: Đơn vị kinh doanh vận tải, bến xe khách.
+d) Cơ quan nhận báo cáo: Sở Giao thông vận tải và Sở Giao thông vận tải - Xây dựng.
+đ) Phương thức gửi, nhận báo cáo: Báo cáo được thể hiện dưới hình thức văn bản giấy hoặc văn bản điện tử. Báo cáo được gửi đến cơ quan nhận báo cáo bằng một trong các phương thức sau: gửi trực tiếp, qua dịch vụ bưu chính, fax, qua hệ thống thư điện tử, hoặc các phương thức khác theo quy định của pháp luật.
+e) Tần suất thực hiện báo cáo: Định kỳ hàng tháng.
+g) Thời hạn gửi báo cáo: Trước ngày 20 của tháng tiếp theo kỳ báo cáo
+h) Thời gian chốt số liệu báo cáo: Từ ngày 01 đến ngày cuối cùng của tháng báo cáo.
+i) Mẫu đề cương báo cáo: Theo quy định tại Phụ lục 20 của Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 36/2024/TT-BGTVT · hiệu lực 2025-01-01
+b) Điều 8 Thông tư số 36/2020/TT-BGTVT ngày 24 tháng 12 năm 2020 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của các Thông tư quy định về chế độ báo cáo định kỳ trong lĩnh vực vận tải đường bộ;
+c) Thông tư số 02/2021/TT-BGTVT ngày 04 tháng 2 năm 2021 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ;
+d) Thông tư số 17/2022/TT-BGTVT ngày 15 tháng 7 năm 2022 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ;
+đ) Điều 17 Thông tư số 05/2023/TT-BGTVT ngày 27 tháng 4 năm 2023 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của các Thông tư liên quan đến lĩnh vực vận tải đường bộ, dịch vụ hỗ trợ vận tải đường bộ, phương tiện và người lái;
+e) Thông tư số 18/2024/TT-BGTVT ngày 31 tháng 5 năm 2024 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ./.
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Nguyễn Duy Lâm</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4588,7 +5419,6 @@
           <t>2025-09-06 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4609,9 +5439,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4627,17 +5454,41 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 36/2024/TT-BGTVT điểm h khoản 1 Điều 46 "Thời gian chốt số liệu báo cáo: từ ngày 01 đến ngày cuối cùng của tháng báo cáo" (báo cáo tình hình hoạt động vận tải của đơn vị kinh doanh vận tải); cùng Bộ GTVT, cùng thông tư bãi bỏ Điều 8 TT 36/2020</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>36/2020/TT-BGTVT · hiệu lực 2021-02-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Sửa đổi, bổ sung Điều 64 của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ như sau:
+1. Báo cáo tình hình hoạt động vận tải của đơn vị
+a) Tên báo cáo: Báo cáo kết quả hoạt động của bến xe.
+b) Nội dung yêu cầu báo cáo: Kết quả hoạt động của bến xe khách, bến xe hàng.
+c) Đối tượng thực hiện báo cáo: Đơn vị kinh doanh vận tải, bến xe khách.
+d) Cơ quan nhận báo cáo: Sở Giao thông vận tải và Sở Giao thông vận tải - Xây dựng.
+đ) Phương thức gửi, nhận báo cáo: Báo cáo được thể hiện dưới hình thức văn bản giấy hoặc văn bản điện tử. Báo cáo được gửi đến cơ quan nhận báo cáo bằng một trong các phương thức sau: gửi trực tiếp, qua dịch vụ bưu chính, fax, qua hệ thống thư điện tử, hoặc các phương thức khác theo quy định của pháp luật.
+e) Tần suất thực hiện báo cáo: Định kỳ hàng tháng.
+g) Thời hạn gửi báo cáo: Trước ngày 20 của tháng tiếp theo kỳ báo cáo
+h) Thời gian chốt số liệu báo cáo: Từ ngày 01 đến ngày cuối cùng của tháng báo cáo.
+i) Mẫu đề cương báo cáo: Theo quy định tại Phụ lục 20 của Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 36/2024/TT-BGTVT · hiệu lực 2025-01-01
+b) Điều 8 Thông tư số 36/2020/TT-BGTVT ngày 24 tháng 12 năm 2020 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của các Thông tư quy định về chế độ báo cáo định kỳ trong lĩnh vực vận tải đường bộ;
+c) Thông tư số 02/2021/TT-BGTVT ngày 04 tháng 2 năm 2021 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ;
+d) Thông tư số 17/2022/TT-BGTVT ngày 15 tháng 7 năm 2022 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ;
+đ) Điều 17 Thông tư số 05/2023/TT-BGTVT ngày 27 tháng 4 năm 2023 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của các Thông tư liên quan đến lĩnh vực vận tải đường bộ, dịch vụ hỗ trợ vận tải đường bộ, phương tiện và người lái;
+e) Thông tư số 18/2024/TT-BGTVT ngày 31 tháng 5 năm 2024 của Bộ trưởng Bộ Giao thông vận tải sửa đổi, bổ sung một số điều của Thông tư số 12/2020/TT-BGTVT ngày 29 tháng 5 năm 2020 của Bộ trưởng Bộ Giao thông vận tải quy định về tổ chức, quản lý hoạt động vận tải bằng xe ô tô và dịch vụ hỗ trợ vận tải đường bộ./.
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Nguyễn Duy Lâm</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4665,7 +5516,6 @@
           <t>2021-01-08 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4686,9 +5536,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27508</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4699,18 +5546,53 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Điều 3 NĐ 151/2018/NĐ-CP bãi bỏ đúng khoản 2 Điều 6 NĐ 17/2012 để cắt giảm điều kiện kinh doanh, không có quy định kế thừa</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>17/2012/NĐ-CP · hiệu lực 2012-05-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 6. Thành viên là tổ chức của công ty trách nhiệm hữu hạn hai thành viên trở lên
+2. Thành viên là tổ chức phải cử một người làm đại diện cho tổ chức vào Hội đồng thành viên. Người đại diện của thành viên là tổ chức phải là kiểm toán viên và phải đăng ký hành nghề tại doanh nghiệp kiểm toán mà tổ chức tham gia góp vốn.</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 151/2018/NĐ-CP · hiệu lực 2018-11-07
+1. Bãi bỏ khoản 2 Điều 6.
+CHUYỂN TIẾP: Điều 15. Hiệu lực thi hành và điều khoản chuyển tiếp
+1. Nghị định này có hiệu lực thi hành từ ngày ký ban hành.
+2. Tổ chức, cá nhân đã nộp hồ sơ cho cơ quan quản lý nhà nước có thẩm quyền để được cấp Giấy chứng nhận đủ điều kiện kinh doanh trong lĩnh vực kế toán, kiểm toán, thẩm định giá, xổ số, trò chơi điện tử có thưởng dành cho người nước ngoài, casino, đặt cược, dịch vụ xếp hạng tín nhiệm, dịch vụ quản lý quỹ hưu trí tự nguyện; Giấy phép thành lập và hoạt động trong lĩnh vực kinh doanh bảo hiểm, kinh doanh chứng khoán; Giấy chứng nhận đăng ký hoạt động văn phòng đại diện tổ chức kinh doanh chứng khoán của tổ chức kinh doanh chứng khoán nước ngoài; chấp thuận công ty chứng khoán được thực hiện giao dịch ký quỹ, giao dịch trong ngày; chấp thuận cho doanh nghiệp kiểm toán được kiểm toán cho đơn vị có lợi ích công chúng trước ngày Nghị định này có hiệu lực thi hành mà chưa được cơ quan quản lý nhà nước cấp giấy hoặc chấp thuận thì được áp dụng các điều kiện đầu tư, kinh doanh quy định tại Nghị định này.
+3. Các Bộ trưởng, Thủ trưởng cơ quan ngang bộ, Thủ trưởng cơ quan thuộc Chính phủ, Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương chịu trách nhiệm hướng dẫn và thi hành Nghị định này./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, KTTH (2). XH
+TM. CHÍNH PHỦ
+THỦ TƯỚNG
+(đã ký)
+Nguyễn Xuân Phúc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4738,7 +5620,6 @@
           <t>2021-05-28 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4759,9 +5640,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27508</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4772,18 +5650,60 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Điều 3 NĐ 151/2018/NĐ-CP bãi bỏ đúng điểm đ khoản 1 Điều 11 NĐ 17/2012, không có quy định kế thừa</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>17/2012/NĐ-CP · hiệu lực 2012-05-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Điều kiện cung cấp dịch vụ kiểm toán qua biên giới
+1. Doanh nghiệp kiểm toán nước ngoài có đủ các điều kiện sau đây được đăng ký cung cấp dịch vụ kiểm toán qua biên giới:
+a) Được phép cung cấp dịch vụ kiểm toán độc lập theo quy định của pháp luật của nước nơi doanh nghiệp kiểm toán nước ngoài đặt trụ sở chính;
+b) Có văn bản của cơ quan quản lý hành nghề kiểm toán (cơ quan quản lý nhà nước về kiểm toán độc lập hoặc tổ chức nghề nghiệp) nơi doanh nghiệp đóng trụ sở chính cho phép cung cấp dịch vụ qua biên giới tại Việt Nam và xác nhận không vi phạm các quy định về hoạt động kiểm toán độc lập và quy định pháp luật khác của nước ngoài trong vòng 3 năm liền kề năm đề nghị cấp giấy chứng nhận được cung cấp dịch vụ kiểm toán qua biên giới;
+c) Có ít nhất 5 (năm) kiểm toán viên được Bộ Tài chính Việt Nam cấp giấy chứng nhận đăng ký hành nghề kiểm toán, trong đó có người đại diện theo pháp luật;
+d) Có vốn chủ sở hữu trên bảng cân đối kế toán tương đương 500.000 (năm trăm nghìn) đô la Mỹ vào cuối năm tài chính trước năm cung cấp dịch vụ kiểm toán qua biên giới tại Việt Nam;
+đ) Có mua bảo hiểm trách nhiệm nghề nghiệp cho các kiểm toán viên hành nghề tại Việt Nam;
+e) Ký quỹ bắt buộc số tiền tương đương vốn pháp định quy định tại Khoản 1 Điều 5 Nghị định này tại một ngân hàng thương mại hoạt động hợp pháp tại Việt Nam và có thư bảo lãnh thanh toán của ngân hàng này cam kết thanh toán trong trường hợp trách nhiệm của các hợp đồng kiểm toán cung cấp dịch vụ qua biên giới tại Việt Nam vượt quá mức ký quỹ bắt buộc;
+g) Thực hiện đầy đủ nghĩa vụ báo cáo và các nghĩa vụ khác quy định tại Điều 13 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 151/2018/NĐ-CP · hiệu lực 2018-11-07
+2. Bãi bỏ các điểm b, đ, g khoản 1 Điều 11.
+CHUYỂN TIẾP: Điều 15. Hiệu lực thi hành và điều khoản chuyển tiếp
+1. Nghị định này có hiệu lực thi hành từ ngày ký ban hành.
+2. Tổ chức, cá nhân đã nộp hồ sơ cho cơ quan quản lý nhà nước có thẩm quyền để được cấp Giấy chứng nhận đủ điều kiện kinh doanh trong lĩnh vực kế toán, kiểm toán, thẩm định giá, xổ số, trò chơi điện tử có thưởng dành cho người nước ngoài, casino, đặt cược, dịch vụ xếp hạng tín nhiệm, dịch vụ quản lý quỹ hưu trí tự nguyện; Giấy phép thành lập và hoạt động trong lĩnh vực kinh doanh bảo hiểm, kinh doanh chứng khoán; Giấy chứng nhận đăng ký hoạt động văn phòng đại diện tổ chức kinh doanh chứng khoán của tổ chức kinh doanh chứng khoán nước ngoài; chấp thuận công ty chứng khoán được thực hiện giao dịch ký quỹ, giao dịch trong ngày; chấp thuận cho doanh nghiệp kiểm toán được kiểm toán cho đơn vị có lợi ích công chúng trước ngày Nghị định này có hiệu lực thi hành mà chưa được cơ quan quản lý nhà nước cấp giấy hoặc chấp thuận thì được áp dụng các điều kiện đầu tư, kinh doanh quy định tại Nghị định này.
+3. Các Bộ trưởng, Thủ trưởng cơ quan ngang bộ, Thủ trưởng cơ quan thuộc Chính phủ, Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương chịu trách nhiệm hướng dẫn và thi hành Nghị định này./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, KTTH (2). XH
+TM. CHÍNH PHỦ
+THỦ TƯỚNG
+(đã ký)
+Nguyễn Xuân Phúc</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4811,7 +5731,6 @@
           <t>2026-07-06 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4832,9 +5751,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27508</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4850,17 +5766,23 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>Khoản 4 Điều 15 NĐ 17/2012/NĐ-CP không bị bãi bỏ ngày 07/11/2018: Điều 3 NĐ 151/2018/NĐ-CP chỉ bãi bỏ khoản 2 Điều 6 và điểm b, đ, g khoản 1 Điều 11 (cùng lỗi với dòng pilot T6 #6). Văn bản tác động của event không có trong kho thô</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>17/2012/NĐ-CP · hiệu lực 2012-05-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 15. Đơn vị được kiểm toán
+4. Các doanh nghiệp, tổ chức thuộc đối tượng phải kiểm toán báo cáo tài chính hàng năm quy định tại Khoản 1 và Khoản 2 Điều này nếu theo quy định của pháp luật phải lập báo cáo tài chính hợp nhất hoặc báo cáo tài chính tổng hợp thì phải thực hiện kiểm toán báo cáo tài chính hợp nhất hoặc báo cáo tài chính tổng hợp.</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>(không có văn bản tác động)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4888,7 +5810,6 @@
           <t>2026-03-16 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -4909,9 +5830,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167525</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4922,18 +5840,56 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>26/2026/NĐ-CP bãi bỏ Điều 15 NĐ 33/2024, không thấy quy định sổ theo dõi mua bán hóa chất Bảng trong nghị định này</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>33/2024/NĐ-CP · hiệu lực 2024-05-19 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 15. Trách nhiệm của tổ chức, cá nhân được cấp Giấy phép sản xuất, kinh doanh hóa chất Bảng
+3. Phải lập sổ theo dõi riêng việc mua bán hóa chất Bảng. Sổ theo dõi có các nội dung: Tên hóa chất Bảng, hàm lượng, khối lượng xuất khẩu, nhập khẩu, mua, bán, tồn kho; tên khách hàng gồm các thông tin như địa chỉ trụ sở chính, địa chỉ kinh doanh, số điện thoại, mục đích mua bán hóa chất Bảng.</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 26/2026/NĐ-CP · hiệu lực 2026-01-17
+4. Bãi bỏ Điều 8, 9 của Nghị định số 17/2020/NĐ-CP ngày 05 tháng 02 năm 2020 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định liên quan đến điều kiện đầu tư kinh doanh thuộc lĩnh vực quản lý nhà nước của Bộ Công Thương; điểm a khoản 14 Điều 4 và các Điều 10, 11, 12, 13, 14, 15, 17, 18, 19, 20 của Nghị định số 33/2024/NĐ-CP ngày 27 tháng 3 năm 2024 của Chính phủ quy định việc thực hiện Công ước cấm phát triển, sản xuất, tàng trữ, sử dụng và phá hủy vũ khí hóa học; các Điều 6, 7, 8, 9 của Nghị định 146/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ quy định về phân quyền, phân cấp trong lĩnh vực công nghiệp và thương mại.
+5. Các Bộ trưởng, Thủ trưởng cơ quan ngang bộ, Thủ trưởng cơ quan thuộc Chính phủ, Chủ tịch Ủy ban nhân dân các tỉnh, thành phố trực thuộc trung ương chịu trách nhiệm thi hành Nghị định này.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các tổ chức chính trị - xã hội;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, CN (2).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Bùi Thanh Sơn
+CHUYỂN TIẾP: Điều 30. Điều khoản chuyển tiếp
+1. Tổ chức, cá nhân đã được cơ quan có thẩm quyền cấp Giấy phép sản xuất, kinh doanh, xuất khẩu, nhập khẩu hóa chất Bảng, tiền chất công nghiệp, hóa chất hạn chế sản xuất kinh doanh trong lĩnh vực công nghiệp trước ngày Nghị định này có hiệu lực thi hành được tiếp tục hoạt động theo Giấy phép đã được cấp đến khi hết thời hạn của Giấy phép.
+2. Tổ chức, cá nhân đã được cơ quan có thẩm quyền cấp Giấy chứng nhận đủ điều kiện sản xuất, kinh doanh hóa chất sản xuất, kinh doanh có điều kiện trong lĩnh vực công nghiệp trước ngày Nghị định này có hiệu lực thi hành được tiếp tục hoạt động theo Giấy chứng nhận đã được cấp đến hết ngày 31 tháng 12 năm 2027.
+3. Đối với việc sản xuất, kinh doanh hóa chất thuộc Danh mục hóa chất cần kiểm soát đặc biệt được ban hành tại Nghị định số 24/2026/NĐ-CP ngày 17 tháng 01 năm 2026 của Chính phủ quy định các danh mục hóa chất thuộc phạm vi điều chỉnh của Luật Hóa chất mà không thuộc Danh mục hóa chất hạn chế sản xuất, kinh doanh và Danh mục tiền chất công nghiệp được ban hành theo Nghị định số 113/2017/NĐ-CP ngày 09 tháng 10 năm 2017 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Hóa chất và Nghị định số 82/2022/NĐ-CP ngày 18 tháng 10 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 113/2017/NĐ-CP ngày 09 tháng 10 năm 2017 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Hóa chất và Danh mục hóa chất Bảng được ban hành tại Nghị định số 33/2024/NĐ-CP ngày 27 tháng 3 năm 2024 của Chính phủ quy định việc thực hiện Công ước cấm phát triển, sản xuất, tàng trữ, sử dụng và phá hủy vũ khí hóa học thì phải đáp ứng quy định của Nghị định này trước ngày 31 tháng 12 năm 2026.
+4. Đối với việc xuất khẩu, nhập khẩu hóa chất thuộc Danh mục hóa chất cần kiểm soát đặc biệt được ban hành theo Nghị định số 24/2026/NĐ-CP ngày 17 tháng 01 năm 2026 của Chính phủ quy định các danh mục hóa chất thuộc phạm vi điều chỉnh của Luật Hóa chất mà không thuộc Danh mục hóa chất hạn chế sản xuất, kinh doanh và Danh mục tiền chất công nghiệp được ban hành tại Nghị định số 113/2017/NĐ-CP ngày 09 tháng 10 năm 2017 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Hóa chất và Nghị định số 82/2022/NĐ-CP ngày 18 tháng 10 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 113/2017/NĐ-CP ngày 09 tháng 10 năm 2017 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Hóa chất và Danh mục hóa chất Bảng được ban hành tại Nghị định số 33/2024/NĐ-CP ngày 27 tháng 3 năm 2024 của Chính phủ quy định việc thực hiện Công ước cấm phát triển, sản xuất, tàng trữ, sử dụng và phá hủy vũ khí hóa học thì được miễn xuất trình hồ sơ về Giấy phép sản xuất, kinh doanh hóa chất cần kiểm soát đặc biệt đến trước ngày 31 tháng 12 năm 2026.
+5. Đối với việc xuất khẩu, nhập khẩu hóa chất là tiền chất công nghiệp được đưa vào Danh mục hóa chất cần kiểm soát đặc biệt ban hành theo Nghị định số 24/2026/NĐ-CP ngày 17 tháng 01 năm 2026 của Chính phủ quy định các danh mục hóa chất thuộc phạm vi điều chỉnh của Luật Hóa chất thì được sử dụng Giấy chứng nhận đủ điều kiện sản xuất, kinh doanh hóa chất sản xuất, kinh doanh có điều kiện trong lĩnh vực công nghiệp đã được cấp thay thế cho Giấy phép sản xuất, kinh doanh hóa chất cần kiểm soát đặc biệt cho đến ngày 31 tháng 12 năm 2027.
+6. Đối với việc xuất khẩu, nhập khẩu hóa chất là hóa chất Bảng; hóa chất hạn chế sản xuất, kinh doanh được đưa vào Danh mục hóa chất cần kiểm soát đặc biệt ban hành theo Nghị định số 24/2026/NĐ-CP ngày 17 tháng 01 năm 2026 của Chính phủ quy định các danh mục hóa chất thuộc phạm vi điều chỉnh của Luật Hóa chất thì được sử dụng Giấy phép sản xuất, kinh doanh đã được cấp thay thế cho Giấy phép sản xuất, kinh doanh hóa chất cần kiểm soát đặc biệt cho đến khi hết hiệu lực của Giấy phép.
+7. Đối với hóa chất thuộc Danh mục hóa chất sản xuất, kinh doanh có điều kiện được ban hành theo Nghị định số 24/2026/NĐ-CP ngày 17 tháng 01 năm 2026 của Chín [...cắt bớt]</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4986,9 +5942,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135173</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5004,17 +5957,25 @@
           <t>question_ambiguous</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>NĐ 36/2019 Điều 3 có hai khoản về nội dung kiểm tra sức khỏe vận động viên: khoản 2 (điểm a, b khoản 1, liệt kê nội dung) và khoản 3 (điểm c khoản 1, "theo quy định của pháp luật"); câu hỏi không phân biệt</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>36/2019/NĐ-CP · hiệu lực 2019-06-14 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Chăm sóc sức khỏe và chữa trị chấn thương
+3. Nội dung kiểm tra sức khỏe cho vận động viên quy định tại điểm c khoản 1 Điều này được thực hiện theo quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 349/2025/NĐ-CP · hiệu lực 2026-02-15
+2. Nghị định số 152/2018/NĐ-CP ngày 07 tháng 11 năm 2018 của Chính phủ quy định một số chế độ đối với huấn luyện viên, vận động viên thể thao trong thời gian tập trung tập huấn, thi đấu; Chương II Nghị định số 36/2019/NĐ-CP ngày 29 tháng 4 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật sửa đổi, bổ sung một số điều của Luật Thể dục, thể thao hết hiệu lực kể từ ngày Nghị định này có hiệu lực thi hành.
+3. Trường hợp các văn bản quy phạm pháp luật dẫn chiếu áp dụng tại Nghị định này được sửa đổi, bổ sung hoặc thay thế thì áp dụng theo các văn bản sửa đổi, bổ sung hoặc thay thế đó đối với các nội dung liên quan.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5042,7 +6003,6 @@
           <t>2026-08-15 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5063,9 +6023,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135173</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5081,17 +6038,25 @@
           <t>question_ambiguous,gold_wrong</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>Như dòng trước. Chuyển chỗ: 349/2025/NĐ-CP khoản 3 Điều 9, giống từng chữ; cùng Chính phủ, cùng nghị định chấm dứt Chương II NĐ 36/2019</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>36/2019/NĐ-CP · hiệu lực 2019-06-14 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Chăm sóc sức khỏe và chữa trị chấn thương
+3. Nội dung kiểm tra sức khỏe cho vận động viên quy định tại điểm c khoản 1 Điều này được thực hiện theo quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 349/2025/NĐ-CP · hiệu lực 2026-02-15
+2. Nghị định số 152/2018/NĐ-CP ngày 07 tháng 11 năm 2018 của Chính phủ quy định một số chế độ đối với huấn luyện viên, vận động viên thể thao trong thời gian tập trung tập huấn, thi đấu; Chương II Nghị định số 36/2019/NĐ-CP ngày 29 tháng 4 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật sửa đổi, bổ sung một số điều của Luật Thể dục, thể thao hết hiệu lực kể từ ngày Nghị định này có hiệu lực thi hành.
+3. Trường hợp các văn bản quy phạm pháp luật dẫn chiếu áp dụng tại Nghị định này được sửa đổi, bổ sung hoặc thay thế thì áp dụng theo các văn bản sửa đổi, bổ sung hoặc thay thế đó đối với các nội dung liên quan.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5119,7 +6084,6 @@
           <t>2026-06-15 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5140,9 +6104,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135173</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5158,17 +6119,25 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 349/2025/NĐ-CP khoản 2 Điều 5 "Thành viên đội thể thao trong thời gian tập trung tập huấn ở nước ngoài được hưởng chế độ dinh dưỡng hằng ngày theo thư mời hoặc hợp đồng …"; cùng Chính phủ, cùng nghị định chấm dứt Chương II NĐ 36/2019</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>36/2019/NĐ-CP · hiệu lực 2019-06-14 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Chế độ dinh dưỡng đặc thù
+7. Huấn luyện viên, vận động viên khi tập huấn ở nước ngoài được hưởng chế độ bữa ăn hàng ngày theo thư mời hoặc hợp đồng ký kết giữa cơ quan quản lý vận động viên ở trong nước với cơ sở đào tạo ở nước ngoài.</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 349/2025/NĐ-CP · hiệu lực 2026-02-15
+2. Nghị định số 152/2018/NĐ-CP ngày 07 tháng 11 năm 2018 của Chính phủ quy định một số chế độ đối với huấn luyện viên, vận động viên thể thao trong thời gian tập trung tập huấn, thi đấu; Chương II Nghị định số 36/2019/NĐ-CP ngày 29 tháng 4 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật sửa đổi, bổ sung một số điều của Luật Thể dục, thể thao hết hiệu lực kể từ ngày Nghị định này có hiệu lực thi hành.
+3. Trường hợp các văn bản quy phạm pháp luật dẫn chiếu áp dụng tại Nghị định này được sửa đổi, bổ sung hoặc thay thế thì áp dụng theo các văn bản sửa đổi, bổ sung hoặc thay thế đó đối với các nội dung liên quan.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5221,9 +6190,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=30338</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5234,18 +6200,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>15/2023/TT-BNNPTNT chỉ bãi bỏ khoản 4 Điều 1 TT 63/2012 (QCVN 01-108:2012), không có quy định kế thừa</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>63/2012/TT-BNNPTNT · hiệu lực 2013-06-16 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Ban hành kèm theo Thông tư này các Quy chuẩn kỹ thuật quốc gia về lĩnh vực Kiểm dịch và Bảo vệ thực vật:
+4. Quy chuẩn Kỹ thuật quốc gia về Quy trình giám định nhóm ruồi đục quả thuộc giống Anastrepha là dịch hại kiểm dịch thực vật của Việt Nam.
+Ký hiệu: QCVN 01-108 : 2012/BNNPTNT.</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 15/2023/TT-BNNPTNT · hiệu lực 2024-02-05
+5. Bãi bỏ các khoản 1, 2, 3, 4, 5, 6, 7, 14 và 15 Điều 1 Thông tư số 63/2012/TT-BNNPTNT ngày 14/12/2012 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về kiểm dịch và bảo vệ thực vật.
+CHUYỂN TIẾP: 2. Quy định chuyển tiếp:
+a) Thuốc bảo vệ thực vật đang thực hiện khảo nghiệm theo quy chuẩn kỹ thuật quốc gia quy định tại khoản 1 Điều 1 Thông tư số 55/2009/TT-BNNPTNT ngày 28/8/2009 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về bảo vệ và kiểm dịch thực vật; khoản 1, 2 Điều 1 Thông tư số 26/2010/TT-BNNPTNT ngày 27/4/2010 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về bảo vệ và kiểm dịch thực vật; khoản 1, 2 và 3 Điều 1 Thông tư số 71/2010/TT-BNNPTNT ngày 10/12/2010 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về bảo vệ và kiểm dịch thực vật; khoản 8, 9, 10, 11 và 12 Điều 1 Thông tư số 32/2013/TT-BNNPTNT ngày 14/6/2013 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về kiểm dịch và bảo vệ thực vật; khoản 2, 6, 12, 13, 16 và 20 Điều 1 Thông tư số 16/2014/TT-BNNPTNT ngày 05/6/2014 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về kiểm dịch và bảo vệ thực vật trước ngày Thông tư này có hiệu lực thi hành thì tiếp tục thực hiện theo quy chuẩn kỹ thuật quốc gia quy định tại khoản 1 Điều 1 Thông tư số 55/2009/TT-BNNPTNT ngày 28/8/2009; khoản 1, 2 Điều 1 Thông tư số 26/2010/TT-BNNPTNT ngày 27/4/2010; khoản 1, 2 và 3 Điều 1 Thông tư số 71/2010/TT-BNNPTNT ngày 10/12/2010; khoản 8, 9, 10, 11 và 12 Điều 1 Thông tư số 32/2013/TT-BNNPTNT ngày 14/6/2013; khoản 2, 6, 12, 13, 16 và 20 Điều 1 Thông tư số 16/2014/TT-BNNPTNT ngày 05/6/2014. Kết quả khảo nghiệm thuốc bảo vệ thực vật thực hiện theo quy chuẩn kỹ thuật quốc gia này được sử dụng để đề nghị cấp Giấy chứng nhận đăng ký thuốc bảo vệ thực vật theo quy định.
+b) Giống cây trồng đang thực hiện khảo nghiệm theo quy chuẩn kỹ thuật quốc gia quy định tại khoản 3, 4, 5 và 6 Điều 1 Thông tư số 67/2011/TT-BNNPTNT ngày 17/10/2011 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về khảo nghiệm giống cây trồng; khoản 3, 6, 7, 9, 10, 11, 12, 13 và 14 Điều 1 Thông tư số 24/2012/TT-BNNPTNT ngày 19/6/2012 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về khảo nghiệm giống cây trồng; khoản 2, 3, 4, 5, 6, 7 và 8 Điều 1 Thông tư số 33/2013/TT-BNNPTNT ngày 21/6/2013 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về khảo nghiệm giống cây trồng; khoản 1, 2, 3, 4 và 5 Điều 1 Thông tư số 05/2014/TT-BNNPTNT ngày 10/02/2014 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia lĩnh vực trồng trọt trước ngày Thông tư này có hiệu lực thi hành thì tiếp tục thực hiện khảo nghiệm theo quy chuẩn kỹ thuật quốc gia được ban hành tại các Thông tư nêu trên đến khi có kết quả khảo nghiệm. Kết quả khảo nghiệm này được sử dụng làm căn cứ cấp Bằng bảo hộ giống cây trồng theo quy định.
+c) Đối với các giống cây trồng được quy định tại khoản 3, 4, 5 và 6 Điều 1 Thông tư số 67/2011/TT-BNNPTNT ngày 17/10/2011 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về khảo nghiệm giống cây trồng; khoản 3, 6, 7, 9, 10, 11, 12, 13 và 14 Điều 1 Thông tư số 24/2012/TT-BNNPTNT ngày 19/6/2012 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về khảo nghiệm giống cây trồng; khoản 2, 3, 4, 5, 6, 7 và 8 Điều 1 Thông tư số 33/2013/TT-BNNPTNT ngày 21/6/2013 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia về khảo nghiệm giống cây trồng; khoản 1, 2, 3, 4 và 5 Điều 1 Thông tư số 05/2014/TT-BNNPTNT ngày 10/02/2014 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn ban hành quy chuẩn kỹ thuật quốc gia lĩnh vực trồng trọt mà đã nộp đơn đăng ký bảo hộ giống cây trồng trước thời điểm Thông tư này có hiệu lực nhưng chưa thực hiện khảo nghiệm được thực hiện khảo nghiệm theo quy định tại khoản 3, 4, 5 và 6 Điều 1 Thông tư số 67/2011/TT-BNNPTNT ngày 17/10/2011; k [...cắt bớt]</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5298,9 +6275,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5311,14 +6285,33 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>18/2026/NĐ-CP · hiệu lực 2026-01-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 10. Sửa đổi, bổ sung một số điều của Nghị định số 08/2020/NĐ-CP về tổ chức và hoạt động của Thừa phát lại
+3. Trong thời hạn 20 ngày làm việc, kể từ ngày nhận được văn bản và hồ sơ đề nghị bổ nhiệm Thừa phát lại của Sở Tư pháp, Chủ tịch Ủy ban nhân dân cấp tỉnh xem xét, quyết định bổ nhiệm Thừa phát lại; trường hợp từ chối phải thông báo bằng văn bản và nêu rõ lý do.
+Trường hợp cần thiết, Chủ tịch Ủy ban nhân dân cấp tỉnh tiến hành xác minh hoặc yêu cầu Sở Tư pháp, cơ quan, tổ chức có liên quan xác minh tiêu chuẩn bổ nhiệm, thông tin trong hồ sơ đề nghị bổ nhiệm trước khi xem xét, quyết định việc bổ nhiệm. Thời gian xác minh không quá 45 ngày kể từ ngày Chủ tịch Ủy ban nhân dân cấp tỉnh có văn bản xác minh; thời gian xác minh không tính vào thời hạn xem xét bổ nhiệm Thừa phát lại nêu tại khoản này.
+Khi giải quyết hồ sơ đề nghị bổ nhiệm Thừa phát lại, cơ quan có thẩm quyền bổ nhiệm Thừa phát lại yêu cầu cơ quan quản lý cơ sở dữ liệu lý lịch tư pháp cung cấp thông tin lý lịch tư pháp đối với người đề nghị bổ nhiệm Thừa phát lại.
+Cơ quan quản lý cơ sở dữ liệu lý lịch tư pháp có trách nhiệm cung cấp thông tin cho cơ quan yêu cầu trong thời hạn 03 ngày làm việc kể từ ngày nhận được yêu cầu. Thời gian phối hợp cung cấp thông tin lý lịch tư pháp không tính vào thời gian giải quyết thủ tục hành chính.</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 151/2026/NĐ-CP · hiệu lực 2026-07-01
+3. Bãi bỏ Điều 10 của Nghị định số 18/2026/NĐ-CP ngày 14 tháng 01 năm 2026 của Chính phủ sửa đổi, bổ sung một số nghị định để cắt giảm, đơn giản hóa thủ tục hành chính, điều kiện kinh doanh thuộc phạm vi quản lý của Bộ Tư pháp; các Điều 27, 28, 29 và 30 của Nghị định số 121/2025/NĐ-CP ngày 11 tháng 6 năm 2025 của Chính phủ quy định về phân quyền, phân cấp trong lĩnh vực quản lý nhà nước của Bộ Tư pháp.
+CHUYỂN TIẾP: Điều 58. Điều khoản chuyển tiếp
+1. Kể từ ngày Nghị định này có hiệu lực thi hành, việc đổi tên Văn phòng Thừa phát lại thành văn phòng thi hành án dân sự quy định tại khoản 5 Điều 116 của Luật Thi hành án dân sự được thực hiện theo trình tự, thủ tục của pháp luật về doanh nghiệp và pháp luật khác có liên quan; việc đổi Thẻ Thừa phát lại thành Thẻ Thừa hành viên quy định tại khoản 5 Điều 116 của Luật Thi hành án dân sự được thực hiện theo trình tự, thủ tục tại khoản 4 Điều 13 Nghị định này.
+Việc đổi Thẻ Thừa phát lại phải thực hiện đồng thời hoặc sau khi đã thực hiện đổi tên Văn phòng Thừa phát lại.
+2. Tại thời điểm Nghị định này có hiệu lực thi hành, người đã tham gia nhưng chưa hoàn thành khóa đào tạo, bồi dưỡng nghề Thừa phát lại theo quy định của Nghị định số 08/2020/NĐ-CP thì tiếp tục được đào tạo, bồi dưỡng và cấp chứng chỉ tốt nghiệp đào tạo nghề Thừa phát lại, giấy chứng nhận hoàn thành khóa bồi dưỡng nghề Thừa phát lại theo quy định của Nghị định số 08/2020/NĐ-CP.
+Chứng chỉ tốt nghiệp đào tạo nghề Thừa phát lại, giấy chứng nhận hoàn thành khóa bồi dưỡng nghề Thừa phát lại quy định tại khoản này được sử dụng để đăng ký tập sự, tham dự kiểm tra kết quả tập sự hành nghề Thừa hành viên, xem xét bổ nhiệm Thừa hành viên theo quy định của Nghị định này.
+3. Người đã có chứng chỉ tốt nghiệp đào tạo nghề Thừa phát lại, giấy chứng nhận hoàn thành khóa bồi dưỡng nghề Thừa phát lại hoặc đã hoàn thành thời gian tập sự hành nghề Thừa phát lại trước ngày Nghị định này có hiệu lực thi hành được đăng ký tập sự hành nghề Thừa hành viên, tham dự kiểm tra kết quả tập sự hành nghề Thừa hành viên, xem xét bổ nhiệm Thừa hành viên theo quy định của Nghị định này.
+Trường hợp người đã đăng ký tập sự hoặc đang tập sự hành nghề Thừa phát lại tại thời điểm Nghị định này có hiệu lực thi hành thì tiếp tục tập sự theo quy định của Nghị định số 08/2020/NĐ-CP hoặc theo quy định của Nghị định này tùy thuộc vào việc đổi tên của văn phòng nơi tập sự.
+4. Giấy chứng nhận kết quả kiểm tra tập sự hành nghề Thừa phát lại được cấp theo quy định của Nghị định số 08/2020/NĐ-CP tiếp tục có hiệu lực sau thời điểm Nghị định này có hiệu lực thi hành. Hết thời hạn 05 năm kể từ ngày Nghị định này có hiệu lực thi hành mà người được cấp giấy chứng nhận kết quả kiểm tra tập sự hành nghề Thừa phát lại không đề nghị bổ nhiệm Thừa hành viên thì giấy chứng nhận hết hiệu lực.
+5. Kể từ ngày Nghị định này có hiệu lực thi hành, việc miễn nhiệm, bổ nhiệm lại đối với Thừa phát lại đã được bổ nhiệm, miễn nhiệm theo quy định tại Nghị định số 08/2020/NĐ-CP được thực hiện theo quy định của Nghị định này.
+6. Tại thời điểm Nghị định này có hiệu lực thi hành, hồ sơ, thủ tục hành chính đang được giải quyết theo quy định của Nghị định số 08/2020/NĐ-CP được sửa đổi, bổ sung bởi Nghị định số 18/2026/NĐ-CP ngày 14 tháng 01 năm 2026 thì tiếp tục được giải quyết theo quy định của Nghị định số 08/2020/NĐ-CP được sửa đổi, bổ sung bởi Nghị định số 18/2026/NĐ-CP, trừ trường hợp hồ sơ, thủ tục hành chính liên quan đến thành lập, đăng ký hoạt động, thay đổi nội dung đăng ký hoạt động, tổ chức lại Văn phòng Thừa phát lại thì được thực hiện theo quy định của pháp luật về doanh nghiệp, Nghị định này và pháp luật khác có liên quan.
+7. Thừa phát lại từ đủ 69 tuổi trở lên tại thời điểm Nghị định này có hiệu lực thi hành được tiếp tục hành nghề cho đến ngày 01 tháng 7 năm 2027. Từ sau ngày 01 tháng 7 năm 2027 sẽ đương nhiên miễn nhiệm theo quy định tại Điều 11 Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5346,7 +6339,6 @@
           <t>2026-08-04 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5367,9 +6359,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5385,17 +6374,38 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 151/2026/NĐ-CP khoản 4 Điều 11 (Chủ tịch Ủy ban nhân dân cấp tỉnh miễn nhiệm theo đề nghị của Sở Tư pháp hoặc tự mình quyết định; Sở Tư pháp lập hồ sơ trong 15 ngày làm việc, Chủ tịch quyết định trong 05 ngày làm việc); cùng Chính phủ, cùng nghị định bãi bỏ Điều 10 NĐ 18/2026. Thừa phát lại đổi thành Thừa hành viên theo khoản 5 Điều 116 Luật Thi hành án dân sự: người audit xem lại yếu tố 2</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>18/2026/NĐ-CP · hiệu lực 2026-01-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 10. Sửa đổi, bổ sung một số điều của Nghị định số 08/2020/NĐ-CP về tổ chức và hoạt động của Thừa phát lại
+3. Trong thời hạn 20 ngày làm việc, kể từ ngày nhận được văn bản và hồ sơ đề nghị bổ nhiệm Thừa phát lại của Sở Tư pháp, Chủ tịch Ủy ban nhân dân cấp tỉnh xem xét, quyết định bổ nhiệm Thừa phát lại; trường hợp từ chối phải thông báo bằng văn bản và nêu rõ lý do.
+Trường hợp cần thiết, Chủ tịch Ủy ban nhân dân cấp tỉnh tiến hành xác minh hoặc yêu cầu Sở Tư pháp, cơ quan, tổ chức có liên quan xác minh tiêu chuẩn bổ nhiệm, thông tin trong hồ sơ đề nghị bổ nhiệm trước khi xem xét, quyết định việc bổ nhiệm. Thời gian xác minh không quá 45 ngày kể từ ngày Chủ tịch Ủy ban nhân dân cấp tỉnh có văn bản xác minh; thời gian xác minh không tính vào thời hạn xem xét bổ nhiệm Thừa phát lại nêu tại khoản này.
+Khi giải quyết hồ sơ đề nghị bổ nhiệm Thừa phát lại, cơ quan có thẩm quyền bổ nhiệm Thừa phát lại yêu cầu cơ quan quản lý cơ sở dữ liệu lý lịch tư pháp cung cấp thông tin lý lịch tư pháp đối với người đề nghị bổ nhiệm Thừa phát lại.
+Cơ quan quản lý cơ sở dữ liệu lý lịch tư pháp có trách nhiệm cung cấp thông tin cho cơ quan yêu cầu trong thời hạn 03 ngày làm việc kể từ ngày nhận được yêu cầu. Thời gian phối hợp cung cấp thông tin lý lịch tư pháp không tính vào thời gian giải quyết thủ tục hành chính.</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 151/2026/NĐ-CP · hiệu lực 2026-07-01
+3. Bãi bỏ Điều 10 của Nghị định số 18/2026/NĐ-CP ngày 14 tháng 01 năm 2026 của Chính phủ sửa đổi, bổ sung một số nghị định để cắt giảm, đơn giản hóa thủ tục hành chính, điều kiện kinh doanh thuộc phạm vi quản lý của Bộ Tư pháp; các Điều 27, 28, 29 và 30 của Nghị định số 121/2025/NĐ-CP ngày 11 tháng 6 năm 2025 của Chính phủ quy định về phân quyền, phân cấp trong lĩnh vực quản lý nhà nước của Bộ Tư pháp.
+CHUYỂN TIẾP: Điều 58. Điều khoản chuyển tiếp
+1. Kể từ ngày Nghị định này có hiệu lực thi hành, việc đổi tên Văn phòng Thừa phát lại thành văn phòng thi hành án dân sự quy định tại khoản 5 Điều 116 của Luật Thi hành án dân sự được thực hiện theo trình tự, thủ tục của pháp luật về doanh nghiệp và pháp luật khác có liên quan; việc đổi Thẻ Thừa phát lại thành Thẻ Thừa hành viên quy định tại khoản 5 Điều 116 của Luật Thi hành án dân sự được thực hiện theo trình tự, thủ tục tại khoản 4 Điều 13 Nghị định này.
+Việc đổi Thẻ Thừa phát lại phải thực hiện đồng thời hoặc sau khi đã thực hiện đổi tên Văn phòng Thừa phát lại.
+2. Tại thời điểm Nghị định này có hiệu lực thi hành, người đã tham gia nhưng chưa hoàn thành khóa đào tạo, bồi dưỡng nghề Thừa phát lại theo quy định của Nghị định số 08/2020/NĐ-CP thì tiếp tục được đào tạo, bồi dưỡng và cấp chứng chỉ tốt nghiệp đào tạo nghề Thừa phát lại, giấy chứng nhận hoàn thành khóa bồi dưỡng nghề Thừa phát lại theo quy định của Nghị định số 08/2020/NĐ-CP.
+Chứng chỉ tốt nghiệp đào tạo nghề Thừa phát lại, giấy chứng nhận hoàn thành khóa bồi dưỡng nghề Thừa phát lại quy định tại khoản này được sử dụng để đăng ký tập sự, tham dự kiểm tra kết quả tập sự hành nghề Thừa hành viên, xem xét bổ nhiệm Thừa hành viên theo quy định của Nghị định này.
+3. Người đã có chứng chỉ tốt nghiệp đào tạo nghề Thừa phát lại, giấy chứng nhận hoàn thành khóa bồi dưỡng nghề Thừa phát lại hoặc đã hoàn thành thời gian tập sự hành nghề Thừa phát lại trước ngày Nghị định này có hiệu lực thi hành được đăng ký tập sự hành nghề Thừa hành viên, tham dự kiểm tra kết quả tập sự hành nghề Thừa hành viên, xem xét bổ nhiệm Thừa hành viên theo quy định của Nghị định này.
+Trường hợp người đã đăng ký tập sự hoặc đang tập sự hành nghề Thừa phát lại tại thời điểm Nghị định này có hiệu lực thi hành thì tiếp tục tập sự theo quy định của Nghị định số 08/2020/NĐ-CP hoặc theo quy định của Nghị định này tùy thuộc vào việc đổi tên của văn phòng nơi tập sự.
+4. Giấy chứng nhận kết quả kiểm tra tập sự hành nghề Thừa phát lại được cấp theo quy định của Nghị định số 08/2020/NĐ-CP tiếp tục có hiệu lực sau thời điểm Nghị định này có hiệu lực thi hành. Hết thời hạn 05 năm kể từ ngày Nghị định này có hiệu lực thi hành mà người được cấp giấy chứng nhận kết quả kiểm tra tập sự hành nghề Thừa phát lại không đề nghị bổ nhiệm Thừa hành viên thì giấy chứng nhận hết hiệu lực.
+5. Kể từ ngày Nghị định này có hiệu lực thi hành, việc miễn nhiệm, bổ nhiệm lại đối với Thừa phát lại đã được bổ nhiệm, miễn nhiệm theo quy định tại Nghị định số 08/2020/NĐ-CP được thực hiện theo quy định của Nghị định này.
+6. Tại thời điểm Nghị định này có hiệu lực thi hành, hồ sơ, thủ tục hành chính đang được giải quyết theo quy định của Nghị định số 08/2020/NĐ-CP được sửa đổi, bổ sung bởi Nghị định số 18/2026/NĐ-CP ngày 14 tháng 01 năm 2026 thì tiếp tục được giải quyết theo quy định của Nghị định số 08/2020/NĐ-CP được sửa đổi, bổ sung bởi Nghị định số 18/2026/NĐ-CP, trừ trường hợp hồ sơ, thủ tục hành chính liên quan đến thành lập, đăng ký hoạt động, thay đổi nội dung đăng ký hoạt động, tổ chức lại Văn phòng Thừa phát lại thì được thực hiện theo quy định của pháp luật về doanh nghiệp, Nghị định này và pháp luật khác có liên quan.
+7. Thừa phát lại từ đủ 69 tuổi trở lên tại thời điểm Nghị định này có hiệu lực thi hành được tiếp tục hành nghề cho đến ngày 01 tháng 7 năm 2027. Từ sau ngày 01 tháng 7 năm 2027 sẽ đương nhiên miễn nhiệm theo quy định tại Điều 11 Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5448,9 +6458,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=42148</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5466,17 +6473,30 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 45/2023/TT-BGTVT Điều 1 ban hành Quy chuẩn kỹ thuật quốc gia về chất lượng an toàn kỹ thuật và bảo vệ môi trường đối với xe máy chuyên dùng, mã số QCVN 13:2023/BGTVT; cùng Bộ GTVT, cùng thông tư bãi bỏ khoản 5 Điều 1 TT 56/2011. Điều khoản chuyển tiếp chỉ giữ QCVN cũ cho xe nhập khẩu về cảng trước ngày hiệu lực, câu hỏi không nêu quan hệ này</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>56/2011/TT-BGTVT · hiệu lực 2012-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Ban hành kèm theo Thông tư này 06 Quy chuẩn kỹ thuật quốc gia về phương tiện cơ giới đường bộ sau đây:
+5. Quy chuẩn kỹ thuật quốc gia về chất lượng an toàn kỹ thuật và bảo vệ môi trường đối với xe máy chuyên dùng; Số hiệu: QCVN 13 : 2011/BGTVT.</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 45/2023/TT-BGTVT · hiệu lực 2024-07-01
+2. Thông tư này bãi bỏ khoản 5 Điều 1 Thông tư số 56/2011/TT-BGTVT ngày 11 tháng 07 năm 2011 của Bộ trưởng Bộ Giao thông vận tải ban hành 06 Quy chuẩn kỹ thuật quốc gia về phương tiện cơ giới đường bộ.
+3. Quy định chuyển tiếp
+a) Giấy chứng nhận chất lượng an toàn kỹ thuật và bảo vệ môi trường xe máy chuyên dùng, Phiếu xuất xưởng hoặc Biên bản nghiệm thu cải tạo cấp theo Quy chuẩn QCVN 13:2011/BGTVT thì vẫn tiếp tục được sử dụng cho đến khi hết hiệu lực;
+b) Đối với xe máy chuyên dùng nhập khẩu có ngày cập cảng hoặc về cửa khẩu Việt Nam trước ngày QCVN 13:2023/BGTVT có hiệu lực thì áp dụng QCVN 13:2011/BGTVT.
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+a) Giấy chứng nhận chất lượng an toàn kỹ thuật và bảo vệ môi trường xe máy chuyên dùng, Phiếu xuất xưởng hoặc Biên bản nghiệm thu cải tạo cấp theo Quy chuẩn QCVN 13:2011/BGTVT thì vẫn tiếp tục được sử dụng cho đến khi hết hiệu lực;
+b) Đối với xe máy chuyên dùng nhập khẩu có ngày cập cảng hoặc về cửa khẩu Việt Nam trước ngày QCVN 13:2023/BGTVT có hiệu lực thì áp dụng QCVN 13:2011/BGTVT.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5504,7 +6524,6 @@
           <t>2023-10-29 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5525,9 +6544,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5748</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5543,17 +6559,44 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>Điều 80 Luật 24/2000/QH10 không hết hiệu lực ngày 01/01/2023: điểm b khoản 3 Điều 156 Luật 08/2022/QH15 giữ "các điều 77, 78, 79, 80, 81, 83, 94 và 98 … có hiệu lực đến hết ngày 31 tháng 12 năm 2027"</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>24/2000/QH10 · hiệu lực 2001-04-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 80. Kiểm soát đối với doanh nghiệp bảo hiểm có nguy cơ mất khả năng thanh toán.
+2. Ban kiểm soát khả năng thanh toán có những nhiệm vụ, quyền hạn sau đây:
+a) Chỉ đạo và giám sát việc triển khai thực hiện các biện pháp khôi phục khả năng thanh toán theo phương án đã được chấp thuận;
+b) Thông báo cho các cơ quan nhà nước có liên quan về việc áp dụng các biện pháp khôi phục khả năng thanh toán để phối hợp thực hiện;
+c) Hạn chế phạm vi và lĩnh vực hoạt động của doanh nghiệp bảo hiểm;
+d) Đình chỉ những hoạt động có thể dẫn đến việc doanh nghiệp bảo hiểm mất khả năng thanh toán;
+đ) Yêu cầu doanh nghiệp bảo hiểm chuyển giao toàn bộ hợp đồng bảo hiểm của một hoặc một số nghiệp vụ bảo hiểm cho doanh nghiệp bảo hiểm khác;
+e) Tạm đình chỉ quyền quản trị, điều hành và yêu cầu doanh nghiệp bảo hiểm thay thế thành viên Hội đồng quản trị, Tổng giám đốc (Giám đốc), Phó Tổng giám đốc (Phó giám đốc) nếu xét thấy cần thiết;
+g) Yêu cầu Hội đồng quản trị, Tổng giám đốc (Giám đốc) miễn nhiệm, đình chỉ công tác đối với những người có hành vi vi phạm pháp luật, không chấp hành phương án khôi phục khả năng thanh toán đã được chấp thuận;
+h) Kiến nghị với Bộ Tài chính tiếp tục hoặc chấm dứt các biện pháp khôi phục khả năng thanh toán;
+i) Báo cáo Bộ Tài chính về việc áp dụng và kết quả của việc áp dụng các biện pháp khôi phục khả năng thanh toán.</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 08/2022/QH15 · hiệu lực 2023-01-01
+b) Các điều 77, 78, 79, 80, 81, 83, 94 và 98 của Luật Kinh doanh bảo hiểm số 24/2000/QH10 đã được sửa đổi, bổ sung một số điều theo Luật số 61/2010/QH12 và Luật số 42/2019/QH14 có hiệu lực đến hết ngày 31 tháng 12 năm 2027.
+CHUYỂN TIẾP: Điều 157. Điều khoản chuyển tiếp
+1. Các hợp đồng bảo hiểm đã giao kết trước ngày Luật này có hiệu lực và còn thời hạn hợp đồng thì tiếp tục thực hiện theo quy định của pháp luật tại thời điểm giao kết hợp đồng bảo hiểm, trừ trường hợp các bên tham gia hợp đồng bảo hiểm có thỏa thuận về việc sửa đổi, bổ sung hợp đồng để phù hợp với Luật này và để áp dụng quy định của Luật này.
+2. Chứng chỉ đại lý bảo hiểm được cấp trước ngày Luật này có hiệu lực được tiếp tục sử dụng đến hết ngày 31 tháng 12 năm 2025. Bộ trưởng Bộ Tài chính quy định chi tiết việc chuyển đổi chứng chỉ đại lý bảo hiểm được cấp trước ngày Luật này có hiệu lực sang chứng chỉ đại lý bảo hiểm theo quy định của Luật này.
+3. Chứng chỉ bảo hiểm, chứng chỉ môi giới bảo hiểm, chứng chỉ về phụ trợ bảo hiểm được cấp trước ngày Luật này có hiệu lực được tiếp tục sử dụng.
+4. Kể từ ngày 01 tháng 01 năm 2023, doanh nghiệp bảo hiểm, chi nhánh doanh nghiệp bảo hiểm phi nhân thọ nước ngoài dừng trích nộp Quỹ bảo vệ người được bảo hiểm.
+5. Việc xử lý số dư Quỹ bảo vệ người được bảo hiểm quy định tại Điều 97 của Luật Kinh doanh bảo hiểm số 24/2000/QH10 đã được sửa đổi, bổ sung một số điều theo Luật số 61/2010/QH12 và Luật số 42/2019/QH14 được thực hiện như sau:
+a) Toàn bộ số dư của Quỹ bảo vệ người được bảo hiểm được Bộ Tài chính quản lý để sử dụng cho mục đích bảo vệ quyền lợi của người được bảo hiểm trong trường hợp doanh nghiệp bảo hiểm mất khả năng thanh toán hoặc phá sản;
+b) Chính phủ quy định chi tiết về quản lý và sử dụng số dư của Quỹ bảo vệ người được bảo hiểm.
+Luật này được Quốc hội nước Cộng hòa xã hội chủ nghĩa Việt Nam khóa XV, kỳ họp thứ 3 thông qua ngày 16 tháng 6 năm 2022./.
+CHỦ TỊCH QUỐC HỘI
+Vương Đình Huệ</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5581,7 +6624,6 @@
           <t>2024-07-02 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5602,9 +6644,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5748</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5620,17 +6659,44 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>Điều 80 Luật 24/2000/QH10 không hết hiệu lực ngày 01/01/2023: điểm b khoản 3 Điều 156 Luật 08/2022/QH15 giữ các điều 77–81, 83, 94, 98 "có hiệu lực đến hết ngày 31 tháng 12 năm 2027"</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>24/2000/QH10 · hiệu lực 2001-04-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 80. Kiểm soát đối với doanh nghiệp bảo hiểm có nguy cơ mất khả năng thanh toán.
+2. Ban kiểm soát khả năng thanh toán có những nhiệm vụ, quyền hạn sau đây:
+a) Chỉ đạo và giám sát việc triển khai thực hiện các biện pháp khôi phục khả năng thanh toán theo phương án đã được chấp thuận;
+b) Thông báo cho các cơ quan nhà nước có liên quan về việc áp dụng các biện pháp khôi phục khả năng thanh toán để phối hợp thực hiện;
+c) Hạn chế phạm vi và lĩnh vực hoạt động của doanh nghiệp bảo hiểm;
+d) Đình chỉ những hoạt động có thể dẫn đến việc doanh nghiệp bảo hiểm mất khả năng thanh toán;
+đ) Yêu cầu doanh nghiệp bảo hiểm chuyển giao toàn bộ hợp đồng bảo hiểm của một hoặc một số nghiệp vụ bảo hiểm cho doanh nghiệp bảo hiểm khác;
+e) Tạm đình chỉ quyền quản trị, điều hành và yêu cầu doanh nghiệp bảo hiểm thay thế thành viên Hội đồng quản trị, Tổng giám đốc (Giám đốc), Phó Tổng giám đốc (Phó giám đốc) nếu xét thấy cần thiết;
+g) Yêu cầu Hội đồng quản trị, Tổng giám đốc (Giám đốc) miễn nhiệm, đình chỉ công tác đối với những người có hành vi vi phạm pháp luật, không chấp hành phương án khôi phục khả năng thanh toán đã được chấp thuận;
+h) Kiến nghị với Bộ Tài chính tiếp tục hoặc chấm dứt các biện pháp khôi phục khả năng thanh toán;
+i) Báo cáo Bộ Tài chính về việc áp dụng và kết quả của việc áp dụng các biện pháp khôi phục khả năng thanh toán.</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 08/2022/QH15 · hiệu lực 2023-01-01
+b) Các điều 77, 78, 79, 80, 81, 83, 94 và 98 của Luật Kinh doanh bảo hiểm số 24/2000/QH10 đã được sửa đổi, bổ sung một số điều theo Luật số 61/2010/QH12 và Luật số 42/2019/QH14 có hiệu lực đến hết ngày 31 tháng 12 năm 2027.
+CHUYỂN TIẾP: Điều 157. Điều khoản chuyển tiếp
+1. Các hợp đồng bảo hiểm đã giao kết trước ngày Luật này có hiệu lực và còn thời hạn hợp đồng thì tiếp tục thực hiện theo quy định của pháp luật tại thời điểm giao kết hợp đồng bảo hiểm, trừ trường hợp các bên tham gia hợp đồng bảo hiểm có thỏa thuận về việc sửa đổi, bổ sung hợp đồng để phù hợp với Luật này và để áp dụng quy định của Luật này.
+2. Chứng chỉ đại lý bảo hiểm được cấp trước ngày Luật này có hiệu lực được tiếp tục sử dụng đến hết ngày 31 tháng 12 năm 2025. Bộ trưởng Bộ Tài chính quy định chi tiết việc chuyển đổi chứng chỉ đại lý bảo hiểm được cấp trước ngày Luật này có hiệu lực sang chứng chỉ đại lý bảo hiểm theo quy định của Luật này.
+3. Chứng chỉ bảo hiểm, chứng chỉ môi giới bảo hiểm, chứng chỉ về phụ trợ bảo hiểm được cấp trước ngày Luật này có hiệu lực được tiếp tục sử dụng.
+4. Kể từ ngày 01 tháng 01 năm 2023, doanh nghiệp bảo hiểm, chi nhánh doanh nghiệp bảo hiểm phi nhân thọ nước ngoài dừng trích nộp Quỹ bảo vệ người được bảo hiểm.
+5. Việc xử lý số dư Quỹ bảo vệ người được bảo hiểm quy định tại Điều 97 của Luật Kinh doanh bảo hiểm số 24/2000/QH10 đã được sửa đổi, bổ sung một số điều theo Luật số 61/2010/QH12 và Luật số 42/2019/QH14 được thực hiện như sau:
+a) Toàn bộ số dư của Quỹ bảo vệ người được bảo hiểm được Bộ Tài chính quản lý để sử dụng cho mục đích bảo vệ quyền lợi của người được bảo hiểm trong trường hợp doanh nghiệp bảo hiểm mất khả năng thanh toán hoặc phá sản;
+b) Chính phủ quy định chi tiết về quản lý và sử dụng số dư của Quỹ bảo vệ người được bảo hiểm.
+Luật này được Quốc hội nước Cộng hòa xã hội chủ nghĩa Việt Nam khóa XV, kỳ họp thứ 3 thông qua ngày 16 tháng 6 năm 2022./.
+CHỦ TỊCH QUỐC HỘI
+Vương Đình Huệ</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5683,9 +6749,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26933</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5696,14 +6759,40 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>25/2011/TT-NHNN · hiệu lực 2011-10-14 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Bổ sung quy định đối với các thủ tục về quản lý vay, trả nợ nước ngoài để thực thi phương án đơn giản hóa nêu tại khoản 7 mục II Phần A của Nghị quyết 60/NQ-CP như sau:
+1. Thủ tục xác nhận đăng ký khoản vay trung, dài hạn nước ngoài theo phương thức tự vay, tự trả:
+a) Trong thời hạn 30 ngày làm việc kể từ ngày:
+- Ký hợp đồng vay vốn nước ngoài trung, dài hạn (không bao gồm vay nước ngoài dưới hình thức phát hành trái phiếu quốc tế) hoặc kể từ ngày văn bản bảo lãnh được ký (trong trường hợp khoản vay có bảo lãnh);
+- Ký hợp đồng gia hạn khoản vay ngắn hạn mà tổng thời gian gia hạn và thời gian đã vay ngắn hạn là trên 1 năm.
+Bên đi vay là doanh nghiệp, tổ chức tín dụng (trừ ngân hàng thương mại nhà nước), chi nhánh ngân hàng nước ngoài (sau đây gọi chung là “doanh nghiệp”) lập 01 bộ hồ sơ đăng ký khoản vay nước ngoài gửi qua đường bưu điện hoặc nộp trực tiếp đến:
+- Ngân hàng Nhà nước (Vụ Quản lý ngoại hối) đối với các khoản vay có kim ngạch vay từ trên 10 triệu USD (hoặc loại ngoại tệ khác có giá trị tương đương);
+- Ngân hàng Nhà nước chi nhánh tỉnh, thành phố nơi doanh nghiệp đặt trụ sở chính đối với các khoản vay có kim ngạch vay đến 10 triệu USD (hoặc loại ngoại tệ khác có giá trị tương đương).
+b) Trong thời hạn 15 ngày làm việc kể từ ngày nhận đầy đủ hồ sơ hợp lệ:
+- Ngân hàng Nhà nước xác nhận đăng ký đối với các khoản vay trung, dài hạn của doanh nghiệp có kim ngạch vay trên 10 triệu USD (hoặc các loại ngoại tệ khác có giá trị tương đương tại thời điểm ký kết hợp đồng vay). Trường hợp từ chối xác nhận, Ngân hàng Nhà nước có văn bản trả lời nêu rõ lý do.
+- Ngân hàng Nhà nước chi nhánh tỉnh, thành phố nơi doanh nghiệp có trụ sở chính xác nhận đăng ký đối với các khoản vay trung, dài hạn của doanh nghiệp có kim ngạch vay đến 10 triệu USD (hoặc các loại ngoại tệ khác có giá trị tương đương tại thời điểm ký kết hợp đồng vay). Trường hợp từ chối xác nhận, Ngân hàng Nhà nước chi nhánh tỉnh, thành phố có văn bản trả lời nêu rõ lý do.
+c) Thành phần hồ sơ:
+- Đơn đăng ký khoản vay trung, dài hạn nước ngoài (theo phụ lục số 01.ĐGH đính kèm Thông tư này);
+- Bản sao được chứng thực từ bản chính hồ sơ pháp lý của doanh nghiệp (trừ tổ chức tín dụng, chi nhánh ngân hàng nước ngoài) như Quyết định thành lập, giấy chứng nhận đăng ký kinh doanh, giấy chứng nhận đầu tư, giấy phép hoạt động, hoặc văn bản liên quan khác do cơ quan có thẩm quyền cấp;
+- Bản sao được chứng thực văn bản của cấp có thẩm quyền phê duyệt Dự án đầu tư hoặc Phương án sản xuất kinh doanh (trừ tổ chức tín dụng, chi nhánh ngân hàng nước ngoài và doanh nghiệp có vốn đầu tư nước ngoài đã có giấy chứng nhận đầu tư hoặc giấy phép đầu tư đối với dự án đầu tư cụ thể);
+- Bản sao và bản dịch ra tiếng Việt hợp đồng vay nước ngoài đã ký (có xác nhận của đại diện có thẩm quyền của doanh nghiệp về tính chính xác của bản dịch);
+- Bản sao và bản dịch ra tiếng Việt (trường hợp bản gốc bằng tiếng nước ngoài) văn bản bảo lãnh của bên bảo lãnh cho khoản vay nước ngoài (có xác nhận của đại diện có thẩm quyền của doanh nghiệp về tính chính xác của bản dịch);
+- Ngoài các hồ sơ trên:
++ Các Tập đoàn, Tổng công ty nhà nước vay trung, dài hạn nước ngoài phải có văn bản đồng ý của Bộ Tài chính và Bộ quản lý ngành về việc thực hiện khoản vay trung, dài hạn nước ngoài;
++ Các doanh nghiệp đăng ký cho khoản vay trung, dài hạn được gia hạn từ khoản vay ngắn hạn phải có: Bản sao và bản dịch ra tiếng Việt hợp đồng gia hạn khoản vay ngắn hạn nước ngoài thành khoản vay trung, dài hạn nước ngoài (có xác nhận của đại diện có thẩm quyền của doanh nghiệp về tính chính xác của bản dịch) và văn bản của ngân hàng thương mại (nơi doanh nghiệp mở tài khoản thực hiện khoản vay) xác nhận tình hình thực hiện khoản vay (rút vốn, trả nợ) đến thời điểm khoản vay nước ngoài ngắn hạn được gia hạn thành trung, dài hạn.</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 25/2014/TT-NHNN · hiệu lực 2014-11-01
+2. Bãi bỏ Điều 1 Thông tư 25/2011/TT-NHNN ngày 31/8/2011 của Ngân hàng Nhà nước về việc thực thi phương án đơn giản hóa thủ tục hành chính lĩnh vực hoạt động ngoại hối theo các Nghị quyết của Chính phủ về đơn giản hóa thủ tục hành chính thuộc phạm vi chức năng quản lý của Ngân hàng Nhà nước Việt Nam và Chương I, Mục I Chương IV Thông tư 09/2004/TT-NHNN ngày 21/12/2004 hướng dẫn việc vay và trả nợ nước ngoài của doanh nghiệp.
+CHUYỂN TIẾP: Điều 22. Điều khoản chuyển tiếp
+1. Các khoản vay nước ngoài của Bên đi vay đã thực hiện trước khi Thông tư này có hiệu lực, được tiếp tục thực hiện theo văn bản xác nhận đăng ký, xác nhận đăng ký thay đổi (nếu có) của Ngân hàng Nhà nước.
+2. Đối với các nội dung thay đổi liên quan đến khoản vay nước ngoài của Bên đi vay phát sinh sau thời điểm Thông tư này có hiệu lực, Bên đi vay phải thực hiện đăng ký thay đổi khoản vay nước ngoài theo quy định tại Thông tư này.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5731,7 +6820,6 @@
           <t>2016-02-11 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5752,9 +6840,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26933</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5770,17 +6855,45 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 25/2014/TT-NHNN Điều 13 (Vụ Quản lý ngoại hối xác nhận khoản vay trên 10 triệu USD, chi nhánh tỉnh đến 10 triệu USD) và khoản 2 Điều 7 (thời hạn 20 ngày, thay 15 ngày làm việc: chỉ đổi thời hạn); cùng NHNN, cùng thông tư bãi bỏ Điều 1 TT 25/2011</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>25/2011/TT-NHNN · hiệu lực 2011-10-14 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Bổ sung quy định đối với các thủ tục về quản lý vay, trả nợ nước ngoài để thực thi phương án đơn giản hóa nêu tại khoản 7 mục II Phần A của Nghị quyết 60/NQ-CP như sau:
+1. Thủ tục xác nhận đăng ký khoản vay trung, dài hạn nước ngoài theo phương thức tự vay, tự trả:
+a) Trong thời hạn 30 ngày làm việc kể từ ngày:
+- Ký hợp đồng vay vốn nước ngoài trung, dài hạn (không bao gồm vay nước ngoài dưới hình thức phát hành trái phiếu quốc tế) hoặc kể từ ngày văn bản bảo lãnh được ký (trong trường hợp khoản vay có bảo lãnh);
+- Ký hợp đồng gia hạn khoản vay ngắn hạn mà tổng thời gian gia hạn và thời gian đã vay ngắn hạn là trên 1 năm.
+Bên đi vay là doanh nghiệp, tổ chức tín dụng (trừ ngân hàng thương mại nhà nước), chi nhánh ngân hàng nước ngoài (sau đây gọi chung là “doanh nghiệp”) lập 01 bộ hồ sơ đăng ký khoản vay nước ngoài gửi qua đường bưu điện hoặc nộp trực tiếp đến:
+- Ngân hàng Nhà nước (Vụ Quản lý ngoại hối) đối với các khoản vay có kim ngạch vay từ trên 10 triệu USD (hoặc loại ngoại tệ khác có giá trị tương đương);
+- Ngân hàng Nhà nước chi nhánh tỉnh, thành phố nơi doanh nghiệp đặt trụ sở chính đối với các khoản vay có kim ngạch vay đến 10 triệu USD (hoặc loại ngoại tệ khác có giá trị tương đương).
+b) Trong thời hạn 15 ngày làm việc kể từ ngày nhận đầy đủ hồ sơ hợp lệ:
+- Ngân hàng Nhà nước xác nhận đăng ký đối với các khoản vay trung, dài hạn của doanh nghiệp có kim ngạch vay trên 10 triệu USD (hoặc các loại ngoại tệ khác có giá trị tương đương tại thời điểm ký kết hợp đồng vay). Trường hợp từ chối xác nhận, Ngân hàng Nhà nước có văn bản trả lời nêu rõ lý do.
+- Ngân hàng Nhà nước chi nhánh tỉnh, thành phố nơi doanh nghiệp có trụ sở chính xác nhận đăng ký đối với các khoản vay trung, dài hạn của doanh nghiệp có kim ngạch vay đến 10 triệu USD (hoặc các loại ngoại tệ khác có giá trị tương đương tại thời điểm ký kết hợp đồng vay). Trường hợp từ chối xác nhận, Ngân hàng Nhà nước chi nhánh tỉnh, thành phố có văn bản trả lời nêu rõ lý do.
+c) Thành phần hồ sơ:
+- Đơn đăng ký khoản vay trung, dài hạn nước ngoài (theo phụ lục số 01.ĐGH đính kèm Thông tư này);
+- Bản sao được chứng thực từ bản chính hồ sơ pháp lý của doanh nghiệp (trừ tổ chức tín dụng, chi nhánh ngân hàng nước ngoài) như Quyết định thành lập, giấy chứng nhận đăng ký kinh doanh, giấy chứng nhận đầu tư, giấy phép hoạt động, hoặc văn bản liên quan khác do cơ quan có thẩm quyền cấp;
+- Bản sao được chứng thực văn bản của cấp có thẩm quyền phê duyệt Dự án đầu tư hoặc Phương án sản xuất kinh doanh (trừ tổ chức tín dụng, chi nhánh ngân hàng nước ngoài và doanh nghiệp có vốn đầu tư nước ngoài đã có giấy chứng nhận đầu tư hoặc giấy phép đầu tư đối với dự án đầu tư cụ thể);
+- Bản sao và bản dịch ra tiếng Việt hợp đồng vay nước ngoài đã ký (có xác nhận của đại diện có thẩm quyền của doanh nghiệp về tính chính xác của bản dịch);
+- Bản sao và bản dịch ra tiếng Việt (trường hợp bản gốc bằng tiếng nước ngoài) văn bản bảo lãnh của bên bảo lãnh cho khoản vay nước ngoài (có xác nhận của đại diện có thẩm quyền của doanh nghiệp về tính chính xác của bản dịch);
+- Ngoài các hồ sơ trên:
++ Các Tập đoàn, Tổng công ty nhà nước vay trung, dài hạn nước ngoài phải có văn bản đồng ý của Bộ Tài chính và Bộ quản lý ngành về việc thực hiện khoản vay trung, dài hạn nước ngoài;
++ Các doanh nghiệp đăng ký cho khoản vay trung, dài hạn được gia hạn từ khoản vay ngắn hạn phải có: Bản sao và bản dịch ra tiếng Việt hợp đồng gia hạn khoản vay ngắn hạn nước ngoài thành khoản vay trung, dài hạn nước ngoài (có xác nhận của đại diện có thẩm quyền của doanh nghiệp về tính chính xác của bản dịch) và văn bản của ngân hàng thương mại (nơi doanh nghiệp mở tài khoản thực hiện khoản vay) xác nhận tình hình thực hiện khoản vay (rút vốn, trả nợ) đến thời điểm khoản vay nước ngoài ngắn hạn được gia hạn thành trung, dài hạn.</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 25/2014/TT-NHNN · hiệu lực 2014-11-01
+2. Bãi bỏ Điều 1 Thông tư 25/2011/TT-NHNN ngày 31/8/2011 của Ngân hàng Nhà nước về việc thực thi phương án đơn giản hóa thủ tục hành chính lĩnh vực hoạt động ngoại hối theo các Nghị quyết của Chính phủ về đơn giản hóa thủ tục hành chính thuộc phạm vi chức năng quản lý của Ngân hàng Nhà nước Việt Nam và Chương I, Mục I Chương IV Thông tư 09/2004/TT-NHNN ngày 21/12/2004 hướng dẫn việc vay và trả nợ nước ngoài của doanh nghiệp.
+CHUYỂN TIẾP: Điều 22. Điều khoản chuyển tiếp
+1. Các khoản vay nước ngoài của Bên đi vay đã thực hiện trước khi Thông tư này có hiệu lực, được tiếp tục thực hiện theo văn bản xác nhận đăng ký, xác nhận đăng ký thay đổi (nếu có) của Ngân hàng Nhà nước.
+2. Đối với các nội dung thay đổi liên quan đến khoản vay nước ngoài của Bên đi vay phát sinh sau thời điểm Thông tư này có hiệu lực, Bên đi vay phải thực hiện đăng ký thay đổi khoản vay nước ngoài theo quy định tại Thông tư này.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5833,9 +6946,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179085</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5846,14 +6956,90 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>64/2025/TT-BTC · hiệu lực 2025-07-01 → 2027-01-01 · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Mức thu một số khoản phí, lệ phí nhằm hỗ trợ cho doanh nghiệp, người dân
+1. Kể từ ngày 01 tháng 7 năm 2025 đến hết ngày 31 tháng 12 năm 2026, mức thu một số khoản phí, lệ phí được quy định như sau:
+Số TT
+Tên phí, lệ phí
+Mức thu
+1
+a) Lệ phí cấp giấy phép thành lập và hoạt động của ngân hàng
+Bằng 50% mức thu lệ phí quy định tại điểm a Mục 1 Biểu mức thu lệ phí tại khoản 1 Điều 4 Thông tư số 150/2016/TT-BTC ngày 14 tháng 10 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp lệ phí cấp giấy phép thành lập và hoạt động của tổ chức tín dụng; giấy phép thành lập chi nhánh ngân hàng nước ngoài, văn phòng đại diện của tổ chức tín dụng nước ngoài, tổ chức nước ngoài khác có hoạt động ngân hàng; giấy phép hoạt động cung ứng dịch vụ trung gian thanh toán cho các tổ chức không phải là ngân hàng.
+b) Lệ phí cấp giấy phép thành lập và hoạt động của tổ chức tín dụng phi ngân hàng
+Bằng 50% mức thu lệ phí quy định tại điểm b Mục 1 Biểu mức thu lệ phí tại khoản 1 Điều 4 Thông tư số 150/2016/TT-BTC.
+2
+a) Phí thẩm định kinh doanh hàng hóa, dịch vụ hạn chế kinh doanh thuộc lĩnh vực thương mại; phí thẩm định kinh doanh hàng hóa, dịch vụ kinh doanh có điều kiện thuộc lĩnh vực thương mại đối với chủ thể kinh doanh là tổ chức, doanh nghiệp; phí thẩm định kinh doanh hàng hóa, dịch vụ kinh doanh có điều kiện thuộc lĩnh vực thương mại đối với chủ thể kinh doanh là hộ kinh doanh, cá nhân
+Bằng 50% mức thu phí quy định tại Điều 4 Thông tư số 168/2016/TT-BTC ngày 26 tháng 10 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí thẩm định kinh doanh hàng hóa, dịch vụ hạn chế kinh doanh; hàng hóa, dịch vụ kinh doanh có điều kiện thuộc lĩnh vực thương mại và lệ phí cấp Giấy phép thành lập Sở Giao dịch hàng hóa.
+b) Lệ phí cấp Giấy phép thành lập Sở Giao dịch hàng hóa
+Bằng 50% mức thu lệ phí quy định tại Điều 4 Thông tư số 168/2016/TT-BTC.
+3
+a) Phí thẩm định cấp chứng chỉ, giấy phép, giấy chứng nhận trong hoạt động hàng không dân dụng; cấp giấy phép ra vào khu vực hạn chế tại cảng hàng không, sân bay (trừ nội dung thu tại các số thứ tự: 4.1, 4.2, 4.3, 4.4, 4.5.1, 5, 6 Mục VI Phần A Biểu mức thu phí, lệ phí áp dụng mức thu phí tương ứng quy định tại Mục VI Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC)
+Bằng 50% mức thu phí quy định tại Mục VI Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí, lệ phí trong lĩnh vực hàng không.
+b) Phí đăng ký giao dịch bảo đảm đối với tàu bay (trừ nội dung thu tại số thứ tự 4 Mục VIII Phần A Biểu mức thu phí, lệ phí áp dụng mức thu phí tương ứng quy định tại Mục VIII Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC)
+Bằng 50% mức thu phí quy định tại Mục VIII Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC.
+4
+a) Lệ phí ra, vào cảng hàng không, sân bay đối với chuyến bay của nước ngoài đến các Cảng hàng không Việt Nam
+Bằng 50% mức thu lệ phí quy định tại khoản 1 Điều 4 Thông tư số 194/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp phí hải quan và lệ phí ra, vào cảng hàng không, sân bay đối với chuyến bay của nước ngoài đến các Cảng hàng không Việt Nam.
+b) Phí hải quan đối với chuyến bay của nước ngoài đến các Cảng hàng không Việt Nam
+Bằng 50% mức thu phí quy định tại khoản 2 Điều 4 Thông tư số 194/2016/TT-BTC.
+5
+Phí khai thác, sử dụng thông tin, dữ liệu khí tượng thủy văn
+Bằng 50% mức thu phí quy định tại Biểu mức thu phí khai thác, sử dụng thông tin, dữ liệu khí tượng thủy văn ban hành kèm theo Thông tư số 197/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí khai thác, sử dụng thông tin, dữ liệu khí tượng thủy văn.
+6
+a) Lệ phí cấp văn bằng bảo hộ, cấp chứng nhận đăng ký hợp đồng chuyển giao quyền sở hữu công nghiệp trong lĩnh vực trồng trọt và giống cây lâm nghiệp
+Bằng 50% mức thu lệ phí quy định tại điểm 1 Mục I Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC ngày 09 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp.
+b) Lệ phí nộp đơn đăng ký bảo hộ quyền sở hữu trí tuệ trong lĩnh vực trồng trọt và giống cây lâm nghiệp
+Bằng 50% mức thu lệ phí quy định tại điểm 2 Mục I Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+c) Lệ phí cấp chứng chỉ hành nghề đại diện sở hữu công nghiệp, công bố, đăng bạ đại diện sở hữu công nghiệp trong lĩnh vực trồng trọt và giống cây lâm nghiệp
+Bằng 50% mức thu lệ phí quy định tại điểm 3 Mục I Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+d) Phí bảo hộ giống cây trồng:
+d.1) Duy trì hiệu lực Bằng bảo hộ giống cây trồng: Từ năm thứ 1 đến năm thứ 3; từ năm thứ 4 đến năm thứ 6; từ năm thứ 7 đến năm thứ 9
+Bằng 50% mức thu phí tương ứng quy định tại điểm 3 Mục III Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+d.2) Duy trì hiệu lực Bằng bảo hộ giống cây trồng: Từ năm thứ 10 đến năm thứ 15; từ năm thứ 16 đến hết thời gian hiệu lực của Bằng bảo hộ
+Bằng 50% mức thu phí tương ứng quy định tại điểm 3 Mục III Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+7
+a) Phí thẩm định nội dung tài liệu không kinh doanh để cấp giấy phép xuất bản
+Bằng 50% mức thu phí quy định tại khoản 1 Điều 4 Thông tư số 214/2016/TT-BTC ngày 10 tháng 11 năm 2016 của Bộ t</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 156/2025/TT-BTC · hiệu lực 2026-01-01
+3. Bãi bỏ quy định giảm 50% mức thu lệ phí cấp giấy chứng nhận kiểm định an toàn kỹ thuật và bảo vệ môi trường đối với xe ô tô dưới 10 chỗ ngồi tại số thứ tự 30 và bãi bỏ số thứ tự 31 khoản 1 Điều 1 Thông tư số 64/2025/TT-BTC ngày 30 tháng 6 năm 2025 của Bộ trưởng Bộ Tài chính quy định mức thu, miễn một số khoản phí, lệ phí nhằm hỗ trợ cho doanh nghiệp, người dân.
+4. Quy định về lệ phí cấp giấy phép hoạt động xây dựng cho nhà thầu nước ngoài tại khoản 2 và khoản 3 Điều 2 Thông tư này hết hiệu lực thi hành từ ngày 01 tháng 7 năm 2026.
+5. Trường hợp các văn bản liên quan viện dẫn tại Thông tư này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo văn bản sửa đổi, bổ sung hoặc thay thế đó.
+6. Trong quá trình thực hiện, trường hợp có vướng mắc, đề nghị các tổ chức, cá nhân phản ánh kịp thời về Bộ Tài chính để nghiên cứu, hướng dẫn./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Văn phòng Trung ương Đảng và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Quốc hội;
+- Hội đồng Dân tộc;
+- Ủy ban Kinh tế và Tài chính;
+- Văn phòng Chủ tịch nước;
+- Viện kiểm sát nhân dân tối cao;
+- Tòa án nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Cơ quan trung ương của các đoàn thể;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Thuế, Sở Tài chính các tỉnh, thành phố trực thuộc trung ương;
+- Kho bạc Nhà nước các khu vực;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Công báo;
+- Cơ sở dữ liệu quốc gia về pháp luật;
+- Cổng Thông tin điện tử Chính phủ, Bộ Tài chính;
+- Các đơn vị thuộc Bộ Tài chính;
+- Lưu: VT, CST (170b).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(đã ký)
+Cao Anh Tuấn</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5881,7 +7067,6 @@
           <t>2026-06-06 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5902,9 +7087,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179085</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5920,17 +7102,95 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>Điểm a (bù trừ phí tần số vô tuyến điện, số thứ tự 28) không bị bãi bỏ ngày 01/01/2026: khoản 3 Điều 3 TT 156/2025/TT-BTC chỉ bãi bỏ mức giảm 50% tại số thứ tự 30 và số thứ tự 31 khoản 1 Điều 1 TT 64/2025; khoản 1 Điều 1 TT 64/2025 áp dụng đến hết 31/12/2026</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>64/2025/TT-BTC · hiệu lực 2025-07-01 → 2027-01-01 · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Mức thu một số khoản phí, lệ phí nhằm hỗ trợ cho doanh nghiệp, người dân
+1. Kể từ ngày 01 tháng 7 năm 2025 đến hết ngày 31 tháng 12 năm 2026, mức thu một số khoản phí, lệ phí được quy định như sau:
+Số TT
+Tên phí, lệ phí
+Mức thu
+1
+a) Lệ phí cấp giấy phép thành lập và hoạt động của ngân hàng
+Bằng 50% mức thu lệ phí quy định tại điểm a Mục 1 Biểu mức thu lệ phí tại khoản 1 Điều 4 Thông tư số 150/2016/TT-BTC ngày 14 tháng 10 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp lệ phí cấp giấy phép thành lập và hoạt động của tổ chức tín dụng; giấy phép thành lập chi nhánh ngân hàng nước ngoài, văn phòng đại diện của tổ chức tín dụng nước ngoài, tổ chức nước ngoài khác có hoạt động ngân hàng; giấy phép hoạt động cung ứng dịch vụ trung gian thanh toán cho các tổ chức không phải là ngân hàng.
+b) Lệ phí cấp giấy phép thành lập và hoạt động của tổ chức tín dụng phi ngân hàng
+Bằng 50% mức thu lệ phí quy định tại điểm b Mục 1 Biểu mức thu lệ phí tại khoản 1 Điều 4 Thông tư số 150/2016/TT-BTC.
+2
+a) Phí thẩm định kinh doanh hàng hóa, dịch vụ hạn chế kinh doanh thuộc lĩnh vực thương mại; phí thẩm định kinh doanh hàng hóa, dịch vụ kinh doanh có điều kiện thuộc lĩnh vực thương mại đối với chủ thể kinh doanh là tổ chức, doanh nghiệp; phí thẩm định kinh doanh hàng hóa, dịch vụ kinh doanh có điều kiện thuộc lĩnh vực thương mại đối với chủ thể kinh doanh là hộ kinh doanh, cá nhân
+Bằng 50% mức thu phí quy định tại Điều 4 Thông tư số 168/2016/TT-BTC ngày 26 tháng 10 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí thẩm định kinh doanh hàng hóa, dịch vụ hạn chế kinh doanh; hàng hóa, dịch vụ kinh doanh có điều kiện thuộc lĩnh vực thương mại và lệ phí cấp Giấy phép thành lập Sở Giao dịch hàng hóa.
+b) Lệ phí cấp Giấy phép thành lập Sở Giao dịch hàng hóa
+Bằng 50% mức thu lệ phí quy định tại Điều 4 Thông tư số 168/2016/TT-BTC.
+3
+a) Phí thẩm định cấp chứng chỉ, giấy phép, giấy chứng nhận trong hoạt động hàng không dân dụng; cấp giấy phép ra vào khu vực hạn chế tại cảng hàng không, sân bay (trừ nội dung thu tại các số thứ tự: 4.1, 4.2, 4.3, 4.4, 4.5.1, 5, 6 Mục VI Phần A Biểu mức thu phí, lệ phí áp dụng mức thu phí tương ứng quy định tại Mục VI Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC)
+Bằng 50% mức thu phí quy định tại Mục VI Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí, lệ phí trong lĩnh vực hàng không.
+b) Phí đăng ký giao dịch bảo đảm đối với tàu bay (trừ nội dung thu tại số thứ tự 4 Mục VIII Phần A Biểu mức thu phí, lệ phí áp dụng mức thu phí tương ứng quy định tại Mục VIII Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC)
+Bằng 50% mức thu phí quy định tại Mục VIII Phần A Biểu mức thu phí, lệ phí trong lĩnh vực hàng không ban hành kèm theo Thông tư số 193/2016/TT-BTC.
+4
+a) Lệ phí ra, vào cảng hàng không, sân bay đối với chuyến bay của nước ngoài đến các Cảng hàng không Việt Nam
+Bằng 50% mức thu lệ phí quy định tại khoản 1 Điều 4 Thông tư số 194/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp phí hải quan và lệ phí ra, vào cảng hàng không, sân bay đối với chuyến bay của nước ngoài đến các Cảng hàng không Việt Nam.
+b) Phí hải quan đối với chuyến bay của nước ngoài đến các Cảng hàng không Việt Nam
+Bằng 50% mức thu phí quy định tại khoản 2 Điều 4 Thông tư số 194/2016/TT-BTC.
+5
+Phí khai thác, sử dụng thông tin, dữ liệu khí tượng thủy văn
+Bằng 50% mức thu phí quy định tại Biểu mức thu phí khai thác, sử dụng thông tin, dữ liệu khí tượng thủy văn ban hành kèm theo Thông tư số 197/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí khai thác, sử dụng thông tin, dữ liệu khí tượng thủy văn.
+6
+a) Lệ phí cấp văn bằng bảo hộ, cấp chứng nhận đăng ký hợp đồng chuyển giao quyền sở hữu công nghiệp trong lĩnh vực trồng trọt và giống cây lâm nghiệp
+Bằng 50% mức thu lệ phí quy định tại điểm 1 Mục I Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC ngày 09 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp.
+b) Lệ phí nộp đơn đăng ký bảo hộ quyền sở hữu trí tuệ trong lĩnh vực trồng trọt và giống cây lâm nghiệp
+Bằng 50% mức thu lệ phí quy định tại điểm 2 Mục I Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+c) Lệ phí cấp chứng chỉ hành nghề đại diện sở hữu công nghiệp, công bố, đăng bạ đại diện sở hữu công nghiệp trong lĩnh vực trồng trọt và giống cây lâm nghiệp
+Bằng 50% mức thu lệ phí quy định tại điểm 3 Mục I Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+d) Phí bảo hộ giống cây trồng:
+d.1) Duy trì hiệu lực Bằng bảo hộ giống cây trồng: Từ năm thứ 1 đến năm thứ 3; từ năm thứ 4 đến năm thứ 6; từ năm thứ 7 đến năm thứ 9
+Bằng 50% mức thu phí tương ứng quy định tại điểm 3 Mục III Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+d.2) Duy trì hiệu lực Bằng bảo hộ giống cây trồng: Từ năm thứ 10 đến năm thứ 15; từ năm thứ 16 đến hết thời gian hiệu lực của Bằng bảo hộ
+Bằng 50% mức thu phí tương ứng quy định tại điểm 3 Mục III Biểu phí, lệ phí trong lĩnh vực trồng trọt và giống cây lâm nghiệp ban hành kèm theo Thông tư số 207/2016/TT-BTC.
+7
+a) Phí thẩm định nội dung tài liệu không kinh doanh để cấp giấy phép xuất bản
+Bằng 50% mức thu phí quy định tại khoản 1 Điều 4 Thông tư số 214/2016/TT-BTC ngày 10 tháng 11 năm 2016 của Bộ t</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 156/2025/TT-BTC · hiệu lực 2026-01-01
+3. Bãi bỏ quy định giảm 50% mức thu lệ phí cấp giấy chứng nhận kiểm định an toàn kỹ thuật và bảo vệ môi trường đối với xe ô tô dưới 10 chỗ ngồi tại số thứ tự 30 và bãi bỏ số thứ tự 31 khoản 1 Điều 1 Thông tư số 64/2025/TT-BTC ngày 30 tháng 6 năm 2025 của Bộ trưởng Bộ Tài chính quy định mức thu, miễn một số khoản phí, lệ phí nhằm hỗ trợ cho doanh nghiệp, người dân.
+4. Quy định về lệ phí cấp giấy phép hoạt động xây dựng cho nhà thầu nước ngoài tại khoản 2 và khoản 3 Điều 2 Thông tư này hết hiệu lực thi hành từ ngày 01 tháng 7 năm 2026.
+5. Trường hợp các văn bản liên quan viện dẫn tại Thông tư này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo văn bản sửa đổi, bổ sung hoặc thay thế đó.
+6. Trong quá trình thực hiện, trường hợp có vướng mắc, đề nghị các tổ chức, cá nhân phản ánh kịp thời về Bộ Tài chính để nghiên cứu, hướng dẫn./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Văn phòng Trung ương Đảng và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Quốc hội;
+- Hội đồng Dân tộc;
+- Ủy ban Kinh tế và Tài chính;
+- Văn phòng Chủ tịch nước;
+- Viện kiểm sát nhân dân tối cao;
+- Tòa án nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Cơ quan trung ương của các đoàn thể;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Thuế, Sở Tài chính các tỉnh, thành phố trực thuộc trung ương;
+- Kho bạc Nhà nước các khu vực;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Công báo;
+- Cơ sở dữ liệu quốc gia về pháp luật;
+- Cổng Thông tin điện tử Chính phủ, Bộ Tài chính;
+- Các đơn vị thuộc Bộ Tài chính;
+- Lưu: VT, CST (170b).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(đã ký)
+Cao Anh Tuấn</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5958,7 +7218,6 @@
           <t>2025-08-12 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -5979,9 +7238,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167546</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5992,18 +7248,65 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>unclear: 12/2025/TT-BTP bãi bỏ Điều 1 TT 04/2024 và ban hành bộ mẫu giấy tờ quốc tịch mới, trong đó có Đơn xin nhập quốc tịch Việt Nam; quy định "thay thế mẫu" là quy định sửa đổi, chưa rõ có tính là chuyển chỗ</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>04/2024/TT-BTP · hiệu lực 2024-06-06 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Sửa đổi, bổ sung một số điều của Thông tư số 02/2020/TT-BTP ngày 08/4/2020 của Bộ trưởng Bộ Tư pháp ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch
+3. Thay thế các loại mẫu giấy tờ về quốc tịch tại Điều 4, gồm:
+a) Thay thế mẫu Đơn xin nhập quốc tịch Việt Nam (TP/QT-2020-ĐXNQT.1) bằng Đơn xin nhập quốc tịch Việt Nam (TP/QT-2024-ĐXNQT.1);
+b) Thay thế mẫu Đơn xin nhập quốc tịch Việt Nam dùng cho người giám hộ/người đại diện theo pháp luật làm Đơn xin nhập quốc tịch Việt Nam cho người được giám hộ/được đại diện (TP/QT-2020-ĐXNQT.2) bằng Đơn xin nhập quốc tịch Việt Nam dùng cho người đại diện theo pháp luật làm Đơn xin nhập quốc tịch Việt Nam cho người được đại diện (TP/QT-2024-ĐXNQT.2);
+c) Thay thế mẫu Đơn xin trở lại quốc tịch Việt Nam (TP/QT-2020-ĐXTLQT.1) bằng Đơn xin trở lại quốc tịch Việt Nam (TP/QT-2024-ĐXTLQT.1);
+d) Thay thế mẫu Đơn xin trở lại quốc tịch Việt Nam dùng cho người giám hộ/người đại diện theo pháp luật làm Đơn xin trở lại quốc tịch Việt Nam cho người được giám hộ/được đại diện (TP/QT-2020-ĐXTLQT.2) bằng Đơn xin trở lại quốc tịch Việt Nam dùng cho người đại diện theo pháp luật làm Đơn xin trở lại quốc tịch Việt Nam cho người được đại diện (TP/QT-2024-ĐXTLQT.2);
+đ) Thay thế mẫu Đơn xin thôi quốc tịch Việt Nam (TP/QT-2020-ĐXTQT.1) bằng Đơn xin thôi quốc tịch Việt Nam (TP/QT-2024-ĐXTQT.1);
+e) Thay thế mẫu Đơn xin thôi quốc tịch Việt Nam dùng cho người giám hộ/người đại diện theo pháp luật làm Đơn thôi quốc tịch Việt Nam cho người được giám hộ/được đại diện (TP/QT-2020-ĐXTQT.2) bằng Đơn xin thôi quốc tịch Việt Nam dùng cho người đại diện theo pháp luật làm Đơn xin thôi quốc tịch Việt Nam cho người được đại diện (TP/QT-2024-ĐXTQT.2);
+g) Thay thế mẫu Bản khai lý lịch (TP/QT-2020-BKLL) bằng Bản khai lý lịch (TP/QT-2024-BKLL);
+h) Thay thế mẫu Tờ khai đề nghị đăng ký xác định có quốc tịch Việt Nam (TP/QT-2020-TKXĐCQTVN) bằng Tờ khai đăng ký xác định có quốc tịch Việt Nam (TP/QT-2024-TKXĐCQTVN);
+i) Thay thế mẫu Tờ khai đề nghị cấp Giấy xác nhận có quốc tịch Việt Nam (TP/QT-2020-TKXNCQTVN) bằng Tờ khai đề nghị cấp Giấy xác nhận có quốc tịch Việt Nam (TP/QT-2024-TKXNCQTVN.1);
+k) Thay thế mẫu Tờ khai đề nghị xác nhận là người gốc Việt Nam (TP/QT-2020-TKXNNGVN) bằng Tờ khai đề nghị xác nhận là người gốc Việt Nam (TP/QT-2024-TKXNNGVN.1);
+l) Thay thế mẫu Trích lục đăng ký xác định có quốc tịch Việt Nam (TP/QT-2020-TLXĐCQTVN) bằng Trích lục đăng ký xác định có quốc tịch Việt Nam (TP/QT-2024-TLXĐCQTVN);
+m) Thay thế mẫu Giấy xác nhận có quốc tịch Việt Nam (TP/QT-2020-XNCQTVN) bằng Giấy xác nhận có quốc tịch Việt Nam (TP/QT-2024-XNCQTVN);
+n) Thay thế mẫu Giấy xác nhận là người gốc Việt Nam (TP/QT-2020-XNNGVN) bằng Giấy xác nhận là người gốc Việt Nam (TP/QT-2024-XNNGVN);
+o) Thay thế mẫu Danh sách người được đề nghị giải quyết các việc quốc tịch (TP/QT-2020-DS) bằng Danh sách người được đề nghị giải quyết các việc quốc tịch (TP/QT-2024-DS);</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 12/2025/TT-BTP · hiệu lực 2025-07-01
+3. Bãi bỏ Điều 1 và khoản 2 Điều 3 của Thông tư số 04/2024/TT-BTP ngày 06/6/2024 của Bộ trưởng Bộ Tư pháp sửa đổi, bổ sung một số điều của Thông tư số 02/2020/TT-BTP ngày 08/4/2020 của Bộ trưởng Bộ Tư pháp ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch và Thông tư số 04/2020/TT-BTP ngày 28/5/2020 của Bộ trưởng Bộ Tư pháp quy định chi tiết thi hành một số điều của Luật Hộ tịch và Nghị định số 123/2015/NĐ-CP ngày 15/11/2015 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Hộ tịch.
+4. Cục trưởng Cục Hành chính tư pháp, Thủ trưởng các đơn vị thuộc Bộ Tư pháp, Giám đốc Sở Tư pháp các tỉnh, thành phố và các cơ quan, tổ chức, cá nhân có liên quan chịu trách nhiệm thi hành Thông tư này.
+CHUYỂN TIẾP: Điều 12. Quy định chuyển tiếp
+Các mẫu sổ quốc tịch được ban hành kèm theo Thông tư số 02/2020/TT- BTP ngày 08/4/2020 của Bộ trưởng Bộ Tư pháp ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch, đã được sửa đổi, bổ sung bởi Thông tư số 04/2024/TT-BTP ngày 06/6/2024 của Bộ trưởng Bộ Tư pháp sửa đổi, bổ sung một số điều của Thông tư số 02/2020/TT -BTP ngày 08/4/2020 của Bộ trưởng Bộ Tư pháp ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch và Thông tư số 04/2020/TT -BTP ngày 28/5/2020 của Bộ trưởng Bộ Tư pháp quy định chi tiết thi hành một số điều của Luật Hộ tịch và Nghị định số 123/2015/NĐ-CP ngày 15/11/2015 của Chính phủ quy định chi tiết một số điều và biện pháp thi hành Luật Hộ tịch được tiếp tục sử dụng đến hết ngày 31 tháng 12 năm 2025./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng Chính phủ;
+- Các Phó Thủ tướng Chính phủ;
+- Bộ Tư pháp: Bộ trưởng, các Thứ trưởng;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc Trung ương;
+- Văn phòng TW Đảng và các ban của Đảng;
+- Văn phòng Quốc hội;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Chính phủ;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Viện kiểm sát nhân dân tối cao;
+- Tòa án nhân dân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Sở Tư pháp các tỉnh, thành phố trực thuộc Trung ương;
+- Công báo; Cổng thông tin điện tử Chính phủ; Cổng thông tin điện tử Bộ Tư pháp;
+- Lưu: VT, Cục HCTP.
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Nguyễn Thanh Ngọc</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6056,9 +7359,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=110885</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6069,14 +7369,21 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>111/2015/TT-BTC · hiệu lực 2015-09-15 → nay · lúc thu thập: Còn hiệu lực
+Điều 40. Phí tổ chức phát hành, thanh toán lãi, gốc trái phiếu
+4. Phí tổ chức phát hành, thanh toán lãi, gốc trái phiếu đối với trái phiếu phát hành theo phương thức đại lý được thanh toán cho các tổ chức sau:
+a) Tối đa 0,1% giá trị danh nghĩa trái phiếu phát hành theo phương thức đại lý được chi trả cho đại lý phát hành. Căn cứ vào mức phí tối đa này, tình hình thị trường, mức độ phức tạp của đợt phát hành (khối lượng, kỳ hạn trái phiếu phát hành), nội dung công việc (tổ chức phát hành, thanh toán lãi, gốc trái phiếu), Kho bạc Nhà nước thỏa thuận và thống nhất với đại lý phát hành mức phí tổ chức phát hành, thanh toán lãi, gốc trái phiếu. Mức phí này không bao gồm chi phí in chứng chỉ (nếu có).
+b) 0,02% giá trị lãi, gốc trái phiếu được chi trả cho Trung tâm Lưu ký chứng khoán Việt Nam đối với trường hợp trái phiếu được thanh toán qua Trung tâm Lưu ký chứng khoán Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 15/2018/TT-BTC · hiệu lực 2018-04-01
+2. Bãi bỏ các nội dung quy định tại Điều 17 Thông tư số 99/2015/TT-BTC ngày 29/06/2015 của Bộ Tài chính hướng dẫn về phát hành trái phiếu được Chính phủ bảo lãnh; Điều 19 Thông tư số 100/2015/TT-BTC ngày 29/06/2015 của Bộ Tài chính hướng dẫn về phát hành trái phiếu chính quyền địa phương tại thị trường trong nước; Điều 40 Thông tư số 111/2015/TT-BTC ngày 28/07/2015 của Bộ Tài chính hướng dẫn phát hành trái phiếu Chính phủ tại thị trường trong nước; Điều 12 Thông tư số 150/2011/TT-BTC ngày 09/11/2011 của Bộ Tài chính hướng dẫn hoán đổi trái phiếu Chính phủ; Khoản 2, Khoản 3 và Điểm b, Điểm c Khoản 4 Điều 20 Thông tư liên tịch số 92/2016/TTLT-BTC-NHNN ngày 27/06/2016 của Bộ Tài chính và Ngân hàng Nhà nước Việt Nam hướng dẫn phát hành tín phiếu Kho bạc qua Ngân hàng Nhà nước Việt Nam.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6104,7 +7411,6 @@
           <t>2019-11-05 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -6125,9 +7431,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=110885</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6143,17 +7446,26 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 15/2018/TT-BTC khoản 4 Điều 3 "Chi phí hoạt động đại lý phát hành … tối đa 0,1% … Kho bạc Nhà nước thỏa thuận và thống nhất với đại lý phát hành"; cùng Bộ Tài chính, cùng thông tư bãi bỏ Điều 40 TT 111/2015</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>111/2015/TT-BTC · hiệu lực 2015-09-15 → nay · lúc thu thập: Còn hiệu lực
+Điều 40. Phí tổ chức phát hành, thanh toán lãi, gốc trái phiếu
+4. Phí tổ chức phát hành, thanh toán lãi, gốc trái phiếu đối với trái phiếu phát hành theo phương thức đại lý được thanh toán cho các tổ chức sau:
+a) Tối đa 0,1% giá trị danh nghĩa trái phiếu phát hành theo phương thức đại lý được chi trả cho đại lý phát hành. Căn cứ vào mức phí tối đa này, tình hình thị trường, mức độ phức tạp của đợt phát hành (khối lượng, kỳ hạn trái phiếu phát hành), nội dung công việc (tổ chức phát hành, thanh toán lãi, gốc trái phiếu), Kho bạc Nhà nước thỏa thuận và thống nhất với đại lý phát hành mức phí tổ chức phát hành, thanh toán lãi, gốc trái phiếu. Mức phí này không bao gồm chi phí in chứng chỉ (nếu có).
+b) 0,02% giá trị lãi, gốc trái phiếu được chi trả cho Trung tâm Lưu ký chứng khoán Việt Nam đối với trường hợp trái phiếu được thanh toán qua Trung tâm Lưu ký chứng khoán Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 15/2018/TT-BTC · hiệu lực 2018-04-01
+2. Bãi bỏ các nội dung quy định tại Điều 17 Thông tư số 99/2015/TT-BTC ngày 29/06/2015 của Bộ Tài chính hướng dẫn về phát hành trái phiếu được Chính phủ bảo lãnh; Điều 19 Thông tư số 100/2015/TT-BTC ngày 29/06/2015 của Bộ Tài chính hướng dẫn về phát hành trái phiếu chính quyền địa phương tại thị trường trong nước; Điều 40 Thông tư số 111/2015/TT-BTC ngày 28/07/2015 của Bộ Tài chính hướng dẫn phát hành trái phiếu Chính phủ tại thị trường trong nước; Điều 12 Thông tư số 150/2011/TT-BTC ngày 09/11/2011 của Bộ Tài chính hướng dẫn hoán đổi trái phiếu Chính phủ; Khoản 2, Khoản 3 và Điểm b, Điểm c Khoản 4 Điều 20 Thông tư liên tịch số 92/2016/TTLT-BTC-NHNN ngày 27/06/2016 của Bộ Tài chính và Ngân hàng Nhà nước Việt Nam hướng dẫn phát hành tín phiếu Kho bạc qua Ngân hàng Nhà nước Việt Nam.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6206,9 +7518,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=28073</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6219,14 +7528,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>11/2013/NĐ-CP · hiệu lực 2013-03-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 38. Chuyển giao quản lý hành chính
+2. Sở Nội vụ chủ trì cùng Ủy ban nhân dân cấp huyện chỉ đạo việc chuyển giao quản lý hành chính theo đề nghị của chủ đầu tư và phương án đã được phê duyệt. Trình tự, thủ tục chuyển giao quản lý hành chính được thực hiện theo các quy định của pháp luật về tổ chức và hoạt động của chính quyền địa phương.</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 207/2026/NĐ-CP · hiệu lực 2026-07-01
+3. Bãi bỏ Điều 8 Nghị định số 140/2025/NĐ-CP; Điều 13 Nghị định số 144/2025/NĐ-CP; khoản 4 Điều 9, Điều 38 của Nghị định số 11/2013/NĐ-CP ngày 14 tháng 01 năm 2013 của Chính phủ về quản lý đầu tư phát triển đô thị được sửa đổi, bổ sung tại Nghị định số 35/2023/NĐ-CP ngày 20 tháng 6 năm 2023 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng.
+CHUYỂN TIẾP: Điều 53. Điều khoản chuyển tiếp
+1. Công trình thuộc dự án đầu tư xây dựng đã được quyết định đầu tư trước ngày Nghị định này có hiệu lực thi hành thì loại và cấp của công trình được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư.
+2. Các hồ sơ thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.
+3. Công trình xây dựng khởi công trước ngày Nghị định này có hiệu lực thi hành thuộc đối tượng kiểm tra công tác nghiệm thu theo quy định của Nghị định số 06/2021/NĐ-CP đã được sửa đổi, bổ sung một số điều theo Nghị định số 35/2023/NĐ-CP, Nghị định số 175/2024/NĐ-CP, Nghị định số 14/2026/NĐ-CP, Nghị định số 67/2026/NĐ-CP nhưng không thuộc đối tượng kiểm tra công tác nghiệm thu theo quy định của Nghị định này thì không tiếp tục thực hiện việc kiểm tra công tác nghiệm thu. Chủ đầu tư có trách nhiệm tổ chức quản lý chất lượng, quản lý thi công xây dựng, nghiệm thu hoàn thành công trình đưa vào khai thác, sử dụng theo quy định của Nghị định này và chịu trách nhiệm về kết quả nghiệm thu của mình.
+4. Công trình xây dựng khởi công trước ngày Nghị định này có hiệu lực thi hành thuộc đối tượng kiểm tra công tác nghiệm thu theo quy định của Nghị định số 06/2021/NĐ-CP đã được sửa đổi, bổ sung một số điều theo Nghị định số 35/2023/NĐ-CP, Nghị định số 175/2024/NĐ-CP, Nghị định số 14/2026/NĐ-CP, Nghị định số 67/2026/NĐ-CP và Nghị định này, đã được cơ quan chuyên môn về xây dựng thuộc bộ quản lý công trình xây dựng chuyên ngành kiểm tra công tác nghiệm thu trước ngày Nghị định này có hiệu lực thi hành thì thực hiện như sau:
+a) Cơ quan chuyên môn về xây dựng thuộc bộ quản lý công trình xây dựng chuyên ngành tiếp tục thực hiện kiểm tra công tác nghiệm thu hoàn thành đối với công trình này và các công trình đã khởi công xây dựng thuộc đối tượng kiểm tra còn lại của dự án có công trình được quy định chuyển tiếp tại khoản này, trừ trường hợp công trình đã được cơ quan chuyên môn về xây dựng thuộc Ủy ban nhân dân cấp tỉnh tổ chức kiểm tra;
+b) Trong quá trình cơ quan chuyên môn về xây dựng thuộc bộ quản lý công trình xây dựng chuyên ngành tiếp tục thực hiện kiểm tra công tác nghiệm thu hoàn thành công trình xây dựng nếu phát hiện những vi phạm về chủ trương đầu tư, quy hoạch, đất đai, giấy phép xây dựng, phòng cháy, chữa cháy và các nội dung vi phạm khác thuộc thẩm quyền giải quyết của các cơ quan quản lý nhà nước tại địa phương thì cơ quan chuyên môn về xây dựng thuộc bộ quản lý công trình xây dựng chuyên ngành có trách nhiệm thông báo đến Ủy ban nhân dân cấp tỉnh để chỉ đạo xử lý và giao cơ quan chuyên môn về xây dựng tại địa phương tiếp tục thực hiện việc kiểm tra công tác nghiệm thu đối với các công trình này sau khi đã khắc phục các vi phạm.
+5. Các công trình xây dựng thuộc danh mục các công trình Hội đồng kiểm tra nhà nước về công tác nghiệm thu công trình xây dựng tổ chức kiểm tra năm 2026 đã được Thủ tướng Chính phủ phê duyệt, đã khởi công xây dựng và đã được kiểm tra công tác nghiệm thu thì Hội đồng tiếp tục kiểm tra đối với các công trình này.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6254,7 +7576,6 @@
           <t>2026-08-03 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -6275,9 +7596,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179825</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6288,18 +7606,28 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>unclear: 247/2026/NĐ-CP thay NĐ 49/2020 nhưng không thấy quy định cơ sở giam giữ thông báo hai tháng trước khi phạm nhân hết hạn án; Điều 13 chỉ quy định việc Công an cấp xã sau khi nhận thông báo</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>184/2025/NĐ-CP · hiệu lực 2025-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 14. Sửa đổi, bổ sung một số điều của Nghị định số 49/2020/NĐ-CP ngày 17 tháng 4 năm 2020 của Chính phủ quy định chi tiết thi hành Luật Thi hành án hình sự về tái hòa nhập cộng đồng
+3. Sửa đổi, bổ sung Điều 8 như sau:
+“Điều 8. Thông báo phạm nhân hết hạn chấp hành án phạt tù</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 247/2026/NĐ-CP · hiệu lực 2026-07-01
+2. Nghị định số 49/2020/NĐ-CP ngày 17 tháng 4 năm 2020 của Chính phủ quy định chi tiết thi hành Luật Thi hành án hình sự về tái hòa nhập cộng đồng hết hiệu lực kể từ ngày Nghị định này có hiệu lực thi hành. Điều 14 Nghị định 184/2025/NĐ-CP ngày 01 tháng 7 năm 2025 của Chính phủ quy định phân định thẩm quyền khi tổ chức chính quyền địa phương 02 cấp và sửa đổi, bổ sung một số điều của các Nghị định của Chính phủ trong lĩnh vực an ninh, trật tự hết hiệu lực đối với nội dung sửa đổi, bổ sung Nghị định số 49/2020/NĐ-CP kể từ ngày Nghị định này có hiệu lực thi hành.
+CHUYỂN TIẾP: Điều 27. Quy định chuyển tiếp
+1. Kết quả việc thực hiện tiếp nhận, quản lý, giám sát, giáo dục, giúp đỡ người chấp hành xong hình phạt tù trước thời điểm Nghị định này có hiệu lực được tính liên tục với kết quả tiếp nhận, giúp đỡ khi Nghị định này có hiệu lực thi hành.
+2. Hồ sơ chuyên đề nghiệp vụ lưu giữ hệ thống những tài liệu phản ánh công tác quản lý người tái hòa nhập cộng đồng trước thời điểm Nghị định này có hiệu lực, tiếp tục quản lý, thực hiện đến khi kết thúc hồ sơ theo quy định.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6327,7 +7655,6 @@
           <t>2024-10-23 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -6348,9 +7675,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25417</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6361,18 +7685,36 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>NĐ 08/2014/NĐ-CP không giữ điều kiện có Giấy chứng nhận đầu tư cho tổ chức khoa học và công nghệ có vốn nước ngoài (khoản 5 Điều 4 dẫn khoản 3 Điều 11 Luật KHCN), không chuyển chỗ</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>80/2010/NĐ-CP · hiệu lực 2010-09-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 13. điều kiện thành lập và thủ tục đăng ký hoạt động của tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài
+1. Điều kiện thành lập tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài:
+a) Có Giấy chứng nhận đầu tư của cơ quan quản lý nhà nước có thẩm quyền về đầu tư cấp;
+b) Có điều lệ hoạt động, trong đó quy định lĩnh vực hoạt động phù hợp với quy định của pháp luật Việt Nam;
+c) Có đủ nhân lực khoa học và công nghệ có trình độ chuyên môn thuộc lĩnh vực hoạt động;
+d) Có trụ sở làm việc, cơ sở vật chất – kỹ thuật đủ khả năng triển khai hoạt động nghiên cứu khoa học, thí nghiệm, thử nghiệm, dịch vụ và các hoạt động khác phù hợp với điều lệ hoạt động của tổ chức và quy định của pháp luật Việt Nam;
+đ) Có văn bản của Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương nơi tổ chức đặt trụ sở chính chấp thuận việc thành lập tổ chức khoa học và công nghệ;
+e) Bảo đảm yêu cầu về môi trường theo quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 08/2014/NĐ-CP · hiệu lực 2014-03-15
+2. Nghị định số 81/2002/NĐ-CP ngày 17 tháng 10 năm 2002 của Chính phủ quy định chi tiết thi hành một số điều của Luật khoa học và công nghệ; Nghị định số 201/2004/NĐ-CP ngày 10 tháng 12 năm 2004 của Chính phủ ban hành Quy chế hoạt động khoa học xã hội và nhân văn; các điều 13, 14, 15, 24, 25, 26, 27, 28 và 29 của Nghị định số 80/2010/NĐ-CP ngày 14 tháng 7 năm 2010 của Chính phủ quy định về hợp tác, đầu tư với nước ngoài trong lĩnh vực khoa học và công nghệ; Điều 8 Nghị định số 119/1999/NĐ-CP ngày 18 tháng 9 năm 1999 của Chính phủ về một số chính sách và cơ chế tài chính khuyến khích các doanh nghiệp đầu tư vào hoạt động khoa học và công nghệ; Điều 12 Nghị định số 61/2010/NĐ-CP ngày 04 tháng 6 năm 2010 của Chính phủ chính sách khuyến khích doanh nghiệp đầu tư vào nông nghiệp, nông thôn hết hiệu lực kể từ ngày Nghị định này có hiệu lực.
+CHUYỂN TIẾP: Điều 48. Quy định chuyển tiếp
+1. Đối với những nhiệm vụ khoa học và công nghệ đã được cơ quan có thẩm quyền phê duyệt trước ngày 01 tháng 01 năm 2014 thì tiếp tục thực hiện theo các quy định của Luật khoa học và công nghệ 2000, Nghị định số 81/2002/NĐ-CP ngày 17 tháng 10 năm 2002 của Chính phủ quy định chi tiết thi hành một số điều của Luật khoa học và công nghệ và quyết định phê duyệt.
+2. Các đơn đăng ký hoạt động khoa học và công nghệ nộp cho cơ quan có thẩm quyền cấp Giấy chứng nhận đăng ký hoạt động khoa học và công nghệ trước ngày 01 tháng 01 năm 2014 mà chưa được cấp Giấy chứng nhận đăng ký hoạt động khoa học và công nghệ thì phải hoàn thiện hồ sơ theo quy định tại Nghị định này.
+Đối với tổ chức đã thành lập và đăng ký hoạt động trước ngày Nghị định này có hiệu lực thì trong thời hạn 02 năm kể từ ngày Nghị định này có hiệu lực có trách nhiệm rà soát điều kiện thành lập theo quy định tại Nghị định này, nếu chưa đáp ứng thì phải tự hoàn thiện theo các điều kiện quy định tại Nghị định này.
+3. Đối với tổ chức khoa học và công nghệ thành lập mới mà hồ sơ thành lập chưa được cơ quan có thẩm quyền phê duyệt trước ngày 01 tháng 01 năm 2014 thì phải hoàn thiện hồ sơ và tuân theo trình tự, thủ tục quy định tại Nghị định này.
+4. Tổ chức khoa học và công nghệ là cơ sở giáo dục đại học, trong thời hạn 18 tháng kể từ ngày Nghị định này có hiệu lực phải tiến hành đăng ký hoạt động theo quy định của Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6400,7 +7742,6 @@
           <t>2021-12-11 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -6421,9 +7762,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=25417</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6439,17 +7777,38 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>Chuyển chỗ: NĐ 08/2014/NĐ-CP điểm đ khoản 2 Điều 7 "Trường hợp không được chấp thuận, Bộ Khoa học và Công nghệ gửi thông báo bằng văn bản cho tổ chức, cá nhân trong đó nêu rõ lý do"; cùng Chính phủ, cùng nghị định chấm dứt Điều 15 NĐ 80/2010</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>80/2010/NĐ-CP · hiệu lực 2010-09-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 15. Trình tự, thủ tục ra quyết định thành lập tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài
+2. Trình tự, thủ tục ra quyết định thành lập:
+a) Tổ chức, cá nhân quy định tại khoản 1 Điều 12 Nghị định này gửi 05 (năm) bộ hồ sơ đề nghị thành lập, trong đó có 01 (một) bộ hồ sơ gốc đến Bộ Khoa học và Công nghệ;
+b) Trong thời hạn 10 (mười) ngày làm việc kể từ ngày nhận được hồ sơ quy định tại khoản 1 điều này, Bộ Khoa học và Công nghệ kiểm tra tính hợp lệ của hồ sơ. Trường hợp hồ sơ không hợp lệ, Bộ Khoa học và Công nghệ thông báo bằng văn bản cho tổ chức, cá nhân biết để sửa đổi, bổ sung hồ sơ.
+Trường hợp hồ sơ hợp lệ, Bộ Khoa học và Công nghệ gửi hồ sơ lấy ý kiến của các Bộ, ngành liên quan và Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương nơi tổ chức đặt trụ sở chính;
+c) Trong thời hạn 15 (mười lăm) ngày làm việc kể từ ngày nhận được hồ sơ đề nghị thành lập tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài, các Bộ, ngành liên quan và Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương nơi dự kiến đặt trụ sở có ý kiến bằng văn bản và chịu trách nhiệm về nội dung theo chức năng quản lý của mình;
+d) Trong thời hạn 30 (ba mươi) ngày làm việc kể từ ngày nhận đủ hồ sơ hợp lệ, Bộ Khoa học và Công nghệ lập báo cáo thẩm tra, trình Thủ tướng Chính phủ ra quyết định thành lập tổ chức khoa học và công nghệ 100% vốn đầu tư nước ngoài quy định tại khoản 1 Điều 14 Nghị định này, ra quyết định thành lập tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài quy định tại khoản 2 Điều 14 Nghị định này;
+đ) Trường hợp hồ sơ thành lập tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài không được chấp thuận, Bộ Khoa học và Công nghệ gửi thông báo bằng văn bản cho tổ chức, cá nhân trong đó nêu rõ lý do;
+e) Trong thời hạn 10 (mười) ngày làm việc kể từ ngày ra quyết định thành lập tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài, Bộ Khoa học và Công nghệ sao gửi Quyết định đến Văn phòng Chính phủ, Bộ Kế hoạch và Đầu tư, Bộ Tài chính, Bộ Ngoại giao, Bộ Công an, Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương nơi tổ chức đó đặt trụ sở chính, Bộ, ngành và các cơ quan có liên quan;
+g) Trong thời hạn 30 (ba mươi) ngày làm việc kể từ ngày có quyết định thành lập, tổ chức khoa học và công nghệ có vốn đầu tư nước ngoài tiến hành thủ tục đăng ký hoạt động khoa học và công nghệ theo quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 08/2014/NĐ-CP · hiệu lực 2014-03-15
+2. Nghị định số 81/2002/NĐ-CP ngày 17 tháng 10 năm 2002 của Chính phủ quy định chi tiết thi hành một số điều của Luật khoa học và công nghệ; Nghị định số 201/2004/NĐ-CP ngày 10 tháng 12 năm 2004 của Chính phủ ban hành Quy chế hoạt động khoa học xã hội và nhân văn; các điều 13, 14, 15, 24, 25, 26, 27, 28 và 29 của Nghị định số 80/2010/NĐ-CP ngày 14 tháng 7 năm 2010 của Chính phủ quy định về hợp tác, đầu tư với nước ngoài trong lĩnh vực khoa học và công nghệ; Điều 8 Nghị định số 119/1999/NĐ-CP ngày 18 tháng 9 năm 1999 của Chính phủ về một số chính sách và cơ chế tài chính khuyến khích các doanh nghiệp đầu tư vào hoạt động khoa học và công nghệ; Điều 12 Nghị định số 61/2010/NĐ-CP ngày 04 tháng 6 năm 2010 của Chính phủ chính sách khuyến khích doanh nghiệp đầu tư vào nông nghiệp, nông thôn hết hiệu lực kể từ ngày Nghị định này có hiệu lực.
+CHUYỂN TIẾP: Điều 48. Quy định chuyển tiếp
+1. Đối với những nhiệm vụ khoa học và công nghệ đã được cơ quan có thẩm quyền phê duyệt trước ngày 01 tháng 01 năm 2014 thì tiếp tục thực hiện theo các quy định của Luật khoa học và công nghệ 2000, Nghị định số 81/2002/NĐ-CP ngày 17 tháng 10 năm 2002 của Chính phủ quy định chi tiết thi hành một số điều của Luật khoa học và công nghệ và quyết định phê duyệt.
+2. Các đơn đăng ký hoạt động khoa học và công nghệ nộp cho cơ quan có thẩm quyền cấp Giấy chứng nhận đăng ký hoạt động khoa học và công nghệ trước ngày 01 tháng 01 năm 2014 mà chưa được cấp Giấy chứng nhận đăng ký hoạt động khoa học và công nghệ thì phải hoàn thiện hồ sơ theo quy định tại Nghị định này.
+Đối với tổ chức đã thành lập và đăng ký hoạt động trước ngày Nghị định này có hiệu lực thì trong thời hạn 02 năm kể từ ngày Nghị định này có hiệu lực có trách nhiệm rà soát điều kiện thành lập theo quy định tại Nghị định này, nếu chưa đáp ứng thì phải tự hoàn thiện theo các điều kiện quy định tại Nghị định này.
+3. Đối với tổ chức khoa học và công nghệ thành lập mới mà hồ sơ thành lập chưa được cơ quan có thẩm quyền phê duyệt trước ngày 01 tháng 01 năm 2014 thì phải hoàn thiện hồ sơ và tuân theo trình tự, thủ tục quy định tại Nghị định này.
+4. Tổ chức khoa học và công nghệ là cơ sở giáo dục đại học, trong thời hạn 18 tháng kể từ ngày Nghị định này có hiệu lực phải tiến hành đăng ký hoạt động theo quy định của Nghị định này.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6502,9 +7861,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127947</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6515,18 +7871,24 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
           <t>21/2025/TT-BVHTTDL bãi bỏ khoản 6 Điều 3 TT 10/2017 để cắt giảm điều kiện, không có quy định kế thừa</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>10/2017/TT-BVHTTDL · hiệu lực 2018-02-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Cơ sở vật chất, trang thiết bị tập luyện
+6. Có bảng nội quy bao gồm những nội dung chủ yếu sau: Đối tượng tham gia tập luyện, trang phục tập luyện, giờ tập luyện, biện pháp đảm bảo an toàn khi tập luyện.</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 21/2025/TT-BVHTTDL · hiệu lực 2025-12-26
+Điều 5. Bãi bỏ khoản 4 và khoản 6 Điều 3 Thông tư số 10/2017/TT- BVHTTDL ngày 29 tháng 12 năm 2017 của Bộ trưởng Bộ Văn hóa, Thể thao và Du lịch quy định về cơ sở vật chất, trang thiết bị và tập huấn nhân viên chuyên môn đối với môn Taekwondo.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6579,9 +7941,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178271</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6592,18 +7951,53 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
           <t>32/2026/NĐ-CP bãi bỏ khoản 4 Điều 7 NĐ 131/2025, không thấy thẩm quyền của Chủ tịch Ủy ban nhân dân cấp xã trong nghị định này</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>131/2025/NĐ-CP · hiệu lực 2025-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 7. Thẩm quyền của Chủ tịch Ủy ban nhân dân cấp xã
+4. Trình Chủ tịch Ủy ban nhân dân cấp tỉnh quyết định hỗ trợ kinh phí, vật tư và nguồn lực khi yêu cầu phòng, chống dịch bệnh động vật vượt quá khả năng của địa phương theo quy định tại điểm d khoản 4 Điều 27, điểm d khoản 4 Điều 35 Luật Thú y.</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 32/2026/NĐ-CP · hiệu lực 2026-01-21
+3. Bãi bỏ Điều 5, các khoản 1, 2, 3, 4 và 5 Điều 6, các khoản 1, 2, 3, 4 và 5 Điều 7 Nghị định số 131/2025/NĐ-CP ngày 12 tháng 6 năm 2025 của Chính phủ quy định phân định thẩm quyền của chính quyền địa phương 02 cấp trong lĩnh vực quản lý nhà nước của Bộ Nông nghiệp và Môi trường.
+CHUYỂN TIẾP: Điều 35. Điều khoản chuyển tiếp
+1. Văn bản quy phạm pháp luật, văn bản hành chính của cơ quan nhà nước, người có thẩm quyền ban hành trước ngày Nghị định này có hiệu lực thi hành thì tiếp tục có hiệu lực thi hành cho đến khi cơ quan nhà nước, người có thẩm quyền ban hành văn bản thay thế theo Nghị định này.
+2. Văn bản, giấy phép, giấy chứng nhận là kết quả giải quyết thủ tục hành chính đã được cơ quan, người có thẩm quyền ban hành trước ngày Nghị định này có hiệu lực thi hành và chưa hết hiệu lực hoặc chưa hết thời hạn thì tiếp tục được áp dụng, sử dụng theo thời hạn ghi trên văn bản, giấy phép, giấy chứng nhận đó cho đến khi hết thời hạn. Trường hợp tổ chức, cá nhân có nhu cầu được sửa đổi, bổ sung, cấp lại, gia hạn văn bản, giấy phép, giấy chứng nhận thì gửi văn bản đề nghị đến cơ quan, người có thẩm quyền tại Nghị định này giải quyết.
+3. Tổ chức, cá nhân đã được cơ quan nhà nước, người có thẩm quyền giải quyết thủ tục hành chính trước ngày Nghị định này có hiệu lực mà chưa có kết quả giải quyết thủ tục hành chính thì tiếp tục được giải quyết theo quy định của pháp luật tại thời điểm tiếp nhận; trừ trường hợp tổ chức, cá nhân đề nghị thực hiện theo quy định của Nghị định này.
+4. Cơ quan được Bộ trưởng Bộ Nông nghiệp và Môi trường giao giải quyết thủ tục hành chính trong lĩnh vực chăn nuôi và thú y thực hiện kiểm tra, giảm kiểm tra chất lượng thức ăn chăn nuôi nhập khẩu đang thực hiện trực tuyến trên Cổng thông tin Một cửa quốc gia đến hết ngày 31 tháng 12 năm 2026.
+Chủ tịch Ủy ban nhân dân cấp tỉnh tổ chức thực hiện kiểm tra, giảm kiểm tra chất lượng thức ăn chăn nuôi nhập khẩu từ ngày 01 tháng 01 năm 2027. Trường hợp Ủy ban nhân dân cấp tỉnh có hệ thống chuyên ngành kết nối Cổng thông tin Một cửa quốc gia để kiểm tra, giảm kiểm tra chất lượng thức ăn chăn nuôi nhập khẩu trước ngày 31 tháng 12 năm 2026 thì Chủ tịch Ủy ban nhân dân cấp tỉnh tổ chức kiểm tra, giảm kiểm tra chất lượng thức ăn chăn nuôi nhập khẩu kể từ ngày kết nối.
+5. Cơ quan được Bộ trưởng Bộ Nông nghiệp và Môi trường giao giải quyết thủ tục hành chính trong lĩnh vực chăn nuôi và thú y thẩm định để công bố, công bố lại, thay đổi thông tin sản phẩm thức ăn bổ sung đang thực hiện trực tuyến trên Cổng thông tin điện tử của Bộ Nông nghiệp và Môi trường đến hết ngày 31 tháng 12 năm 2026.
+Chủ tịch Ủy ban nhân dân cấp tỉnh tổ chức thẩm định để công bố, công bố lại, thay đổi thông tin sản phẩm thức ăn bổ sung từ ngày 01 tháng 01 năm 2027. Trường hợp Ủy ban nhân dân cấp tỉnh có hệ thống chuyên ngành kết nối Cổng thông tin điện tử của Bộ Nông nghiệp và Môi trường để công bố, công bố lại, thay đổi thông tin sản phẩm thức ăn bổ sung trước ngày 31 tháng 12 năm 2026 thì Chủ tịch Ủy ban nhân dân cấp tỉnh tổ chức thẩm định để công bố, công bố lại, thay đổi thông tin sản phẩm thức ăn bổ sung kể từ ngày kết nối.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các tổ chức chính trị - xã hội;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT, các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, NN (2).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+Trần Hồng Hà</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6656,9 +8050,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98444</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6674,17 +8065,51 @@
           <t>question_ambiguous</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
           <t>Điều 4 TTLT 21/2015 liệt kê ba loại thành tích (khoản 1 bài báo, sách; khoản 2 giải thưởng; khoản 3 sáng chế), câu hỏi hỏi chung "thành tích … được xác định như thế nào" nên khớp cả điều, đáp án chỉ là khoản 1</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>21/2015/TTLT-BKHCN-BNV-BTC · hiệu lực 2016-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Thành tích khoa học và công nghệ để xem xét áp dụng chính sách sử dụng, trọng dụng
+1. Bài báo khoa học đã được công bố trên tạp chí khoa học uy tín trong nước và quốc tế; báo cáo khoa học tại hội thảo khoa học quốc gia và quốc tế được in trong kỷ yếu hội thảo đã được xuất bản; sách chuyên khảo đã được xuất bản theo quy định của pháp luật.
+Yêu cầu về bài báo khoa học đã được công bố, sách chuyên khảo đã được xuất bản thực hiện theo quy định tại Điều 2, Điều 3 Thông tư số 16/2009/TT-BGDĐT ngày 17 tháng 7 năm 2009 của Bộ Giáo dục và Đào tạo quy định chi tiết việc xét công nhận đạt tiêu chuẩn, bổ nhiệm, miễn nhiệm chức danh giáo sư, phó giáo sư.
+Danh mục tạp chí khoa học uy tín trong nước và quốc tế được xác định theo Quyết định phê duyệt danh mục các tạp chí khoa học chuyên ngành được tính điểm công trình khoa học quy đổi khi xét công nhận đạt tiêu chuẩn chức danh giáo sư, phó giáo sư của Hội đồng chức danh giáo sư nhà nước hằng năm.</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 05/2023/TT-BKHCN · hiệu lực 2023-07-07
+a) Điều 4 về Thành tích khoa học và công nghệ để xem xét áp dụng chính sách sử dụng, trọng dụng;
+b) Điều 5, Điều 6, Điều 7, Điều 8, Điều 9, Điều 10, Điều 12, Điều 13, Điều 14 và Điều 15 của Chương II về chính sách ưu đãi trong sử dụng cá nhân hoạt động khoa học và công nghệ;
+c) Điều 17, Điều 18, Điều 19, Điều 20, Điều 21, Điều 22 và Điều 24 của Chương III về trọng dụng nhà khoa học đầu ngành.
+3. Trường hợp các văn bản quy phạm pháp luật được dẫn chiếu tại Thông tư này được sửa đổi, bổ sung hoặc thay thế bằng các văn bản quy phạm pháp luật mới thì áp dụng theo các văn bản mới.
+4. Trong quá trình thực hiện nếu có khó khăn, vướng mắc, đề nghị phản ánh về Bộ Khoa học và Công nghệ để tổng hợp và xem xét, giải quyết./.
+Nơi nhận:
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc Chính phủ;
+- UBND tỉnh, thành phố trực thuộc TW;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Trung ương và các Ban của TW Đảng;
+- Văn phòng Quốc hội;
+- Văn phòng Chủ tịch nước;
+- Viện Kiểm sát nhân dân tối cao;
+- Tòa án nhân dân;
+- Kiểm toán Nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ủy ban TW Mặt trận Tổ quốc Việt Nam;
+- Cơ quan TW của các Đoàn thể;
+- Cục Kiểm tra văn bản QPPL (Bộ Tư pháp);
+- Công báo; Website Chính phủ; Website Bộ Khoa học và Công nghệ;
+- Các đơn vị thuộc Bộ Khoa học và Công nghệ;
+- Lưu: VT, TCCB.
+BỘ TRƯỞNG
+(Đã ký)
+Trần Văn Tùng</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6712,7 +8137,6 @@
           <t>2024-03-27 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -6733,9 +8157,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=98444</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6751,17 +8172,51 @@
           <t>question_ambiguous</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
           <t>Như dòng trước. 05/2023/TT-BKHCN do một bộ ban hành thay ba bộ liên tịch (yếu tố 6 không đạt), không chuyển chỗ</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>21/2015/TTLT-BKHCN-BNV-BTC · hiệu lực 2016-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Thành tích khoa học và công nghệ để xem xét áp dụng chính sách sử dụng, trọng dụng
+1. Bài báo khoa học đã được công bố trên tạp chí khoa học uy tín trong nước và quốc tế; báo cáo khoa học tại hội thảo khoa học quốc gia và quốc tế được in trong kỷ yếu hội thảo đã được xuất bản; sách chuyên khảo đã được xuất bản theo quy định của pháp luật.
+Yêu cầu về bài báo khoa học đã được công bố, sách chuyên khảo đã được xuất bản thực hiện theo quy định tại Điều 2, Điều 3 Thông tư số 16/2009/TT-BGDĐT ngày 17 tháng 7 năm 2009 của Bộ Giáo dục và Đào tạo quy định chi tiết việc xét công nhận đạt tiêu chuẩn, bổ nhiệm, miễn nhiệm chức danh giáo sư, phó giáo sư.
+Danh mục tạp chí khoa học uy tín trong nước và quốc tế được xác định theo Quyết định phê duyệt danh mục các tạp chí khoa học chuyên ngành được tính điểm công trình khoa học quy đổi khi xét công nhận đạt tiêu chuẩn chức danh giáo sư, phó giáo sư của Hội đồng chức danh giáo sư nhà nước hằng năm.</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 05/2023/TT-BKHCN · hiệu lực 2023-07-07
+a) Điều 4 về Thành tích khoa học và công nghệ để xem xét áp dụng chính sách sử dụng, trọng dụng;
+b) Điều 5, Điều 6, Điều 7, Điều 8, Điều 9, Điều 10, Điều 12, Điều 13, Điều 14 và Điều 15 của Chương II về chính sách ưu đãi trong sử dụng cá nhân hoạt động khoa học và công nghệ;
+c) Điều 17, Điều 18, Điều 19, Điều 20, Điều 21, Điều 22 và Điều 24 của Chương III về trọng dụng nhà khoa học đầu ngành.
+3. Trường hợp các văn bản quy phạm pháp luật được dẫn chiếu tại Thông tư này được sửa đổi, bổ sung hoặc thay thế bằng các văn bản quy phạm pháp luật mới thì áp dụng theo các văn bản mới.
+4. Trong quá trình thực hiện nếu có khó khăn, vướng mắc, đề nghị phản ánh về Bộ Khoa học và Công nghệ để tổng hợp và xem xét, giải quyết./.
+Nơi nhận:
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc Chính phủ;
+- UBND tỉnh, thành phố trực thuộc TW;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Trung ương và các Ban của TW Đảng;
+- Văn phòng Quốc hội;
+- Văn phòng Chủ tịch nước;
+- Viện Kiểm sát nhân dân tối cao;
+- Tòa án nhân dân;
+- Kiểm toán Nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ủy ban TW Mặt trận Tổ quốc Việt Nam;
+- Cơ quan TW của các Đoàn thể;
+- Cục Kiểm tra văn bản QPPL (Bộ Tư pháp);
+- Công báo; Website Chính phủ; Website Bộ Khoa học và Công nghệ;
+- Các đơn vị thuộc Bộ Khoa học và Công nghệ;
+- Lưu: VT, TCCB.
+BỘ TRƯỞNG
+(Đã ký)
+Trần Văn Tùng</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6789,7 +8244,6 @@
           <t>2026-08-05 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -6810,9 +8264,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=58638</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6823,18 +8274,40 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>86/2026/TT-BTC bãi bỏ Điều 132 TT 38/2015; không thấy trình tự xử lý số tiền còn thừa sau bù trừ từ tài khoản tiền gửi trong phần quy định của thông tư này</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>38/2015/TT-BTC · hiệu lực 2015-04-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 132. Xử lý số tiền thuế, tiền chậm nộp, tiền phạt nộp thừa sau khi ban hành quyết định hoàn tiền thuế, tiền chậm nộp, tiền phạt nộp thừa
+1. Trường hợp nguồn tiền hoàn tiền thuế, tiền chậm nộp, tiền phạt nộp thừa từ tài khoản tiền gửi (trước đây là tài khoản tạm thu), cơ quan hải quan nơi người nộp thuế có số tiền thuế được hoàn, tiền thuế, tiền chậm nộp, tiền phạt nộp thừa phải đối chiếu trên hệ thống kế toán tập trung và xử lý theo trình tự như sau:
+a) Trường hợp người nộp thuế không còn nợ tiền thuế, tiền chậm nộp, tiền phạt thì thực hiện hoàn trả tiền thuế, tiền chậm nộp, tiền phạt cho người nộp thuế theo đúng quy định;
+b) Trường hợp người nộp thuế phải nộp tờ khai hải quan giấy trong hồ sơ hoàn thuế, khi bù trừ vào số tiền thuế, tiền chậm nộp, tiền phạt phải nộp lần sau của người nộp thuế, cơ quan hải quan đóng dấu trên tờ khai hải quan (bản gốc người khai hải quan lưu và bản gốc lưu tại đơn vị hải quan) được trừ thuế với nội dung "Số tiền thuế được trừ... đồng, theo Quyết định hoàn tiền thuế, tiền chậm nộp, tiền phạt nộp thừa số... ngày... tháng... năm... của... và Quyết định khấu trừ số... ngày... tháng... năm... của..."; đồng thời đóng dấu ghi rõ số tiền thuế, tiền chậm nộp, tiền phạt đã trừ và số, ngày, tháng, năm của tờ khai hải quan được bù trừ lên bản chính quyết định hoàn thuế, các tờ khai hải quan được hoàn thuế có số tiền thuế, tiền chậm nộp, tiền phạt nộp thừa, chứng từ nộp thuế của tờ khai hải quan được hoàn thuế để theo dõi (Mẫu dấu thực hiện theo mẫu số 18/MDHT/TXNK Phụ lục VI ban hành kèm theo Thông tư này);
+c) Trường hợp người nộp thuế còn nợ tiền thuế, tiền chậm nộp, tiền phạt của các lô hàng cùng loại hình nhập khẩu phải nộp vào tài khoản tiền gửi, cơ quan hải quan thực hiện bù trừ số tiền thuế, tiền chậm nộp, tiền phạt nộp thừa được hoàn với số tiền thuế, tiền chậm nộp hoặc tiền phạt người nộp thuế còn nợ;
+d) Trường hợp người nộp thuế còn nợ tiền thuế, tiền chậm nộp, tiền phạt của các lô hàng không cùng loại hình nhập khẩu phải nộp ngân sách, cơ quan hải quan viết giấy nộp tiền vào ngân sách nhà nước hoặc giấy nộp tiền vào tài khoản để nộp thay người nộp thuế theo đúng số tiền thuế, tiền chậm nộp, tiền phạt người nộp thuế còn nợ;
+đ) Trường hợp sau khi đã thực hiện bù trừ như nêu trên mà còn thừa, cơ quan hải quan nơi người nộp thuế có số tiền thuế, tiền chậm nộp, tiền phạt được hoàn, nộp thừa làm thủ tục hoàn trả số tiền thuế, tiền chậm nộp, tiền phạt còn lại cho người nộp thuế;
+e) Trường hợp người nộp thuế đề nghị không hoàn trả lại tiền thuế được hoàn hoặc tiền thuế, tiền chậm nộp, tiền phạt còn thừa sau khi đã thực hiện thanh toán hết các khoản nợ theo thứ tự thanh toán tiền thuế mà đề nghị cho bù trừ vào số tiền thuế phát sinh của hàng hóa xuất khẩu, nhập khẩu lần sau, cơ quan hải quan nơi người nộp thuế có số tiền thuế được hoàn, tiền thuế, tiền chậm nộp, tiền phạt nộp thừa thực hiện bù trừ theo đề nghị của người nộp thuế như hướng dẫn tại điểm c, d khoản này;
+g) Khi hoàn thuế, bù trừ vào số tiền thuế, tiền chậm nộp, tiền phạt phải nộp lần sau của người nộp thuế, cơ quan hải quan cập nhật quyết định hoàn thuế, các tờ khai hải quan được hoàn thuế có số tiền thuế, tiền chậm nộp, tiền phạt nộp thừa, chứng từ nộp thuế của tờ khai hải quan được hoàn thuế để theo dõi trên hệ thống kế toán tập trung.</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 86/2026/TT-BTC · hiệu lực 2026-07-01
+a) Điều 104, Điều 105, Điều 131, Điều 132, Điều 134, Điều 135, Điều 140 Thông tư số 38/2015/TT-BTC;
+b) Khoản 64, khoản 65, khoản 67, khoản 68, khoản 71 Điều 1 Thông tư số 39/2018/TT-BTC;
+c) Khoản 58, khoản 60, khoản 61 Điều 1 Thông tư số 121/2025/TT-BTC.
+4. Trường hợp các văn bản quy phạm pháp luật viện dẫn tại Thông tư này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo văn bản được sửa đổi, bổ sung hoặc thay thế đó.
+CHUYỂN TIẾP: Điều 44. Điều khoản chuyển tiếp
+1. Trường hợp hồ sơ miễn thuế, giảm thuế, hoàn thuế, không thu thuế, không chịu thuế, xử lý tiền thuế, khoản thu khác, tiền chậm nộp, tiền phạt nộp thừa, gia hạn nộp thuế, miễn tiền chậm nộp, nộp dần tiền thuế nợ, xác nhận hoàn thành nghĩa vụ nộp thuế, khoanh tiền thuế nợ, xóa tiền thuế nợ, người nộp thuế đã nộp trước ngày Thông tư này có hiệu lực thì tiếp tục thực hiện theo quy định tại văn bản quy phạm pháp luật có hiệu lực tại thời điểm nộp hồ sơ.
+2. Trường hợp kiểm tra đã có kế hoạch kiểm tra nhưng chưa thực hiện kiểm tra thì thực hiện kiểm tra thuế theo quy định tại Thông tư này. Đối với trường hợp đang thực hiện kiểm tra thì tiếp tục thực hiện theo quy định tại văn bản quy phạm pháp luật có hiệu lực tại thời điểm ban hành quyết định kiểm tra.
+3. Trường hợp tổ chức, cá nhân nhận chuyển nhượng dự án trước ngày Thông tư này có hiệu lực nhưng chưa thực hiện đăng ký tờ khai hải quan mới theo quy định tại điểm d khoản 9 Điều 28 Thông tư này thì phải hoàn thành việc đăng ký tờ khai hải quan mới trước ngày 31/12/2026.
+Quá thời hạn quy định tại khoản này, tổ chức cá nhân nhận chuyển nhượng không thực hiện đăng ký tờ khai hải quan mới thì cơ quan hải quan tiến hành xử phạt theo quy định.
+4. Trường hợp dự án đã kết thúc nhập khẩu hàng hóa theo Danh mục miễn thuế hoặc Danh mục miễn thuế hết hiệu lực, tổ chức, cá nhân thực hiện thông báo tình hình sử dụng hàng hóa miễn thuế gửi cơ quan hải quan nơi tiếp nhận Danh mục miễn thuế theo quy định tại điểm b.2 khoản 1 Điều 29 Thông tư này, thời điểm thực hiện thông báo tình hình sử dụng hàng hóa miễn thuế cho cơ quan hải quan tính từ năm tài chính Thông tư này có hiệu lực.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6887,9 +8360,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=125654</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6905,17 +8375,57 @@
           <t>question_leaks</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
           <t>Câu hỏi nêu khung phạt và diễn đạt lại gần đủ đáp án (đánh giá đối với lĩnh vực chưa được đăng ký)</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>119/2017/NĐ-CP · hiệu lực 2017-12-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 21. Vi phạm quy định về hoạt động đánh giá sự phù hợp
+1. Phạt tiền từ 30.000.000 đồng đến 40.000.000 đồng đối với một trong các hành vi sau đây:
+a) Thực hiện hoạt động đánh giá sự phù hợp khi chưa được cơ quan có thẩm quyền cấp đăng ký hoạt động theo quy định;
+b) Thực hiện đánh giá sự phù hợp ngoài lĩnh vực đã đăng ký;
+c) Không thực hiện việc báo cáo định kỳ hoặc đột xuất khi có yêu cầu của cơ quan có thẩm quyền về kết quả hoạt động đánh giá sự phù hợp đã đăng ký;
+d) Không thông báo trên các phương tiện thông tin đại chúng về việc cấp, cấp lại, mở rộng, thu hẹp phạm vi hoặc tạm đình chỉ, thu hồi giấy chứng nhận sự phù hợp và quyền sử dụng dấu hợp chuẩn, dấu hợp quy.</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 126/2021/NĐ-CP · hiệu lực 2022-01-01
+2. Bãi bỏ điểm c khoản 3 Điều 3; điểm g, điểm h khoản 3, khoản 5 Điều 19; khoản 3 Điều 20; điểm a, điểm b khoản 1 Điều 21; điểm b khoản 3 Điều 24; Điều 28; khoản 5, khoản 6 Điều 31; điểm đ, điểm g khoản 1 Điều 32 Nghị định số 119/2017/NĐ-CP.
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+a) Đối với hành vi vi phạm hành chính trong lĩnh vực sở hữu công nghiệp; tiêu chuẩn, đo lường và chất lượng sản phẩm, hàng hóa; hoạt động khoa học và công nghệ, chuyển giao công nghệ; năng lượng nguyên tử xảy ra trước ngày Nghị định này có hiệu lực, sau đó mới bị phát hiện hoặc đang xem xét, giải quyết mà Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn thì áp dụng các quy định tại Nghị định này;
+b) Đối với quyết định xử phạt vi phạm hành chính đã được ban hành hoặc đã được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 99/2013/NĐ-CP ngày 29 tháng 8 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực sở hữu công nghiệp, Nghị định số 119/2017/NĐ-CP ngày 01 tháng 11 năm 2017 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực tiêu chuẩn, đo lường và chất lượng sản phẩm, hàng hóa, Nghị định số 51/2019/NĐ-CP ngày 13 tháng 6 năm 2019 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động khoa học và công nghệ, chuyển giao công nghệ, Nghị định số 107/2013/NĐ-CP ngày 20 tháng 9 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực năng lượng nguyên tử.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách Xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, KGVX (2b).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Vũ Đức Đam</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6968,9 +8478,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=125654</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6986,17 +8493,57 @@
           <t>question_leaks,gold_wrong</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
           <t>Như dòng trước. Chuyển chỗ: 126/2021/NĐ-CP (khoản 38 Điều 2) bổ sung điểm d khoản 3 Điều 21 NĐ 119/2017 "Thực hiện đánh giá sự phù hợp ngoài lĩnh vực đã đăng ký", cùng nghị định bãi bỏ điểm b khoản 1 Điều 21; chỉ đổi mức phạt</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>119/2017/NĐ-CP · hiệu lực 2017-12-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 21. Vi phạm quy định về hoạt động đánh giá sự phù hợp
+1. Phạt tiền từ 30.000.000 đồng đến 40.000.000 đồng đối với một trong các hành vi sau đây:
+a) Thực hiện hoạt động đánh giá sự phù hợp khi chưa được cơ quan có thẩm quyền cấp đăng ký hoạt động theo quy định;
+b) Thực hiện đánh giá sự phù hợp ngoài lĩnh vực đã đăng ký;
+c) Không thực hiện việc báo cáo định kỳ hoặc đột xuất khi có yêu cầu của cơ quan có thẩm quyền về kết quả hoạt động đánh giá sự phù hợp đã đăng ký;
+d) Không thông báo trên các phương tiện thông tin đại chúng về việc cấp, cấp lại, mở rộng, thu hẹp phạm vi hoặc tạm đình chỉ, thu hồi giấy chứng nhận sự phù hợp và quyền sử dụng dấu hợp chuẩn, dấu hợp quy.</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 126/2021/NĐ-CP · hiệu lực 2022-01-01
+2. Bãi bỏ điểm c khoản 3 Điều 3; điểm g, điểm h khoản 3, khoản 5 Điều 19; khoản 3 Điều 20; điểm a, điểm b khoản 1 Điều 21; điểm b khoản 3 Điều 24; Điều 28; khoản 5, khoản 6 Điều 31; điểm đ, điểm g khoản 1 Điều 32 Nghị định số 119/2017/NĐ-CP.
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+a) Đối với hành vi vi phạm hành chính trong lĩnh vực sở hữu công nghiệp; tiêu chuẩn, đo lường và chất lượng sản phẩm, hàng hóa; hoạt động khoa học và công nghệ, chuyển giao công nghệ; năng lượng nguyên tử xảy ra trước ngày Nghị định này có hiệu lực, sau đó mới bị phát hiện hoặc đang xem xét, giải quyết mà Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn thì áp dụng các quy định tại Nghị định này;
+b) Đối với quyết định xử phạt vi phạm hành chính đã được ban hành hoặc đã được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 99/2013/NĐ-CP ngày 29 tháng 8 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực sở hữu công nghiệp, Nghị định số 119/2017/NĐ-CP ngày 01 tháng 11 năm 2017 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực tiêu chuẩn, đo lường và chất lượng sản phẩm, hàng hóa, Nghị định số 51/2019/NĐ-CP ngày 13 tháng 6 năm 2019 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động khoa học và công nghệ, chuyển giao công nghệ, Nghị định số 107/2013/NĐ-CP ngày 20 tháng 9 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực năng lượng nguyên tử.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách Xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, KGVX (2b).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Vũ Đức Đam</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7024,7 +8571,6 @@
           <t>2024-09-29 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -7045,9 +8591,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92234</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7063,17 +8606,54 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 08/2017/TT-BLĐTBXH khoản 1 Điều 5 (Mục 1, sơ cấp, Tiêu chuẩn 3 về Trình độ tin học), cùng chuẩn theo TT 03/2014/TT-BTTTT, thêm "hoặc tương đương trở lên"; cùng Bộ, cùng thông tư bãi bỏ Chương II TT 40/2015. Tin học thành tiêu chuẩn riêng, không còn thuộc "kiến thức chuyên môn" như câu hỏi nêu</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>40/2015/TT-BLĐTBXH · hiệu lực 2015-12-05 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 6. Tiêu chí 2: Năng lực chuyên môn
+1. Tiêu chuẩn 1: Kiến thức chuyên môn
+a) Có bằng tốt nghiệp trung cấp trở lên, chuyên ngành phù hợp với nghề giảng dạy; Có kiến thức về môn học, mô-đun liên quan và hiểu biết về thực tiễn sản xuất của nghề;
+b) Có trình độ ngoại ngữ thông dụng tối thiểu Bậc 1 theo quy định tại Thông tư số 01/2014/TT-BGDĐT ngày 24/01/2014 của Bộ Giáo dục và Đào tạo Ban hành Khung năng lực ngoại ngữ 6 bậc dùng cho Việt Nam hoặc tương đương;
+c) Có trình độ tin học đạt chuẩn kỹ năng sử dụng công nghệ thông tin cơ bản theo quy định tại Thông tư số 03/2014/TT-BTTTT ngày 11/3/2014 của Bộ Thông tin và Truyền thông Quy định Chuẩn kỹ năng sử dụng Công nghệ thông tin;</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 08/2017/TT-BLĐTBXH · hiệu lực 2017-05-01
+3. Bãi bỏ Chương II Thông tư số 40/2015/TT-BLĐTBXH ngày 20/10/2015 của Bộ trưởng Bộ Lao động - Thương binh và Xã hội quy định chuẩn về chuyên môn, nghiệp vụ và chế độ làm việc của nhà giáo dạy trình độ sơ cấp.
+4. Trong quá trình thực hiện, nếu có vướng mắc, đề nghị phản ánh về Bộ Lao động - Thương binh và Xã hội để được hướng dẫn./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội, Hội đồng dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Chính phủ;
+- Tòa án nhân dân tối cao;
+- Viện Kiểm sát nhân dân tối cao;
+- Kiểm toán Nhà nước;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc Chính phủ;
+- Cơ quan Trung ương của các đoàn thể;
+- HĐND, UBND, Sở LĐTBXH các tỉnh, thành phố trực thuộc Trung ương;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cục Kiểm tra văn bản QPPL (Bộ Tư pháp);
+- Công báo;
+- Cổng TTĐT Chính phủ;
+- Cổng TTĐT Bộ LĐTBXH;
+- Lưu: VT, TCGDNN.
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Doãn Mậu Diệp
+CHUYỂN TIẾP: Điều 55. Điều khoản chuyển tiếp
+Nhà giáo dạy thực hành hoặc dạy tích hợp trình độ trung cấp, cao đẳng mà chưa đáp ứng chuẩn về kỹ năng nghề quy định tại Thông tư này, phải hoàn thiện để đáp ứng quy định của Thông tư này trước ngày 31 tháng 12 năm 2019.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7101,7 +8681,6 @@
           <t>2026-03-01 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -7122,9 +8701,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92234</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7140,17 +8716,53 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 08/2017/TT-BLĐTBXH khoản 1 Điều 9 (Mục 1, nhà giáo dạy trình độ sơ cấp) "Lựa chọn và thiết kế các công cụ kiểm tra, đánh giá kết quả học tập của người học phù hợp với mô-đun được phân công giảng dạy"; cùng Bộ, cùng thông tư bãi bỏ Chương II TT 40/2015. Bỏ cụm "kiến thức, kỹ năng và thái độ", "môn học, học phần": người audit xem lại yếu tố 1</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>40/2015/TT-BLĐTBXH · hiệu lực 2015-12-05 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 7. Tiêu chí 3: Năng lực sư phạm
+4. Tiêu chuẩn 4: Kiểm tra, đánh giá kết quả học tập của người học
+a) Lựa chọn và thiết kế được các công cụ kiểm tra, đánh giá kết quả học tập của người học về kiến thức, kỹ năng và thái độ phù hợp với môn học, mô-đun, học phần được phân công giảng dạy;
+b) Thực hiện việc kiểm tra, đánh giá toàn diện, chính xác, mang tính giáo dục và đúng với các quy định.</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 08/2017/TT-BLĐTBXH · hiệu lực 2017-05-01
+3. Bãi bỏ Chương II Thông tư số 40/2015/TT-BLĐTBXH ngày 20/10/2015 của Bộ trưởng Bộ Lao động - Thương binh và Xã hội quy định chuẩn về chuyên môn, nghiệp vụ và chế độ làm việc của nhà giáo dạy trình độ sơ cấp.
+4. Trong quá trình thực hiện, nếu có vướng mắc, đề nghị phản ánh về Bộ Lao động - Thương binh và Xã hội để được hướng dẫn./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội, Hội đồng dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Chính phủ;
+- Tòa án nhân dân tối cao;
+- Viện Kiểm sát nhân dân tối cao;
+- Kiểm toán Nhà nước;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc Chính phủ;
+- Cơ quan Trung ương của các đoàn thể;
+- HĐND, UBND, Sở LĐTBXH các tỉnh, thành phố trực thuộc Trung ương;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cục Kiểm tra văn bản QPPL (Bộ Tư pháp);
+- Công báo;
+- Cổng TTĐT Chính phủ;
+- Cổng TTĐT Bộ LĐTBXH;
+- Lưu: VT, TCGDNN.
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Doãn Mậu Diệp
+CHUYỂN TIẾP: Điều 55. Điều khoản chuyển tiếp
+Nhà giáo dạy thực hành hoặc dạy tích hợp trình độ trung cấp, cao đẳng mà chưa đáp ứng chuẩn về kỹ năng nghề quy định tại Thông tư này, phải hoàn thiện để đáp ứng quy định của Thông tư này trước ngày 31 tháng 12 năm 2019.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7178,7 +8790,6 @@
           <t>2022-01-11 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -7199,9 +8810,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27435</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7217,17 +8825,30 @@
           <t>gold_wrong</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
           <t>Chuyển chỗ: 140/2018/NĐ-CP Điều 17 sửa thủ tục chung của NĐ 136/2013 và NĐ 28/2012: Hội đồng xét duyệt trợ giúp xã hội xét duyệt trong 10 ngày làm việc, niêm yết 05 ngày làm việc, kết luận khiếu nại trong 10 ngày làm việc; cùng nghị định bãi bỏ Điều 20–22 NĐ 28/2012 (Điều 18). Chỉ đổi thời hạn và tên Hội đồng</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>28/2012/NĐ-CP · hiệu lực 2012-06-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 21. Thủ tục thực hiện trợ cấp xã hội, hỗ trợ kinh phí chăm sóc hàng tháng
+1. Thủ tục thực hiện trợ cấp xã hội, hỗ trợ kinh phí chăm sóc được quy định như sau:
+a) Để được hưởng trợ cấp xã hội, hỗ trợ kinh phí chăm sóc thì người đề nghị trợ cấp hoặc hỗ trợ kinh phí chăm sóc làm hồ sơ theo quy định tại Điều 20 Nghị định này gửi Ủy ban nhân dân cấp xã;
+b) Trong thời hạn 15 ngày, kể từ ngày nhận đủ hồ sơ hợp lệ, Hội đồng xét duyệt trợ cấp xã hội xã, phường, thị trấn (sau đây gọi chung là Hội đồng xét duyệt trợ cấp xã hội) tổ chức họp, xét duyệt hồ sơ đối tượng và niêm yết công khai kết luận tại trụ sở Ủy ban nhân dân cấp xã và thông báo trên các phương tiện thông tin đại chúng trong thời gian 07 ngày;
+Khi hết thời gian niêm yết công khai, nếu không có ý kiến thắc mắc, khiếu nại thì Hội đồng xét duyệt trợ cấp xã hội bổ sung biên bản họp Hội đồng xét duyệt trợ cấp xã hội vào hồ sơ của đối tượng và trình Chủ tịch Ủy ban nhân dân cấp xã có văn bản gửi Phòng Lao động - Thương binh và Xã hội để xem xét, giải quyết.
+Trường hợp có khiếu nại, tố cáo của công dân thì trong thời hạn 10 ngày, Hội đồng xét duyệt trợ cấp xã hội tiến hành xác minh, thẩm tra, kết luận cụ thể, công khai trước nhân dân và có văn bản kết luận của Hội đồng xét duyệt trợ cấp xã hội để bổ sung vào hồ sơ của đối tượng.
+c) Trong thời hạn 07 ngày làm việc, kể từ ngày, nhận đủ hồ sơ đề nghị của Chủ tịch Ủy ban nhân dân cấp xã, Phòng Lao động - Thương binh và Xã hội có trách nhiệm thẩm định, trình Chủ tịch Ủy ban nhân dân huyện, quận, thị xã, thành phố thuộc tỉnh (sau đây gọi chung là cấp huyện) quyết định hoặc có thông báo cho Ủy ban nhân dân cấp xã về lý do không được trợ cấp xã hội hoặc hỗ trợ kinh phí chăm sóc;
+d) Trong thời hạn 03 ngày làm việc, Chủ tịch Ủy ban nhân dân cấp huyện có trách nhiệm xem xét và ký Quyết định trợ cấp xã hội hoặc hỗ trợ kinh phí chăm sóc.</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 140/2018/NĐ-CP · hiệu lực 2018-10-08
+Điều 18. Bãi bỏ Điều 20, Điều 21, Điều 22 Nghị định số 28/2012/NĐ-CP ngày 10 tháng 4 năm 2012 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật người khuyết tật; Điều 21 Nghị định số 136/2013/NĐ-CP ngày 21 tháng 10 năm 2013 của Chính phủ quy định chính sách trợ giúp xã hội đối với đối tượng bảo trợ xã hội.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7255,7 +8876,6 @@
           <t>2023-08-21 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -7276,9 +8896,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37330</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7289,18 +8906,37 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
           <t>103/2021/TT-BTC (một bộ, thay thông tư liên tịch, yếu tố 6 không đạt) đổi ngưỡng sử dụng Quỹ thành 7–10% và trên 10% (yếu tố 3 không đạt)</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>39/2014/TTLT-BCT-BTC · hiệu lực 2014-11-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 7. Cơ chế sử dụng Quỹ Bình ổn giá
+2. Phương thức sử dụng Quỹ Bình ổn giá
+a) Nghiêm cấm sử dụng Quỹ Bình ổn giá để cấp vốn kinh doanh hoặc cho các mục đích khác ngoài quy định tại khoản 1 Điều 6 Thông tư này;
+b) Quỹ Bình ổn giá được sử dụng trong các trường hợp sau:
+- Trường hợp các yếu tố cấu thành biến động làm cho giá cơ sở kỳ công bố tăng trong phạm vi đến ba phần trăm (≤ 03%) so với giá cơ sở liền kề trước đó, nhưng việc tăng giá ảnh hưởng đến tình hình kinh tế - xã hội và đời sống nhân dân, Liên Bộ Công Thương - Tài chính xem xét sử dụng Quỹ Bình ổn giá để điều hành giá xăng dầu;
+- Trường hợp các yếu tố cấu thành biến động làm cho giá cơ sở tăng vượt ba phần trăm (&gt; 03%) đến bốn phần trăm (≤ 04%) so với giá cơ sở liền kề trước đó, thương nhân đầu mối được quyền điều chỉnh giá bán tăng trong phạm vi đến ba phần trăm (≤ 03%) và được sử dụng Quỹ Bình ổn giá đối với phần tăng vượt ba phần trăm (&gt; 03%) đến bốn phần trăm (≤ 04%). Thương nhân đầu mối gửi văn bản kê khai giá, dự kiến mức điều chỉnh giá tới Liên Bộ Công Thương - Tài chính;
+- Trường hợp các yếu tố cấu thành biến động làm cho giá cơ sở tăng vượt bốn phần trăm (&gt; 04%) đến bảy phần trăm (≤ 07%) so với giá cơ sở liền kề trước đó, thương nhân đầu mối được quyền điều chỉnh giá bán tăng trong phạm vi đến ba phần trăm (≤ 03%) cộng (+) thêm năm mươi phần trăm (50%) của mức chênh lệch giá tính từ tỷ lệ giá cơ sở tăng vượt ba (&gt; 03%) đến tỷ lệ tăng thực tế trong phạm vi tăng vượt từ ba phần trăm (&gt; 03%) đến bảy phần trăm (≤ 07%); năm mươi phần trăm (50%) còn lại được bù đắp từ Quỹ Bình ổn giá. Thương nhân đầu mối gửi văn bản kê khai giá, dự kiến mức điều chỉnh giá tới Liên Bộ Công Thương - Tài chính;
+c) Sử dụng Quỹ Bình ổn giá theo quy định tại điểm b Khoản này phù hợp với thời gian giữa hai (02) lần điều chỉnh giá;
+d) Trường hợp các yếu tố cấu thành biến động làm cho giá cơ sở tăng trên bảy phần trăm (&gt; 07%) so với giá cơ sở liền kề trước đó hoặc việc tăng giá xăng dầu có tác động bất lợi đến phát triển kinh tế, xã hội và đời sống của nhân dân, Bộ Công Thương chủ trì phối hợp Bộ Tài chính báo cáo</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 103/2021/TT-BTC · hiệu lực 2022-01-02
+Bãi bỏ Điều 6, Điều 7, Điều 8, Điều 9 Thông tư liên tịch số 39/2014/TTLT-BCT-BTC ngày 29 tháng 10 năm 2014 của Bộ Công Thương, Bộ Tài chính quy định về phương pháp tính giá cơ sở; cơ chế hình thành, quản lý, sử dụng Quỹ bình ổn giá xăng dầu và điều hành giá xăng dầu theo quy định tại Nghị định số 83/2014/NĐ-CP ngày 03 tháng 9 năm 2014 của Chính phủ về kinh doanh xăng dầu; Khoản 4 Điều 1 Thông tư liên tịch số 90/2016/TTLT-BTC-BCT ngày 24 tháng 6 năm 2016 của Bộ Tài chính, Bộ Công Thương sửa đổi, bổ sung một số điều của Thông tư liên tịch số 39/2014/TTLT-BCT-BTC ngày 29 tháng 10 năm 2014 của Bộ Công Thương, Bộ Tài chính quy định về phương pháp tính giá cơ sở, cơ chế hình thành, quản lý, sử dụng Quỹ bình ổn giá xăng dầu và điều hành giá xăng dầu theo quy định tại Nghị định số 83/2014/NĐ-CP ngày 03 tháng 9 năm 2014 của Chính phủ về kinh doanh xăng dầu và các quy định trước đây trái với quy định tại Thông tư này.
+2. Giao Cục Quản lý Giá (Bộ Tài chính) chủ trì phối hợp với các đơn vị khác có liên quan hướng dẫn, tổ chức triển khai và kiểm tra thực hiện Thông tư này theo quy định.
+3. Các thương nhân đầu mối kinh doanh xăng dầu có trách nhiệm thực hiện và tổng hợp số liệu thực tế tại đơn vị, công khai, báo cáo về Bộ Tài chính (Cục Quản lý Giá), Bộ Công Thương (Vụ Thị trường trong nước) theo đúng quy định tại Thông tư này.
+Trong quá trình triển khai thực hiện, nếu có khó khăn, vướng mắc đề nghị kịp thời phản ánh về Bộ Tài chính (Cục Quản lý Giá) để nghiên cứu, sửa đổi, bổ sung cho phù hợp./.
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+Tạ Anh Tuấn</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7353,9 +8989,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135710</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7366,14 +8999,151 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>33/2019/TT-BTC · hiệu lực 2019-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Tổ chức thực hiện và điều khoản thi hành
+2. Biểu mức thu phí khai thác, sử dụng thông tin dữ liệu đo đạc và bản đồ ban hành kèm theo Thông tư số 196/2016/TT-BTC ngày 08 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí khai thác, sử dụng thông tin dữ liệu đo đạc và bản đồ được thay thế bằng Biểu mức thu phí ban hành kèm theo Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>[repeal] 47/2024/TT-BTC · hiệu lực 2024-09-01
+c) Bãi bỏ Điều 2, khoản 2 Điều 3 và Biểu mức thu phí khai thác, sử dụng thông tin dữ liệu đo đạc và bản đồ ban hành kèm theo Thông tư số 33/2019/TT-BTC ngày 10 tháng 6 năm 2019 của Bộ trưởng Bộ Tài chính sửa đổi, bổ sung một số điều của Thông tư số 34/2017/TT-BTC ngày 21 tháng 4 năm 2017 quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí thẩm định cấp giấy phép hoạt động đo đạc và bản đồ và Thông tư số 196/2016/TT-BTC ngày 08 tháng 11 năm 2016 quy định mức thu, chế độ thu, nộp, quản lý và sử dụng phí khai thác, sử dụng thông tin dữ liệu đo đạc và bản đồ.
+3. Các nội dung khác liên quan đến thu, nộp, quản lý, sử dụng, chứng từ thu, công khai chế độ thu phí khai thác, sử dụng thông tin dữ liệu đo đạc và bản đồ không đề cập tại Thông tư này được thực hiện theo quy định tại các văn bản: Luật Phí và lệ phí; Nghị định số 120/2016/NĐ-CP ngày 23 tháng 8 năm 2016 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Phí và lệ phí; Nghị định số 82/2023/NĐ-CP; Luật Quản lý thuế; Nghị định số 126/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định chi tiết một số điều của Luật Quản lý thuế, Nghị định số 91/2022/NĐ-CP ngày 30 tháng 10 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 126/2020/NĐ-CP; Nghị định số 11/2020/NĐ-CP ngày 20 tháng 01 năm 2020 của Chính phủ quy định về thủ tục hành chính thuộc lĩnh vực Kho bạc Nhà nước; Nghị định số 123/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định về hoá đơn, chứng từ; Thông tư số 78/2021/TT-BTC ngày 17 tháng 9 năm 2021 của Bộ trưởng Bộ Tài chính hướng dẫn thực hiện một số điều của Luật Quản lý thuế ngày 13 tháng 6 năm 2019, Nghị định số 123/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định về hoá đơn, chứng từ.
+4. Trường hợp các văn bản quy phạm pháp luật nêu tại Thông tư này được sửa đổi, bổ sung hoặc thay thế thì thực hiện theo văn bản mới được sửa đổi, bổ sung hoặc thay thế.
+5. Trong quá trình thực hiện, nếu có vướng mắc đề nghị các tổ chức, cá nhân phản ánh kịp thời về Bộ Tài chính để nghiên cứu, hướng dẫn bổ sung./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Văn phòng Trung ương Đảng và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Quốc hội;
+- Hội đồng dân tộc;
+- Ủy ban Tài chính, Ngân sách;
+- Văn phòng Chủ tịch nước;
+- Viện Kiểm sát nhân dân tối cao;
+- Tòa án nhân dân tối cao;
+- Kiểm toán Nhà nước;
+- Cơ quan trung ương của các Hội, Đoàn thể;
+- Các bộ, cơ quan ngang Bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Sở Tài chính, Cục Thuế, KBNN các tỉnh, thành phố
+trực thuộc trung ương;
+- Cục Kiểm tra văn bản quy phạm pháp luật, Bộ Tư pháp;
+- Công báo;
+- Cổng thông tin điện tử Chính phủ;
+- Cổng thông tin điện tử Bộ Tài chính;
+- Các đơn vị thuộc Bộ Tài chính;
+- Lưu: VT, Cục CST (300b).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Cao Anh Tuấn
+BIÊU MỨC THU PHÍ KHAI THÁC, SỬ DỤNG
+THÔNG TIN DỮ LIỆU ĐO ĐẠC VÀ BẢN ĐỒ
+(Kèm theo Thông tư số 47/2024/TT-BTC ngày 10 tháng 7 năm 2024 của Bộ trưởng Bộ Tài chính)
+Số TT
+Loại thông tin, dữ liệu
+Đơn vị tính
+Mức thu (đồng)
+Ghi chú
+I
+Số liệu của mạng lưới đo đạc quốc gia
+1
+Số liệu của mạng lưới tọa độ quốc gia
+1.1
+Cấp 0
+điểm
+340.000
+1.2
+Hạng I
+điểm
+250.000
+1.3
+Hạng II
+điểm
+220.000
+1.4
+Hạng III
+điểm
+200.000
+Áp dụng cho cả các điểm địa chính cơ sở
+2
+Số liệu của mạng lưới độ cao quốc gia
+2.1
+Hạng I
+điểm
+160.000
+2.2
+Hạng II
+điểm
+150.000
+2.3
+Hạng III
+điểm
+120.000
+3
+Số liệu của mạng lưới trọng lực quốc gia
+3.1
+Điểm cơ sở
+điểm
+200.000
+3.2
+Hạng I
+điểm
+160.000
+3.3
+Hạng II
+điểm
+140.000
+4
+Ghi chú điểm tọa độ quốc gia, độ cao quốc gia, trọng lực quốc gia
+tờ
+20.000
+II
+Dữ liệu ảnh hàng không
+1
+Dữ liệu ảnh hàng không kỹ thuật số
+file
+250.000
+2
+Dữ liệu ảnh hàng không quét từ tờ phim độ phân giải 16 μm
+file
+250.000
+3
+Dữ liệu ảnh hàng không quét từ tờ phim độ phân giải 20 μm
+file
+200.000
+4
+Dữ liệu ảnh hàng không quét từ tờ phim độ phân giải 22 μm
+file
+150.000
+5
+Bình đồ ảnh số tỷ lệ: 1:2.000; 1:5.000
+mảnh
+60.000
+6
+Bình đồ ảnh số tỷ lệ: 1:10.000; 1:25.000; 1:50.000
+mảnh
+70.000
+III
+Cơ sở dữ liệu nền địa lý quốc gia và hệ thống bản đồ địa hình quốc gia
+1
+Cơ sở dữ liệu nền địa lý quốc gia
+1.1
+Cơ sở dữ liệu nền địa lý quốc gia tỷ lệ 1:2.000
+mảnh
+400.000
+1. Nếu chọn lọc nội dung theo dữ liệu thành phần thì mức thu phí như sau:
+a) Các nhóm lớp dữ liệu: địa hình; dân cư; giao thông; thuỷ văn: thu bằng 1/6 mức thu phí nhân với hệ số 1,2.
+b) Các nhóm lớp dữ liệu: địa giới hành chính, biên giới quốc gia; lớp phủ bề mặt: thu bằng 1/6 mức thu phí.
+2. Nếu đã thu phí sử dụng cơ sở dữ liệu nền địa lý quốc gia thì không thu phí sử dụng bản đồ địa hình quốc gia định dạng số cùng tỷ lệ (chỉ áp dụng trong trường hợp khai thác theo mảnh và đủ 07 nhóm lớp dữ liệu).
+3. Trường hợp khai thác dữ liệu theo phạm vi địa lý thì thu bằng mức thu phí nhân với diện tích khu vực khai thác chia tổng diện tích các mảnh theo tỷ lệ tương ứng. (diện tích tối thiểu đề nghị khai thác bằng diện tích 01 mảnh bản đồ cùng tỷ lệ).
+1.2
+Cơ sở dữ liệu nền đị [...cắt bớt]</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7401,7 +9171,6 @@
           <t>2025-09-29 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -7422,9 +9191,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=57219</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7435,18 +9201,26 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
           <t>30/2022/TT-BNNPTNT hướng dẫn nhiệm vụ của Sở, Phòng; không thấy nhiệm vụ của Chi cục Phát triển nông thôn (yếu tố 2 không đạt)</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>15/2015/TT-BNNPTNT · hiệu lực 2015-05-12 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 6. Nhiệm vụ Chi cục Phát triển nông thôn
+2. Hướng dẫn, tổ chức thực hiện các văn bản quy phạm pháp luật, quy hoạch, kế hoạch, chương trình, đề án, dự án, tiêu chuẩn, quy chuẩn kỹ thuật, quy trình, quy phạm, định mức kinh tế-kỹ thuật đã được phê duyệt. Thông tin, tuyên truyền, phổ biến pháp luật chuyên ngành, lĩnh vực thuộc phạm vi quản lý.</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 30/2022/TT-BNNPTNT · hiệu lực 2023-03-31
+b) Điều 1, Điều 2, Điều 3, Điều 4, Điều 5, Điều 6, Điều 7 Thông tư số 15/2015/TT-BNNPTNT ngày 26 tháng 3 năm 2015 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn hướng dẫn nhiệm vụ các chi cục và các tổ chức sự nghiệp trực thuộc Sở Nông nghiệp và Phát triển nông thôn;
+c) Khoản 2 Điều 9 Thông tư số 15/2015/TT-BNNPTNT ngày 26 tháng 3 năm 2015 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn được sửa đổi, bổ sung tại Điều 1 Thông tư số 30/2016/TT-BNNPTNT ngày 25 tháng 8 năm 2016 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn sửa đổi, bổ sung Điều 9 Thông tư số 15/2015/TT-BNNPTNT ngày 26 tháng 3 năm 2015 hướng dẫn nhiệm vụ các chi cục và các tổ chức sự nghiệp trực thuộc Sở Nông nghiệp và Phát triển nông thôn;
+d) Khoản 2 Điều 2 Thông tư số 30/2016/TT-BNNPTNT ngày 25 tháng 8 năm 2016 của Bộ trưởng Bộ Nông nghiệp và Phát triển nông thôn sửa đổi, bổ sung Điều 9 Thông tư số 15/2015/TT-BNNPTNT ngày 26 tháng 3 năm 2015 hướng dẫn nhiệm vụ các chi cục và các tổ chức sự nghiệp trực thuộc Sở Nông nghiệp và Phát triển nông thôn.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7499,9 +9273,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112967</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7512,14 +9283,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>83/2016/TT-BTC · hiệu lực 2016-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 5. Hướng dẫn về ưu đãi thuế nhập khẩu
+8. Hồ sơ, thủ tục miễn thuế nhập khẩu, báo cáo kiểm tra việc sử dụng hàng hóa miễn thuế:
+a) Hàng hóa nhập khẩu miễn thuế của dự án đầu tư nêu tại khoản 1, khoản 2, khoản 3, khoản 4, khoản 5, khoản 6 Điều này thuộc trường hợp phải đăng ký Danh mục hàng hóa nhập khẩu miễn thuế. Khi đăng ký Danh mục hàng hóa nhập khẩu miễn thuế với cơ quan hải quan, chủ dự án đầu tư có trách nhiệm nộp 01 bản chụp, xuất trình bản chính Giấy chứng nhận đăng ký đầu tư hoặc văn bản quyết định chủ trương đầu tư có ghi nội dung dự án đầu tư có quy mô vốn từ 6.000 tỷ đồng trở lên, thực hiện giải ngân tối thiểu 6.000 tỷ đồng trong thời hạn 03 năm kể từ ngày được cấp Giấy chứng nhận đăng ký đầu tư hoặc kể từ ngày được quyết định chủ trương đầu tư hoặc dự án đầu tư tại vùng nông thôn sử dụng từ 500 lao động trở lên. Trường hợp dự án đầu tư tại vùng nông thôn sử dụng từ 500 lao động trở lên không thuộc diện cấp Giấy chứng nhận đăng ký đầu tư hoặc quyết định chủ trương đầu tư, chủ dự án đầu tư nộp 01 bản chính văn bản thông báo về thông tin về lao động và tiến độ thực hiện dự án, 01 bản chụp, xuất trình bản chính Luận chứng kinh tế kỹ thuật/Tài liệu kinh tế, kỹ thuật. Việc đăng ký Danh mục hàng hóa nhập khẩu miễn thuế nhập khẩu thực hiện theo hướng dẫn tại Điều 104 Thông tư số 38/2015/TT-BTC ngày 25/3/2015 của Bộ Tài chính hướng dẫn về thủ tục hải quan; kiểm tra, giám sát hải quan; thuế xuất khẩu, thuế nhập khẩu và quản lý thuế đối với hàng hóa xuất khẩu, nhập khẩu (sau đây gọi là Thông tư số 38/2015/TT-BTC).
+b) Hồ sơ, thủ tục miễn thuế nhập khẩu đối với các dự án đầu tư nêu tại khoản 1, khoản 2, khoản 3, khoản 4, khoản 5, khoản 6 Điều này thực hiện theo hướng dẫn tại Điều 105 Thông tư số 38/2015/TT-BTC.
+c) Báo cáo, kiểm tra việc sử dụng hàng hóa miễn thuế nhập khẩu của các dự án đầu tư nêu tại khoản 1, khoản 2, khoản 3, khoản 4, khoản 5, khoản 6 Điều này thực hiện theo hướng dẫn tại Điều 106 Thông tư số 38/2015/TT-BTC.</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 18/2021/NĐ-CP · hiệu lực 2021-04-25
+c) Bãi bỏ Điều 5 Thông tư số 83/2016/TT-BTC ngày 17 tháng 6 năm 2016 của Bộ Tài chính về việc hướng dẫn thực hiện ưu đãi đầu tư quy định tại Luật Đầu tư số 67/2014/QH13 và Nghị định số 118/2015/NĐ-CP ngày 12 tháng 11 năm 2015 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư.
+CHUYỂN TIẾP: 3. Quy định về chuyển tiếp ưu đãi thuế nhập khẩu cho đối tượng được miễn thuế nhập khẩu quy định tại khoản 9 Điều 1 Nghị định này:
+Đối với các dự án đầu tư, trồng sản phẩm nông sản thuộc Danh mục quy định tại Phụ lục VIII ban hành kèm theo Nghị định này đang được hưởng chính sách ưu đãi thuế theo quy định của pháp luật thuế xuất khẩu, nhập khẩu trước ngày Nghị định này có hiệu lực thi hành thì tiếp tục được hưởng chính sách miễn thuế nhập khẩu theo quy định tại khoản 9 Điều 1 Nghị định này trong thời gian còn lại của Giấy chứng nhận đầu tư ra nước ngoài đã được cơ quan nhà nước có thẩm quyền cấp.
+Trường hợp Campuchia điều chỉnh địa giới hành chính dẫn đến tên tỉnh Campuchia nêu tại Giấy chứng nhận đầu tư ra nước ngoài của doanh nghiệp đang được hưởng chính sách ưu đãi miễn thuế theo quy định tại khoản 9 Điều 1 Nghị định này không còn là tỉnh tiếp giáp biên giới Việt Nam thì doanh nghiệp tiếp tục được hưởng chính sách ưu đãi miễn thuế nhập khẩu theo quy định tại khoản 9 Điều 1 Nghị định này trong thời gian còn lại của Giấy chứng nhận đầu tư ra nước ngoài đã được cơ quan nhà nước có thẩm quyền cấp.
+4. Quy định chuyển tiếp đối với hàng hóa xuất khẩu tại chỗ, nhập khẩu tại chỗ:
+Việc áp dụng thuế suất đối với hàng hoá xuất khẩu tại chỗ, nhập khẩu tại chỗ theo quy định tại khoản 1 Điều 1 Nghị định này được áp dụng kể từ ngày Luật Thuế xuất khẩu, thuế nhập khẩu số 107/2016/QH13 có hiệu lực thi hành.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7547,7 +9331,6 @@
           <t>2023-07-20 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>(không có đáp án: provision_repealed)</t>
@@ -7568,9 +9351,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112967</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7581,18 +9361,32 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
           <t>18/2021/NĐ-CP (Chính phủ) bãi bỏ Điều 5 TT 83/2016 của Bộ Tài chính và tự quy định hồ sơ miễn thuế: cơ quan ban hành khác (yếu tố 6 không đạt)</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>83/2016/TT-BTC · hiệu lực 2016-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 5. Hướng dẫn về ưu đãi thuế nhập khẩu
+8. Hồ sơ, thủ tục miễn thuế nhập khẩu, báo cáo kiểm tra việc sử dụng hàng hóa miễn thuế:
+a) Hàng hóa nhập khẩu miễn thuế của dự án đầu tư nêu tại khoản 1, khoản 2, khoản 3, khoản 4, khoản 5, khoản 6 Điều này thuộc trường hợp phải đăng ký Danh mục hàng hóa nhập khẩu miễn thuế. Khi đăng ký Danh mục hàng hóa nhập khẩu miễn thuế với cơ quan hải quan, chủ dự án đầu tư có trách nhiệm nộp 01 bản chụp, xuất trình bản chính Giấy chứng nhận đăng ký đầu tư hoặc văn bản quyết định chủ trương đầu tư có ghi nội dung dự án đầu tư có quy mô vốn từ 6.000 tỷ đồng trở lên, thực hiện giải ngân tối thiểu 6.000 tỷ đồng trong thời hạn 03 năm kể từ ngày được cấp Giấy chứng nhận đăng ký đầu tư hoặc kể từ ngày được quyết định chủ trương đầu tư hoặc dự án đầu tư tại vùng nông thôn sử dụng từ 500 lao động trở lên. Trường hợp dự án đầu tư tại vùng nông thôn sử dụng từ 500 lao động trở lên không thuộc diện cấp Giấy chứng nhận đăng ký đầu tư hoặc quyết định chủ trương đầu tư, chủ dự án đầu tư nộp 01 bản chính văn bản thông báo về thông tin về lao động và tiến độ thực hiện dự án, 01 bản chụp, xuất trình bản chính Luận chứng kinh tế kỹ thuật/Tài liệu kinh tế, kỹ thuật. Việc đăng ký Danh mục hàng hóa nhập khẩu miễn thuế nhập khẩu thực hiện theo hướng dẫn tại Điều 104 Thông tư số 38/2015/TT-BTC ngày 25/3/2015 của Bộ Tài chính hướng dẫn về thủ tục hải quan; kiểm tra, giám sát hải quan; thuế xuất khẩu, thuế nhập khẩu và quản lý thuế đối với hàng hóa xuất khẩu, nhập khẩu (sau đây gọi là Thông tư số 38/2015/TT-BTC).
+b) Hồ sơ, thủ tục miễn thuế nhập khẩu đối với các dự án đầu tư nêu tại khoản 1, khoản 2, khoản 3, khoản 4, khoản 5, khoản 6 Điều này thực hiện theo hướng dẫn tại Điều 105 Thông tư số 38/2015/TT-BTC.
+c) Báo cáo, kiểm tra việc sử dụng hàng hóa miễn thuế nhập khẩu của các dự án đầu tư nêu tại khoản 1, khoản 2, khoản 3, khoản 4, khoản 5, khoản 6 Điều này thực hiện theo hướng dẫn tại Điều 106 Thông tư số 38/2015/TT-BTC.</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>[repeal_ancestor] 18/2021/NĐ-CP · hiệu lực 2021-04-25
+c) Bãi bỏ Điều 5 Thông tư số 83/2016/TT-BTC ngày 17 tháng 6 năm 2016 của Bộ Tài chính về việc hướng dẫn thực hiện ưu đãi đầu tư quy định tại Luật Đầu tư số 67/2014/QH13 và Nghị định số 118/2015/NĐ-CP ngày 12 tháng 11 năm 2015 của Chính phủ quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư.
+CHUYỂN TIẾP: 3. Quy định về chuyển tiếp ưu đãi thuế nhập khẩu cho đối tượng được miễn thuế nhập khẩu quy định tại khoản 9 Điều 1 Nghị định này:
+Đối với các dự án đầu tư, trồng sản phẩm nông sản thuộc Danh mục quy định tại Phụ lục VIII ban hành kèm theo Nghị định này đang được hưởng chính sách ưu đãi thuế theo quy định của pháp luật thuế xuất khẩu, nhập khẩu trước ngày Nghị định này có hiệu lực thi hành thì tiếp tục được hưởng chính sách miễn thuế nhập khẩu theo quy định tại khoản 9 Điều 1 Nghị định này trong thời gian còn lại của Giấy chứng nhận đầu tư ra nước ngoài đã được cơ quan nhà nước có thẩm quyền cấp.
+Trường hợp Campuchia điều chỉnh địa giới hành chính dẫn đến tên tỉnh Campuchia nêu tại Giấy chứng nhận đầu tư ra nước ngoài của doanh nghiệp đang được hưởng chính sách ưu đãi miễn thuế theo quy định tại khoản 9 Điều 1 Nghị định này không còn là tỉnh tiếp giáp biên giới Việt Nam thì doanh nghiệp tiếp tục được hưởng chính sách ưu đãi miễn thuế nhập khẩu theo quy định tại khoản 9 Điều 1 Nghị định này trong thời gian còn lại của Giấy chứng nhận đầu tư ra nước ngoài đã được cơ quan nhà nước có thẩm quyền cấp.
+4. Quy định chuyển tiếp đối với hàng hóa xuất khẩu tại chỗ, nhập khẩu tại chỗ:
+Việc áp dụng thuế suất đối với hàng hoá xuất khẩu tại chỗ, nhập khẩu tại chỗ theo quy định tại khoản 1 Điều 1 Nghị định này được áp dụng kể từ ngày Luật Thuế xuất khẩu, thuế nhập khẩu số 107/2016/QH13 có hiệu lực thi hành.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
